--- a/dwl-fantasy-platform/backend/WWC_Config.xlsx
+++ b/dwl-fantasy-platform/backend/WWC_Config.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kishan/Downloads/Delulu Leagues/DWL Delulu Women's League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0A5AF84-1DA0-40B9-B2F8-F81E4F27644B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC40D813-FAD6-49CE-8E95-F1785420A2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" firstSheet="4" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="1" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
     <sheet name="DWLTeams" sheetId="2" r:id="rId2"/>
-    <sheet name="CT" sheetId="5" r:id="rId3"/>
-    <sheet name="GD" sheetId="4" r:id="rId4"/>
-    <sheet name="JR" sheetId="10" r:id="rId5"/>
-    <sheet name="KQ" sheetId="9" r:id="rId6"/>
-    <sheet name="RR" sheetId="11" r:id="rId7"/>
-    <sheet name="SS" sheetId="7" r:id="rId8"/>
+    <sheet name="GD" sheetId="4" r:id="rId3"/>
+    <sheet name="JR" sheetId="10" r:id="rId4"/>
+    <sheet name="KQ" sheetId="9" r:id="rId5"/>
+    <sheet name="RR" sheetId="11" r:id="rId6"/>
+    <sheet name="SS" sheetId="7" r:id="rId7"/>
+    <sheet name="SGS" sheetId="5" r:id="rId8"/>
     <sheet name="VW" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -130,7 +130,7 @@
     <t>Phoebe Litchfield</t>
   </si>
   <si>
-    <t>Chennai Thunder</t>
+    <t>Singara Singapengal</t>
   </si>
   <si>
     <t>Sophie Molineux</t>
@@ -676,9 +676,6 @@
     <t>Team Name</t>
   </si>
   <si>
-    <t>CT</t>
-  </si>
-  <si>
     <t>GD</t>
   </si>
   <si>
@@ -694,10 +691,13 @@
     <t>SS</t>
   </si>
   <si>
+    <t>SGS</t>
+  </si>
+  <si>
     <t>VW</t>
   </si>
   <si>
-    <t>CHENNAI THUNDER</t>
+    <t>GULLY DIVAS</t>
   </si>
   <si>
     <t>Team Player No.</t>
@@ -706,15 +706,12 @@
     <t>Captain/ Vice-Captain</t>
   </si>
   <si>
+    <t>Vice-Captain</t>
+  </si>
+  <si>
     <t>Captain</t>
   </si>
   <si>
-    <t>Vice-Captain</t>
-  </si>
-  <si>
-    <t>GULLY DIVAS</t>
-  </si>
-  <si>
     <t>JANAKI ROYALS</t>
   </si>
   <si>
@@ -728,6 +725,9 @@
   </si>
   <si>
     <t>SARAFA STRIKERS</t>
+  </si>
+  <si>
+    <t>SINGARA SINGAPENGAL</t>
   </si>
   <si>
     <t>VANITHA WARRIORS</t>
@@ -771,12 +771,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="28"/>
-      <color rgb="FF0070C0"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -842,8 +836,14 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FF33764E"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -988,6 +988,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33764E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD700"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1036,27 +1048,12 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1065,16 +1062,7 @@
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1086,9 +1074,33 @@
     <xf numFmtId="0" fontId="1" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1133,6 +1145,47 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FF046307"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF33764E"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1337,47 +1390,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1398,6 +1410,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFD700"/>
+      <color rgb="FF33764E"/>
       <color rgb="FF046307"/>
       <color rgb="FF0B0C10"/>
       <color rgb="FFE759AC"/>
@@ -1406,8 +1420,6 @@
       <color rgb="FF800080"/>
       <color rgb="FFFAEBC8"/>
       <color rgb="FFD4B631"/>
-      <color rgb="FFFCD732"/>
-      <color rgb="FFB7A680"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1455,110 +1467,110 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FF09F066-F6AA-4643-AA12-841C9478CEE4}" name="CT" displayName="CT" ref="A5:D23" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
-  <autoFilter ref="A5:D23" xr:uid="{FF09F066-F6AA-4643-AA12-841C9478CEE4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}" name="BL" displayName="BL" ref="A5:D23" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41" tableBorderDxfId="40">
+  <autoFilter ref="A5:D23" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{74BA643C-B079-8B4F-8344-2C9B9BC12707}" name="Team Player No." dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{432B80D9-19D7-AF43-AB9E-82D1257517E4}" name="Player Name" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{AA077A69-6CDA-934A-8174-723FA3593002}" name="Country" dataDxfId="38">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{08FE8A15-D3B6-DF4B-88B3-A051E62A20E6}" name="Team Player No." dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{4ECD4789-FFEE-F647-8611-EA766F1EEB38}" name="Player Name" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{E23434DC-5066-554A-A1F3-30A49F38C773}" name="Country" dataDxfId="37">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3A3DF73D-E88E-1644-A4F0-7B6F72118B2E}" name="Captain/ Vice-Captain" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{B716E680-D978-7440-AE9C-6B18870AC674}" name="Captain/ Vice-Captain" dataDxfId="36"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{BA0A3757-C1BF-6F4E-8593-2BAF45FE9FDE}" name="NR" displayName="NR" ref="A5:D23" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+  <autoFilter ref="A5:D23" xr:uid="{BA0A3757-C1BF-6F4E-8593-2BAF45FE9FDE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
+    <sortCondition ref="B5:B23"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{9685E0E1-CFC1-4D4C-9DA8-9D0D67FFF359}" name="Team Player No." dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{4127652B-4321-704E-8135-B6E29F440927}" name="Player Name" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{7E01B81D-BAB5-574F-BBB7-719FC4E16DC4}" name="Country" dataDxfId="31">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{0C3C6BB9-DD76-DD4A-97EF-189E0310831A}" name="Captain/ Vice-Captain" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}" name="MB" displayName="MB" ref="A5:D23" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A5:D23" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
+    <sortCondition ref="B5:B23"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0D27ED80-3738-7F47-94AF-0A6B61961EB3}" name="Team Player No." dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{267FF8CD-F86C-DE4D-922E-8D12B710755E}" name="Player Name" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{20C938BF-DCD0-1941-ACC8-F620B1FDFF4A}" name="Country" dataDxfId="25">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{BC210CBE-A244-1A47-9738-6D3C52D2F342}" name="Captain/ Vice-Captain" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}" name="BL" displayName="BL" ref="A5:D23" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35" tableBorderDxfId="34">
-  <autoFilter ref="A5:D23" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}"/>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{695645B6-531C-9947-BD49-AB7DD4777E06}" name="RR" displayName="RR" ref="A5:D23" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="A5:D23" xr:uid="{695645B6-531C-9947-BD49-AB7DD4777E06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{08FE8A15-D3B6-DF4B-88B3-A051E62A20E6}" name="Team Player No." dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{4ECD4789-FFEE-F647-8611-EA766F1EEB38}" name="Player Name" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{E23434DC-5066-554A-A1F3-30A49F38C773}" name="Country" dataDxfId="31">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{234B9EE4-D33E-1447-BB49-68C355C76983}" name="Team Player No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{F46522FB-98C6-BD44-8237-8D453678EEE8}" name="Player Name" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{420600D5-2F08-1849-A91C-2F03DFE81977}" name="Country" dataDxfId="19">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B716E680-D978-7440-AE9C-6B18870AC674}" name="Captain/ Vice-Captain" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{F0D8CC44-F2B1-B443-B44A-5AE8610B9D3B}" name="Captain/ Vice-Captain" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{BA0A3757-C1BF-6F4E-8593-2BAF45FE9FDE}" name="NR" displayName="NR" ref="A5:D23" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A5:D23" xr:uid="{BA0A3757-C1BF-6F4E-8593-2BAF45FE9FDE}"/>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{649331E8-BE4C-7A4A-8F63-4638AD1C1FDD}" name="KKR" displayName="KKR" ref="A5:D23" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A5:D23" xr:uid="{649331E8-BE4C-7A4A-8F63-4638AD1C1FDD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9685E0E1-CFC1-4D4C-9DA8-9D0D67FFF359}" name="Team Player No." dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{4127652B-4321-704E-8135-B6E29F440927}" name="Player Name" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{7E01B81D-BAB5-574F-BBB7-719FC4E16DC4}" name="Country" dataDxfId="25">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{31A5AA7F-D358-494F-8889-0D3934B9DF61}" name="Team Player No." dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{196D6C69-3CAF-0A44-BF6D-64F1AC14B9D2}" name="Player Name" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{9DCA5DAF-0152-FA41-87A0-FBE7254C3CCC}" name="Country" dataDxfId="13">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0C3C6BB9-DD76-DD4A-97EF-189E0310831A}" name="Captain/ Vice-Captain" dataDxfId="24"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}" name="MB" displayName="MB" ref="A5:D23" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
-  <autoFilter ref="A5:D23" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
-    <sortCondition ref="B5:B23"/>
-  </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0D27ED80-3738-7F47-94AF-0A6B61961EB3}" name="Team Player No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{267FF8CD-F86C-DE4D-922E-8D12B710755E}" name="Player Name" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{20C938BF-DCD0-1941-ACC8-F620B1FDFF4A}" name="Country" dataDxfId="19">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{BC210CBE-A244-1A47-9738-6D3C52D2F342}" name="Captain/ Vice-Captain" dataDxfId="18"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{695645B6-531C-9947-BD49-AB7DD4777E06}" name="RR" displayName="RR" ref="A5:D23" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A5:D23" xr:uid="{695645B6-531C-9947-BD49-AB7DD4777E06}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
-    <sortCondition ref="B5:B23"/>
-  </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{234B9EE4-D33E-1447-BB49-68C355C76983}" name="Team Player No." dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{F46522FB-98C6-BD44-8237-8D453678EEE8}" name="Player Name" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{420600D5-2F08-1849-A91C-2F03DFE81977}" name="Country" dataDxfId="13">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{F0D8CC44-F2B1-B443-B44A-5AE8610B9D3B}" name="Captain/ Vice-Captain" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{E65D1282-79BC-3640-9D14-2CB9941E7D9C}" name="Captain/ Vice-Captain" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{649331E8-BE4C-7A4A-8F63-4638AD1C1FDD}" name="KKR" displayName="KKR" ref="A5:D23" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A5:D23" xr:uid="{649331E8-BE4C-7A4A-8F63-4638AD1C1FDD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FF09F066-F6AA-4643-AA12-841C9478CEE4}" name="CT" displayName="CT" ref="A5:D23" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A5:D23" xr:uid="{FF09F066-F6AA-4643-AA12-841C9478CEE4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{31A5AA7F-D358-494F-8889-0D3934B9DF61}" name="Team Player No." dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{196D6C69-3CAF-0A44-BF6D-64F1AC14B9D2}" name="Player Name" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{9DCA5DAF-0152-FA41-87A0-FBE7254C3CCC}" name="Country" dataDxfId="7">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{74BA643C-B079-8B4F-8344-2C9B9BC12707}" name="Team Player No." dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{432B80D9-19D7-AF43-AB9E-82D1257517E4}" name="Player Name" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{AA077A69-6CDA-934A-8174-723FA3593002}" name="Country" dataDxfId="7">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E65D1282-79BC-3640-9D14-2CB9941E7D9C}" name="Captain/ Vice-Captain" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{3A3DF73D-E88E-1644-A4F0-7B6F72118B2E}" name="Captain/ Vice-Captain" dataDxfId="6"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1938,7 +1950,7 @@
       <c r="E2">
         <v>0.98</v>
       </c>
-      <c r="G2" s="33"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:7" ht="15.75">
       <c r="A3" s="4" t="s">
@@ -1956,7 +1968,7 @@
       <c r="E3">
         <v>14.27</v>
       </c>
-      <c r="G3" s="33"/>
+      <c r="G3" s="25"/>
     </row>
     <row r="4" spans="1:7" ht="15.75">
       <c r="A4" s="4" t="s">
@@ -1974,7 +1986,7 @@
       <c r="E4">
         <v>7.54</v>
       </c>
-      <c r="G4" s="33"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" ht="15.75">
       <c r="A5" s="4" t="s">
@@ -1992,7 +2004,7 @@
       <c r="E5">
         <v>19.12</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:7" ht="15.75">
       <c r="A6" s="4" t="s">
@@ -2010,7 +2022,7 @@
       <c r="E6">
         <v>3.86</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" ht="15.75">
       <c r="A7" s="4" t="s">
@@ -2028,7 +2040,7 @@
       <c r="E7">
         <v>11.44</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:7" ht="15.75">
       <c r="A8" s="4" t="s">
@@ -2046,7 +2058,7 @@
       <c r="E8">
         <v>6.13</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="25"/>
     </row>
     <row r="9" spans="1:7" ht="15.75">
       <c r="A9" s="4" t="s">
@@ -2064,7 +2076,7 @@
       <c r="E9">
         <v>18.940000000000001</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" spans="1:7" ht="15.75">
       <c r="A10" s="4" t="s">
@@ -2080,7 +2092,7 @@
       <c r="E10">
         <v>2.37</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="25"/>
     </row>
     <row r="11" spans="1:7" ht="15.75">
       <c r="A11" s="4" t="s">
@@ -2098,7 +2110,7 @@
       <c r="E11">
         <v>9.65</v>
       </c>
-      <c r="G11" s="33"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="1:7" ht="15.75">
       <c r="A12" s="4" t="s">
@@ -2116,7 +2128,7 @@
       <c r="E12">
         <v>15.71</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="25"/>
     </row>
     <row r="13" spans="1:7" ht="15.75">
       <c r="A13" s="4" t="s">
@@ -2134,7 +2146,7 @@
       <c r="E13">
         <v>4.28</v>
       </c>
-      <c r="G13" s="33"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="14" spans="1:7" ht="15.75">
       <c r="A14" s="4" t="s">
@@ -2152,7 +2164,7 @@
       <c r="E14">
         <v>20</v>
       </c>
-      <c r="G14" s="33"/>
+      <c r="G14" s="25"/>
     </row>
     <row r="15" spans="1:7" ht="15.75">
       <c r="A15" s="4" t="s">
@@ -2168,7 +2180,7 @@
       <c r="E15">
         <v>1.55</v>
       </c>
-      <c r="G15" s="33"/>
+      <c r="G15" s="25"/>
     </row>
     <row r="16" spans="1:7" ht="15.75">
       <c r="A16" s="4" t="s">
@@ -2186,7 +2198,7 @@
       <c r="E16">
         <v>13.09</v>
       </c>
-      <c r="G16" s="33"/>
+      <c r="G16" s="25"/>
     </row>
     <row r="17" spans="1:7" ht="15.75">
       <c r="A17" s="5" t="s">
@@ -2202,7 +2214,7 @@
       <c r="E17">
         <v>8.42</v>
       </c>
-      <c r="G17" s="33"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" spans="1:7" ht="15.75">
       <c r="A18" s="5" t="s">
@@ -2220,7 +2232,7 @@
       <c r="E18">
         <v>17.829999999999998</v>
       </c>
-      <c r="G18" s="33"/>
+      <c r="G18" s="25"/>
     </row>
     <row r="19" spans="1:7" ht="15.75">
       <c r="A19" s="5" t="s">
@@ -2238,7 +2250,7 @@
       <c r="E19">
         <v>5.61</v>
       </c>
-      <c r="G19" s="33"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" spans="1:7" ht="15.75">
       <c r="A20" s="5" t="s">
@@ -2256,7 +2268,7 @@
       <c r="E20">
         <v>10.97</v>
       </c>
-      <c r="G20" s="33"/>
+      <c r="G20" s="25"/>
     </row>
     <row r="21" spans="1:7" ht="15.75">
       <c r="A21" s="5" t="s">
@@ -2272,7 +2284,7 @@
       <c r="E21">
         <v>12.34</v>
       </c>
-      <c r="G21" s="33"/>
+      <c r="G21" s="25"/>
     </row>
     <row r="22" spans="1:7" ht="15.75">
       <c r="A22" s="5" t="s">
@@ -2290,7 +2302,7 @@
       <c r="E22">
         <v>0.72</v>
       </c>
-      <c r="G22" s="33"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" spans="1:7" ht="15.75">
       <c r="A23" s="5" t="s">
@@ -2308,7 +2320,7 @@
       <c r="E23">
         <v>16.48</v>
       </c>
-      <c r="G23" s="33"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="5" t="s">
@@ -2324,7 +2336,7 @@
       <c r="E24">
         <v>19.88</v>
       </c>
-      <c r="G24" s="33"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="5" t="s">
@@ -2340,7 +2352,7 @@
       <c r="E25">
         <v>3.15</v>
       </c>
-      <c r="G25" s="33"/>
+      <c r="G25" s="25"/>
     </row>
     <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="5" t="s">
@@ -2356,7 +2368,7 @@
       <c r="E26">
         <v>7.93</v>
       </c>
-      <c r="G26" s="33"/>
+      <c r="G26" s="25"/>
     </row>
     <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="5" t="s">
@@ -2374,7 +2386,7 @@
       <c r="E27">
         <v>14.56</v>
       </c>
-      <c r="G27" s="33"/>
+      <c r="G27" s="25"/>
     </row>
     <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="5" t="s">
@@ -2392,7 +2404,7 @@
       <c r="E28">
         <v>2.81</v>
       </c>
-      <c r="G28" s="33"/>
+      <c r="G28" s="25"/>
     </row>
     <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="5" t="s">
@@ -2410,7 +2422,7 @@
       <c r="E29">
         <v>9.19</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="5" t="s">
@@ -2428,7 +2440,7 @@
       <c r="E30">
         <v>18.27</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="25"/>
     </row>
     <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="5" t="s">
@@ -2446,7 +2458,7 @@
       <c r="E31">
         <v>6.64</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="25"/>
     </row>
     <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="6" t="s">
@@ -2464,7 +2476,7 @@
       <c r="E32">
         <v>11.05</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="25"/>
     </row>
     <row r="33" spans="1:7" ht="15.75">
       <c r="A33" s="6" t="s">
@@ -2482,7 +2494,7 @@
       <c r="E33">
         <v>20</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" spans="1:7" ht="15.75">
       <c r="A34" s="6" t="s">
@@ -2500,7 +2512,7 @@
       <c r="E34">
         <v>1.98</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" spans="1:7" ht="15.75">
       <c r="A35" s="6" t="s">
@@ -2518,7 +2530,7 @@
       <c r="E35">
         <v>13.77</v>
       </c>
-      <c r="G35" s="33"/>
+      <c r="G35" s="25"/>
     </row>
     <row r="36" spans="1:7" ht="15.75">
       <c r="A36" s="6" t="s">
@@ -2534,7 +2546,7 @@
       <c r="E36">
         <v>4.91</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="25"/>
     </row>
     <row r="37" spans="1:7" ht="15.75">
       <c r="A37" s="6" t="s">
@@ -2552,7 +2564,7 @@
       <c r="E37">
         <v>8.0299999999999994</v>
       </c>
-      <c r="G37" s="33"/>
+      <c r="G37" s="25"/>
     </row>
     <row r="38" spans="1:7" ht="15.75">
       <c r="A38" s="6" t="s">
@@ -2568,7 +2580,7 @@
       <c r="E38">
         <v>16.22</v>
       </c>
-      <c r="G38" s="33"/>
+      <c r="G38" s="25"/>
     </row>
     <row r="39" spans="1:7" ht="15.75">
       <c r="A39" s="6" t="s">
@@ -2586,7 +2598,7 @@
       <c r="E39">
         <v>0.5</v>
       </c>
-      <c r="G39" s="33"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" spans="1:7" ht="15.75">
       <c r="A40" s="6" t="s">
@@ -2602,7 +2614,7 @@
       <c r="E40">
         <v>12.69</v>
       </c>
-      <c r="G40" s="33"/>
+      <c r="G40" s="25"/>
     </row>
     <row r="41" spans="1:7" ht="15.75">
       <c r="A41" s="6" t="s">
@@ -2620,7 +2632,7 @@
       <c r="E41">
         <v>17.46</v>
       </c>
-      <c r="G41" s="33"/>
+      <c r="G41" s="25"/>
     </row>
     <row r="42" spans="1:7" ht="15.75">
       <c r="A42" s="6" t="s">
@@ -2638,7 +2650,7 @@
       <c r="E42">
         <v>5.32</v>
       </c>
-      <c r="G42" s="33"/>
+      <c r="G42" s="25"/>
     </row>
     <row r="43" spans="1:7" ht="15.75">
       <c r="A43" s="6" t="s">
@@ -2656,7 +2668,7 @@
       <c r="E43">
         <v>19.309999999999999</v>
       </c>
-      <c r="G43" s="33"/>
+      <c r="G43" s="25"/>
     </row>
     <row r="44" spans="1:7" ht="15.75">
       <c r="A44" s="6" t="s">
@@ -2672,7 +2684,7 @@
       <c r="E44">
         <v>10.5</v>
       </c>
-      <c r="G44" s="33"/>
+      <c r="G44" s="25"/>
     </row>
     <row r="45" spans="1:7" ht="15.75">
       <c r="A45" s="6" t="s">
@@ -2690,7 +2702,7 @@
       <c r="E45">
         <v>3.48</v>
       </c>
-      <c r="G45" s="33"/>
+      <c r="G45" s="25"/>
     </row>
     <row r="46" spans="1:7" ht="15.75">
       <c r="A46" s="6" t="s">
@@ -2708,7 +2720,7 @@
       <c r="E46">
         <v>15.88</v>
       </c>
-      <c r="G46" s="33"/>
+      <c r="G46" s="25"/>
     </row>
     <row r="47" spans="1:7" ht="15.75">
       <c r="A47" s="7" t="s">
@@ -2726,7 +2738,7 @@
       <c r="E47">
         <v>7.14</v>
       </c>
-      <c r="G47" s="33"/>
+      <c r="G47" s="25"/>
     </row>
     <row r="48" spans="1:7" ht="15.75">
       <c r="A48" s="7" t="s">
@@ -2744,7 +2756,7 @@
       <c r="E48">
         <v>2.09</v>
       </c>
-      <c r="G48" s="33"/>
+      <c r="G48" s="25"/>
     </row>
     <row r="49" spans="1:7" ht="15.75">
       <c r="A49" s="7" t="s">
@@ -2762,7 +2774,7 @@
       <c r="E49">
         <v>18.649999999999999</v>
       </c>
-      <c r="G49" s="33"/>
+      <c r="G49" s="25"/>
     </row>
     <row r="50" spans="1:7" ht="15.75">
       <c r="A50" s="7" t="s">
@@ -2780,7 +2792,7 @@
       <c r="E50">
         <v>9.83</v>
       </c>
-      <c r="G50" s="33"/>
+      <c r="G50" s="25"/>
     </row>
     <row r="51" spans="1:7" ht="15.75">
       <c r="A51" s="7" t="s">
@@ -2798,7 +2810,7 @@
       <c r="E51">
         <v>14.12</v>
       </c>
-      <c r="G51" s="33"/>
+      <c r="G51" s="25"/>
     </row>
     <row r="52" spans="1:7" ht="15.75">
       <c r="A52" s="7" t="s">
@@ -2816,7 +2828,7 @@
       <c r="E52">
         <v>1.23</v>
       </c>
-      <c r="G52" s="33"/>
+      <c r="G52" s="25"/>
     </row>
     <row r="53" spans="1:7" ht="15.75">
       <c r="A53" s="7" t="s">
@@ -2834,7 +2846,7 @@
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="G53" s="33"/>
+      <c r="G53" s="25"/>
     </row>
     <row r="54" spans="1:7" ht="15.75">
       <c r="A54" s="7" t="s">
@@ -2852,7 +2864,7 @@
       <c r="E54">
         <v>6.91</v>
       </c>
-      <c r="G54" s="33"/>
+      <c r="G54" s="25"/>
     </row>
     <row r="55" spans="1:7" ht="15.75">
       <c r="A55" s="7" t="s">
@@ -2868,7 +2880,7 @@
       <c r="E55">
         <v>11.68</v>
       </c>
-      <c r="G55" s="33"/>
+      <c r="G55" s="25"/>
     </row>
     <row r="56" spans="1:7" ht="15.75">
       <c r="A56" s="7" t="s">
@@ -2886,7 +2898,7 @@
       <c r="E56">
         <v>4.03</v>
       </c>
-      <c r="G56" s="33"/>
+      <c r="G56" s="25"/>
     </row>
     <row r="57" spans="1:7" ht="15.75">
       <c r="A57" s="7" t="s">
@@ -2902,7 +2914,7 @@
       <c r="E57">
         <v>16.79</v>
       </c>
-      <c r="G57" s="33"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" spans="1:7" ht="15.75">
       <c r="A58" s="7" t="s">
@@ -2920,7 +2932,7 @@
       <c r="E58">
         <v>8.57</v>
       </c>
-      <c r="G58" s="33"/>
+      <c r="G58" s="25"/>
     </row>
     <row r="59" spans="1:7" ht="15.75">
       <c r="A59" s="7" t="s">
@@ -2938,7 +2950,7 @@
       <c r="E59">
         <v>0.86</v>
       </c>
-      <c r="G59" s="33"/>
+      <c r="G59" s="25"/>
     </row>
     <row r="60" spans="1:7" ht="15.75">
       <c r="A60" s="7" t="s">
@@ -2956,7 +2968,7 @@
       <c r="E60">
         <v>13.44</v>
       </c>
-      <c r="G60" s="33"/>
+      <c r="G60" s="25"/>
     </row>
     <row r="61" spans="1:7" ht="15.75">
       <c r="A61" s="7" t="s">
@@ -2972,7 +2984,7 @@
       <c r="E61">
         <v>19.559999999999999</v>
       </c>
-      <c r="G61" s="33"/>
+      <c r="G61" s="25"/>
     </row>
     <row r="62" spans="1:7" ht="15.75">
       <c r="A62" s="8" t="s">
@@ -2990,7 +3002,7 @@
       <c r="E62">
         <v>3.77</v>
       </c>
-      <c r="G62" s="33"/>
+      <c r="G62" s="25"/>
     </row>
     <row r="63" spans="1:7" ht="15.75">
       <c r="A63" s="8" t="s">
@@ -3008,7 +3020,7 @@
       <c r="E63">
         <v>10.23</v>
       </c>
-      <c r="G63" s="33"/>
+      <c r="G63" s="25"/>
     </row>
     <row r="64" spans="1:7" ht="15.75">
       <c r="A64" s="8" t="s">
@@ -3024,7 +3036,7 @@
       <c r="E64">
         <v>17.010000000000002</v>
       </c>
-      <c r="G64" s="33"/>
+      <c r="G64" s="25"/>
     </row>
     <row r="65" spans="1:7" ht="15.75">
       <c r="A65" s="8" t="s">
@@ -3042,7 +3054,7 @@
       <c r="E65">
         <v>2.65</v>
       </c>
-      <c r="G65" s="33"/>
+      <c r="G65" s="25"/>
     </row>
     <row r="66" spans="1:7" ht="15.75">
       <c r="A66" s="8" t="s">
@@ -3060,7 +3072,7 @@
       <c r="E66">
         <v>14.89</v>
       </c>
-      <c r="G66" s="33"/>
+      <c r="G66" s="25"/>
     </row>
     <row r="67" spans="1:7" ht="15.75">
       <c r="A67" s="8" t="s">
@@ -3078,7 +3090,7 @@
       <c r="E67">
         <v>5.97</v>
       </c>
-      <c r="G67" s="33"/>
+      <c r="G67" s="25"/>
     </row>
     <row r="68" spans="1:7" ht="15.75">
       <c r="A68" s="8" t="s">
@@ -3094,7 +3106,7 @@
       <c r="E68">
         <v>12.5</v>
       </c>
-      <c r="G68" s="33"/>
+      <c r="G68" s="25"/>
     </row>
     <row r="69" spans="1:7" ht="15.75">
       <c r="A69" s="8" t="s">
@@ -3112,7 +3124,7 @@
       <c r="E69">
         <v>0.94</v>
       </c>
-      <c r="G69" s="33"/>
+      <c r="G69" s="25"/>
     </row>
     <row r="70" spans="1:7" ht="15.75">
       <c r="A70" s="8" t="s">
@@ -3130,7 +3142,7 @@
       <c r="E70">
         <v>18.18</v>
       </c>
-      <c r="G70" s="33"/>
+      <c r="G70" s="25"/>
     </row>
     <row r="71" spans="1:7" ht="15.75">
       <c r="A71" s="8" t="s">
@@ -3146,7 +3158,7 @@
       <c r="E71">
         <v>7.36</v>
       </c>
-      <c r="G71" s="33"/>
+      <c r="G71" s="25"/>
     </row>
     <row r="72" spans="1:7" ht="15.75">
       <c r="A72" s="8" t="s">
@@ -3164,7 +3176,7 @@
       <c r="E72">
         <v>15.22</v>
       </c>
-      <c r="G72" s="33"/>
+      <c r="G72" s="25"/>
     </row>
     <row r="73" spans="1:7" ht="15.75">
       <c r="A73" s="8" t="s">
@@ -3182,7 +3194,7 @@
       <c r="E73">
         <v>4.72</v>
       </c>
-      <c r="G73" s="33"/>
+      <c r="G73" s="25"/>
     </row>
     <row r="74" spans="1:7" ht="15.75">
       <c r="A74" s="8" t="s">
@@ -3200,7 +3212,7 @@
       <c r="E74">
         <v>9.08</v>
       </c>
-      <c r="G74" s="33"/>
+      <c r="G74" s="25"/>
     </row>
     <row r="75" spans="1:7" ht="15.75">
       <c r="A75" s="8" t="s">
@@ -3218,7 +3230,7 @@
       <c r="E75">
         <v>19.75</v>
       </c>
-      <c r="G75" s="33"/>
+      <c r="G75" s="25"/>
     </row>
     <row r="76" spans="1:7" ht="15.75">
       <c r="A76" s="8" t="s">
@@ -3236,7 +3248,7 @@
       <c r="E76">
         <v>1.87</v>
       </c>
-      <c r="G76" s="33"/>
+      <c r="G76" s="25"/>
     </row>
     <row r="77" spans="1:7" ht="15.75">
       <c r="A77" s="9" t="s">
@@ -3254,7 +3266,7 @@
       <c r="E77">
         <v>11.32</v>
       </c>
-      <c r="G77" s="33"/>
+      <c r="G77" s="25"/>
     </row>
     <row r="78" spans="1:7" ht="15.75">
       <c r="A78" s="9" t="s">
@@ -3270,7 +3282,7 @@
       <c r="E78">
         <v>20</v>
       </c>
-      <c r="G78" s="33"/>
+      <c r="G78" s="25"/>
     </row>
     <row r="79" spans="1:7" ht="15.75">
       <c r="A79" s="9" t="s">
@@ -3288,7 +3300,7 @@
       <c r="E79">
         <v>3.49</v>
       </c>
-      <c r="G79" s="33"/>
+      <c r="G79" s="25"/>
     </row>
     <row r="80" spans="1:7" ht="15.75">
       <c r="A80" s="9" t="s">
@@ -3306,7 +3318,7 @@
       <c r="E80">
         <v>16.03</v>
       </c>
-      <c r="G80" s="33"/>
+      <c r="G80" s="25"/>
     </row>
     <row r="81" spans="1:7" ht="15.75">
       <c r="A81" s="9" t="s">
@@ -3324,7 +3336,7 @@
       <c r="E81">
         <v>6.28</v>
       </c>
-      <c r="G81" s="33"/>
+      <c r="G81" s="25"/>
     </row>
     <row r="82" spans="1:7" ht="15.75">
       <c r="A82" s="9" t="s">
@@ -3342,7 +3354,7 @@
       <c r="E82">
         <v>13.91</v>
       </c>
-      <c r="G82" s="33"/>
+      <c r="G82" s="25"/>
     </row>
     <row r="83" spans="1:7" ht="15.75">
       <c r="A83" s="9" t="s">
@@ -3360,7 +3372,7 @@
       <c r="E83">
         <v>8.7899999999999991</v>
       </c>
-      <c r="G83" s="33"/>
+      <c r="G83" s="25"/>
     </row>
     <row r="84" spans="1:7" ht="15.75">
       <c r="A84" s="9" t="s">
@@ -3378,7 +3390,7 @@
       <c r="E84">
         <v>0.68</v>
       </c>
-      <c r="G84" s="33"/>
+      <c r="G84" s="25"/>
     </row>
     <row r="85" spans="1:7" ht="15.75">
       <c r="A85" s="9" t="s">
@@ -3396,7 +3408,7 @@
       <c r="E85">
         <v>17.579999999999998</v>
       </c>
-      <c r="G85" s="33"/>
+      <c r="G85" s="25"/>
     </row>
     <row r="86" spans="1:7" ht="15.75">
       <c r="A86" s="9" t="s">
@@ -3414,7 +3426,7 @@
       <c r="E86">
         <v>2.14</v>
       </c>
-      <c r="G86" s="33"/>
+      <c r="G86" s="25"/>
     </row>
     <row r="87" spans="1:7" ht="15.75">
       <c r="A87" s="9" t="s">
@@ -3432,7 +3444,7 @@
       <c r="E87">
         <v>10.41</v>
       </c>
-      <c r="G87" s="33"/>
+      <c r="G87" s="25"/>
     </row>
     <row r="88" spans="1:7" ht="15.75">
       <c r="A88" s="9" t="s">
@@ -3448,7 +3460,7 @@
       <c r="E88">
         <v>14.77</v>
       </c>
-      <c r="G88" s="33"/>
+      <c r="G88" s="25"/>
     </row>
     <row r="89" spans="1:7" ht="15.75">
       <c r="A89" s="9" t="s">
@@ -3464,7 +3476,7 @@
       <c r="E89">
         <v>5.03</v>
       </c>
-      <c r="G89" s="33"/>
+      <c r="G89" s="25"/>
     </row>
     <row r="90" spans="1:7" ht="15.75">
       <c r="A90" s="9" t="s">
@@ -3480,7 +3492,7 @@
       <c r="E90">
         <v>18.420000000000002</v>
       </c>
-      <c r="G90" s="33"/>
+      <c r="G90" s="25"/>
     </row>
     <row r="91" spans="1:7" ht="15.75">
       <c r="A91" s="9" t="s">
@@ -3498,7 +3510,7 @@
       <c r="E91">
         <v>7.69</v>
       </c>
-      <c r="G91" s="33"/>
+      <c r="G91" s="25"/>
     </row>
     <row r="92" spans="1:7" ht="15.75">
       <c r="A92" s="10" t="s">
@@ -3516,7 +3528,7 @@
       <c r="E92">
         <v>1.34</v>
       </c>
-      <c r="G92" s="33"/>
+      <c r="G92" s="25"/>
     </row>
     <row r="93" spans="1:7" ht="15.75">
       <c r="A93" s="10" t="s">
@@ -3534,7 +3546,7 @@
       <c r="E93">
         <v>12.15</v>
       </c>
-      <c r="G93" s="33"/>
+      <c r="G93" s="25"/>
     </row>
     <row r="94" spans="1:7" ht="15.75">
       <c r="A94" s="10" t="s">
@@ -3552,7 +3564,7 @@
       <c r="E94">
         <v>4.59</v>
       </c>
-      <c r="G94" s="33"/>
+      <c r="G94" s="25"/>
     </row>
     <row r="95" spans="1:7" ht="15.75">
       <c r="A95" s="10" t="s">
@@ -3570,7 +3582,7 @@
       <c r="E95">
         <v>9.91</v>
       </c>
-      <c r="G95" s="33"/>
+      <c r="G95" s="25"/>
     </row>
     <row r="96" spans="1:7" ht="15.75">
       <c r="A96" s="10" t="s">
@@ -3586,7 +3598,7 @@
       <c r="E96">
         <v>20</v>
       </c>
-      <c r="G96" s="33"/>
+      <c r="G96" s="25"/>
     </row>
     <row r="97" spans="1:7" ht="15.75">
       <c r="A97" s="10" t="s">
@@ -3602,7 +3614,7 @@
       <c r="E97">
         <v>15.44</v>
       </c>
-      <c r="G97" s="33"/>
+      <c r="G97" s="25"/>
     </row>
     <row r="98" spans="1:7" ht="15.75">
       <c r="A98" s="10" t="s">
@@ -3620,7 +3632,7 @@
       <c r="E98">
         <v>3.02</v>
       </c>
-      <c r="G98" s="33"/>
+      <c r="G98" s="25"/>
     </row>
     <row r="99" spans="1:7" ht="15.75">
       <c r="A99" s="10" t="s">
@@ -3636,7 +3648,7 @@
       <c r="E99">
         <v>11.86</v>
       </c>
-      <c r="G99" s="33"/>
+      <c r="G99" s="25"/>
     </row>
     <row r="100" spans="1:7" ht="15.75">
       <c r="A100" s="10" t="s">
@@ -3652,7 +3664,7 @@
       <c r="E100">
         <v>6.57</v>
       </c>
-      <c r="G100" s="33"/>
+      <c r="G100" s="25"/>
     </row>
     <row r="101" spans="1:7" ht="15.75">
       <c r="A101" s="10" t="s">
@@ -3670,7 +3682,7 @@
       <c r="E101">
         <v>0.77</v>
       </c>
-      <c r="G101" s="33"/>
+      <c r="G101" s="25"/>
     </row>
     <row r="102" spans="1:7" ht="15.75">
       <c r="A102" s="10" t="s">
@@ -3686,7 +3698,7 @@
       <c r="E102">
         <v>17.34</v>
       </c>
-      <c r="G102" s="33"/>
+      <c r="G102" s="25"/>
     </row>
     <row r="103" spans="1:7" ht="15.75">
       <c r="A103" s="10" t="s">
@@ -3704,7 +3716,7 @@
       <c r="E103">
         <v>8.2100000000000009</v>
       </c>
-      <c r="G103" s="33"/>
+      <c r="G103" s="25"/>
     </row>
     <row r="104" spans="1:7" ht="15.75">
       <c r="A104" s="10" t="s">
@@ -3722,7 +3734,7 @@
       <c r="E104">
         <v>13.66</v>
       </c>
-      <c r="G104" s="33"/>
+      <c r="G104" s="25"/>
     </row>
     <row r="105" spans="1:7" ht="15.75">
       <c r="A105" s="10" t="s">
@@ -3738,7 +3750,7 @@
       <c r="E105">
         <v>2.4300000000000002</v>
       </c>
-      <c r="G105" s="33"/>
+      <c r="G105" s="25"/>
     </row>
     <row r="106" spans="1:7" ht="15.75">
       <c r="A106" s="10" t="s">
@@ -3754,7 +3766,7 @@
       <c r="E106">
         <v>19.23</v>
       </c>
-      <c r="G106" s="33"/>
+      <c r="G106" s="25"/>
     </row>
     <row r="107" spans="1:7" ht="15.75">
       <c r="A107" s="11" t="s">
@@ -3770,7 +3782,7 @@
       <c r="E107">
         <v>4.18</v>
       </c>
-      <c r="G107" s="33"/>
+      <c r="G107" s="25"/>
     </row>
     <row r="108" spans="1:7" ht="15.75">
       <c r="A108" s="11" t="s">
@@ -3786,7 +3798,7 @@
       <c r="E108">
         <v>10.72</v>
       </c>
-      <c r="G108" s="33"/>
+      <c r="G108" s="25"/>
     </row>
     <row r="109" spans="1:7" ht="15.75">
       <c r="A109" s="11" t="s">
@@ -3804,7 +3816,7 @@
       <c r="E109">
         <v>16.97</v>
       </c>
-      <c r="G109" s="33"/>
+      <c r="G109" s="25"/>
     </row>
     <row r="110" spans="1:7" ht="15.75">
       <c r="A110" s="11" t="s">
@@ -3820,7 +3832,7 @@
       <c r="E110">
         <v>1.1100000000000001</v>
       </c>
-      <c r="G110" s="33"/>
+      <c r="G110" s="25"/>
     </row>
     <row r="111" spans="1:7" ht="15.75">
       <c r="A111" s="11" t="s">
@@ -3838,7 +3850,7 @@
       <c r="E111">
         <v>7.85</v>
       </c>
-      <c r="G111" s="33"/>
+      <c r="G111" s="25"/>
     </row>
     <row r="112" spans="1:7" ht="15.75">
       <c r="A112" s="11" t="s">
@@ -3856,7 +3868,7 @@
       <c r="E112">
         <v>14.08</v>
       </c>
-      <c r="G112" s="33"/>
+      <c r="G112" s="25"/>
     </row>
     <row r="113" spans="1:7" ht="15.75">
       <c r="A113" s="11" t="s">
@@ -3874,7 +3886,7 @@
       <c r="E113">
         <v>20</v>
       </c>
-      <c r="G113" s="33"/>
+      <c r="G113" s="25"/>
     </row>
     <row r="114" spans="1:7" ht="15.75">
       <c r="A114" s="11" t="s">
@@ -3892,7 +3904,7 @@
       <c r="E114">
         <v>5.46</v>
       </c>
-      <c r="G114" s="33"/>
+      <c r="G114" s="25"/>
     </row>
     <row r="115" spans="1:7" ht="15.75">
       <c r="A115" s="11" t="s">
@@ -3910,7 +3922,7 @@
       <c r="E115">
         <v>12.81</v>
       </c>
-      <c r="G115" s="33"/>
+      <c r="G115" s="25"/>
     </row>
     <row r="116" spans="1:7" ht="15.75">
       <c r="A116" s="11" t="s">
@@ -3928,7 +3940,7 @@
       <c r="E116">
         <v>3.63</v>
       </c>
-      <c r="G116" s="33"/>
+      <c r="G116" s="25"/>
     </row>
     <row r="117" spans="1:7" ht="15.75">
       <c r="A117" s="11" t="s">
@@ -3944,7 +3956,7 @@
       <c r="E117">
         <v>9.2899999999999991</v>
       </c>
-      <c r="G117" s="33"/>
+      <c r="G117" s="25"/>
     </row>
     <row r="118" spans="1:7" ht="15.75">
       <c r="A118" s="11" t="s">
@@ -3962,7 +3974,7 @@
       <c r="E118">
         <v>18.71</v>
       </c>
-      <c r="G118" s="33"/>
+      <c r="G118" s="25"/>
     </row>
     <row r="119" spans="1:7" ht="15.75">
       <c r="A119" s="11" t="s">
@@ -3980,7 +3992,7 @@
       <c r="E119">
         <v>0.63</v>
       </c>
-      <c r="G119" s="33"/>
+      <c r="G119" s="25"/>
     </row>
     <row r="120" spans="1:7" ht="15.75">
       <c r="A120" s="11" t="s">
@@ -3998,7 +4010,7 @@
       <c r="E120">
         <v>15.6</v>
       </c>
-      <c r="G120" s="33"/>
+      <c r="G120" s="25"/>
     </row>
     <row r="121" spans="1:7" ht="15.75">
       <c r="A121" s="11" t="s">
@@ -4016,7 +4028,7 @@
       <c r="E121">
         <v>2.98</v>
       </c>
-      <c r="G121" s="33"/>
+      <c r="G121" s="25"/>
     </row>
     <row r="122" spans="1:7" ht="15.75">
       <c r="A122" s="12" t="s">
@@ -4034,7 +4046,7 @@
       <c r="E122">
         <v>8.8800000000000008</v>
       </c>
-      <c r="G122" s="33"/>
+      <c r="G122" s="25"/>
     </row>
     <row r="123" spans="1:7" ht="15.75">
       <c r="A123" s="12" t="s">
@@ -4050,7 +4062,7 @@
       <c r="E123">
         <v>1.76</v>
       </c>
-      <c r="G123" s="33"/>
+      <c r="G123" s="25"/>
     </row>
     <row r="124" spans="1:7" ht="15.75">
       <c r="A124" s="12" t="s">
@@ -4066,7 +4078,7 @@
       <c r="E124">
         <v>19.04</v>
       </c>
-      <c r="G124" s="33"/>
+      <c r="G124" s="25"/>
     </row>
     <row r="125" spans="1:7" ht="15.75">
       <c r="A125" s="12" t="s">
@@ -4082,7 +4094,7 @@
       <c r="E125">
         <v>4.37</v>
       </c>
-      <c r="G125" s="33"/>
+      <c r="G125" s="25"/>
     </row>
     <row r="126" spans="1:7" ht="15.75">
       <c r="A126" s="12" t="s">
@@ -4098,7 +4110,7 @@
       <c r="E126">
         <v>11.19</v>
       </c>
-      <c r="G126" s="33"/>
+      <c r="G126" s="25"/>
     </row>
     <row r="127" spans="1:7" ht="15.75">
       <c r="A127" s="12" t="s">
@@ -4116,7 +4128,7 @@
       <c r="E127">
         <v>17.22</v>
       </c>
-      <c r="G127" s="33"/>
+      <c r="G127" s="25"/>
     </row>
     <row r="128" spans="1:7" ht="15.75">
       <c r="A128" s="12" t="s">
@@ -4134,7 +4146,7 @@
       <c r="E128">
         <v>6.82</v>
       </c>
-      <c r="G128" s="33"/>
+      <c r="G128" s="25"/>
     </row>
     <row r="129" spans="1:7" ht="15.75">
       <c r="A129" s="12" t="s">
@@ -4150,7 +4162,7 @@
       <c r="E129">
         <v>13.33</v>
       </c>
-      <c r="G129" s="33"/>
+      <c r="G129" s="25"/>
     </row>
     <row r="130" spans="1:7" ht="15.75">
       <c r="A130" s="12" t="s">
@@ -4166,7 +4178,7 @@
       <c r="E130">
         <v>20</v>
       </c>
-      <c r="G130" s="33"/>
+      <c r="G130" s="25"/>
     </row>
     <row r="131" spans="1:7" ht="15.75">
       <c r="A131" s="12" t="s">
@@ -4182,7 +4194,7 @@
       <c r="E131">
         <v>0.59</v>
       </c>
-      <c r="G131" s="33"/>
+      <c r="G131" s="25"/>
     </row>
     <row r="132" spans="1:7" ht="15.75">
       <c r="A132" s="12" t="s">
@@ -4198,7 +4210,7 @@
       <c r="E132">
         <v>14.45</v>
       </c>
-      <c r="G132" s="33"/>
+      <c r="G132" s="25"/>
     </row>
     <row r="133" spans="1:7" ht="15.75">
       <c r="A133" s="12" t="s">
@@ -4216,7 +4228,7 @@
       <c r="E133">
         <v>3.91</v>
       </c>
-      <c r="G133" s="33"/>
+      <c r="G133" s="25"/>
     </row>
     <row r="134" spans="1:7" ht="15.75">
       <c r="A134" s="12" t="s">
@@ -4234,7 +4246,7 @@
       <c r="E134">
         <v>9.74</v>
       </c>
-      <c r="G134" s="33"/>
+      <c r="G134" s="25"/>
     </row>
     <row r="135" spans="1:7" ht="15.75">
       <c r="A135" s="12" t="s">
@@ -4250,7 +4262,7 @@
       <c r="E135">
         <v>16.36</v>
       </c>
-      <c r="G135" s="33"/>
+      <c r="G135" s="25"/>
     </row>
     <row r="136" spans="1:7" ht="15.75">
       <c r="A136" s="12" t="s">
@@ -4268,7 +4280,7 @@
       <c r="E136">
         <v>7.48</v>
       </c>
-      <c r="G136" s="33"/>
+      <c r="G136" s="25"/>
     </row>
     <row r="137" spans="1:7" ht="15.75">
       <c r="A137" s="13" t="s">
@@ -4286,7 +4298,7 @@
       <c r="E137">
         <v>2.2599999999999998</v>
       </c>
-      <c r="G137" s="33"/>
+      <c r="G137" s="25"/>
     </row>
     <row r="138" spans="1:7" ht="15.75">
       <c r="A138" s="13" t="s">
@@ -4304,7 +4316,7 @@
       <c r="E138">
         <v>13.33</v>
       </c>
-      <c r="G138" s="33"/>
+      <c r="G138" s="25"/>
     </row>
     <row r="139" spans="1:7" ht="15.75">
       <c r="A139" s="13" t="s">
@@ -4322,7 +4334,7 @@
       <c r="E139">
         <v>20</v>
       </c>
-      <c r="G139" s="33"/>
+      <c r="G139" s="25"/>
     </row>
     <row r="140" spans="1:7" ht="15.75">
       <c r="A140" s="13" t="s">
@@ -4338,7 +4350,7 @@
       <c r="E140">
         <v>0.59</v>
       </c>
-      <c r="G140" s="33"/>
+      <c r="G140" s="25"/>
     </row>
     <row r="141" spans="1:7" ht="15.75">
       <c r="A141" s="13" t="s">
@@ -4356,7 +4368,7 @@
       <c r="E141">
         <v>14.45</v>
       </c>
-      <c r="G141" s="33"/>
+      <c r="G141" s="25"/>
     </row>
     <row r="142" spans="1:7" ht="15.75">
       <c r="A142" s="13" t="s">
@@ -4372,7 +4384,7 @@
       <c r="E142">
         <v>3.91</v>
       </c>
-      <c r="G142" s="33"/>
+      <c r="G142" s="25"/>
     </row>
     <row r="143" spans="1:7" ht="15.75">
       <c r="A143" s="13" t="s">
@@ -4390,7 +4402,7 @@
       <c r="E143">
         <v>9.74</v>
       </c>
-      <c r="G143" s="33"/>
+      <c r="G143" s="25"/>
     </row>
     <row r="144" spans="1:7" ht="15.75">
       <c r="A144" s="13" t="s">
@@ -4406,7 +4418,7 @@
       <c r="E144">
         <v>16.36</v>
       </c>
-      <c r="G144" s="33"/>
+      <c r="G144" s="25"/>
     </row>
     <row r="145" spans="1:7" ht="15.75">
       <c r="A145" s="13" t="s">
@@ -4424,7 +4436,7 @@
       <c r="E145">
         <v>7.48</v>
       </c>
-      <c r="G145" s="33"/>
+      <c r="G145" s="25"/>
     </row>
     <row r="146" spans="1:7" ht="15.75">
       <c r="A146" s="13" t="s">
@@ -4440,7 +4452,7 @@
       <c r="E146">
         <v>2.2599999999999998</v>
       </c>
-      <c r="G146" s="33"/>
+      <c r="G146" s="25"/>
     </row>
     <row r="147" spans="1:7" ht="15.75">
       <c r="A147" s="13" t="s">
@@ -4458,7 +4470,7 @@
       <c r="E147">
         <v>12.93</v>
       </c>
-      <c r="G147" s="33"/>
+      <c r="G147" s="25"/>
     </row>
     <row r="148" spans="1:7" ht="15.75">
       <c r="A148" s="13" t="s">
@@ -4476,7 +4488,7 @@
       <c r="E148">
         <v>18.03</v>
       </c>
-      <c r="G148" s="33"/>
+      <c r="G148" s="25"/>
     </row>
     <row r="149" spans="1:7" ht="15.75">
       <c r="A149" s="13" t="s">
@@ -4492,7 +4504,7 @@
       <c r="E149">
         <v>5.18</v>
       </c>
-      <c r="G149" s="33"/>
+      <c r="G149" s="25"/>
     </row>
     <row r="150" spans="1:7" ht="15.75">
       <c r="A150" s="13" t="s">
@@ -4508,7 +4520,7 @@
       <c r="E150">
         <v>9.2899999999999991</v>
       </c>
-      <c r="G150" s="33"/>
+      <c r="G150" s="25"/>
     </row>
     <row r="151" spans="1:7" ht="15.75">
       <c r="A151" s="13" t="s">
@@ -4526,534 +4538,534 @@
       <c r="E151">
         <v>18.71</v>
       </c>
-      <c r="G151" s="33"/>
+      <c r="G151" s="25"/>
     </row>
     <row r="152" spans="1:7" ht="15.75">
-      <c r="A152" s="16" t="s">
+      <c r="A152" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B152" s="16" t="s">
+      <c r="B152" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C152" s="16" t="s">
+      <c r="C152" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D152" s="16" t="s">
+      <c r="D152" s="15" t="s">
         <v>39</v>
       </c>
       <c r="E152">
         <v>2.2599999999999998</v>
       </c>
-      <c r="G152" s="33"/>
+      <c r="G152" s="25"/>
     </row>
     <row r="153" spans="1:7" ht="15.75">
-      <c r="A153" s="16" t="s">
+      <c r="A153" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="B153" s="16" t="s">
+      <c r="B153" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C153" s="16" t="s">
+      <c r="C153" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D153" s="16" t="s">
+      <c r="D153" s="15" t="s">
         <v>26</v>
       </c>
       <c r="E153">
         <v>13.33</v>
       </c>
-      <c r="G153" s="33"/>
+      <c r="G153" s="25"/>
     </row>
     <row r="154" spans="1:7" ht="15.75">
-      <c r="A154" s="16" t="s">
+      <c r="A154" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B154" s="16" t="s">
+      <c r="B154" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C154" s="16" t="s">
+      <c r="C154" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D154" s="16"/>
+      <c r="D154" s="15"/>
       <c r="E154">
         <v>20</v>
       </c>
-      <c r="G154" s="33"/>
+      <c r="G154" s="25"/>
     </row>
     <row r="155" spans="1:7" ht="15.75">
-      <c r="A155" s="16" t="s">
+      <c r="A155" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B155" s="16" t="s">
+      <c r="B155" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C155" s="16" t="s">
+      <c r="C155" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D155" s="16" t="s">
+      <c r="D155" s="15" t="s">
         <v>15</v>
       </c>
       <c r="E155">
         <v>0.59</v>
       </c>
-      <c r="G155" s="33"/>
+      <c r="G155" s="25"/>
     </row>
     <row r="156" spans="1:7" ht="15.75">
-      <c r="A156" s="16" t="s">
+      <c r="A156" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B156" s="16" t="s">
+      <c r="B156" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C156" s="16" t="s">
+      <c r="C156" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D156" s="16" t="s">
+      <c r="D156" s="15" t="s">
         <v>26</v>
       </c>
       <c r="E156">
         <v>14.45</v>
       </c>
-      <c r="G156" s="33"/>
+      <c r="G156" s="25"/>
     </row>
     <row r="157" spans="1:7" ht="15.75">
-      <c r="A157" s="16" t="s">
+      <c r="A157" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B157" s="16" t="s">
+      <c r="B157" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C157" s="16" t="s">
+      <c r="C157" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D157" s="16"/>
+      <c r="D157" s="15"/>
       <c r="E157">
         <v>3.91</v>
       </c>
-      <c r="G157" s="33"/>
+      <c r="G157" s="25"/>
     </row>
     <row r="158" spans="1:7" ht="15.75">
-      <c r="A158" s="16" t="s">
+      <c r="A158" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B158" s="16" t="s">
+      <c r="B158" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C158" s="16" t="s">
+      <c r="C158" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D158" s="16" t="s">
+      <c r="D158" s="15" t="s">
         <v>39</v>
       </c>
       <c r="E158">
         <v>9.74</v>
       </c>
-      <c r="G158" s="33"/>
+      <c r="G158" s="25"/>
     </row>
     <row r="159" spans="1:7" ht="15.75">
-      <c r="A159" s="16" t="s">
+      <c r="A159" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B159" s="16" t="s">
+      <c r="B159" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C159" s="16" t="s">
+      <c r="C159" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D159" s="16"/>
+      <c r="D159" s="15"/>
       <c r="E159">
         <v>16.36</v>
       </c>
-      <c r="G159" s="33"/>
+      <c r="G159" s="25"/>
     </row>
     <row r="160" spans="1:7" ht="15.75">
-      <c r="A160" s="16" t="s">
+      <c r="A160" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B160" s="16" t="s">
+      <c r="B160" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C160" s="16" t="s">
+      <c r="C160" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D160" s="16" t="s">
+      <c r="D160" s="15" t="s">
         <v>39</v>
       </c>
       <c r="E160">
         <v>7.48</v>
       </c>
-      <c r="G160" s="33"/>
+      <c r="G160" s="25"/>
     </row>
     <row r="161" spans="1:7" ht="15.75">
-      <c r="A161" s="16" t="s">
+      <c r="A161" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="B161" s="16" t="s">
+      <c r="B161" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C161" s="16" t="s">
+      <c r="C161" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D161" s="16" t="s">
+      <c r="D161" s="15" t="s">
         <v>18</v>
       </c>
       <c r="E161">
         <v>2.2599999999999998</v>
       </c>
-      <c r="G161" s="33"/>
+      <c r="G161" s="25"/>
     </row>
     <row r="162" spans="1:7" ht="15.75">
-      <c r="A162" s="16" t="s">
+      <c r="A162" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B162" s="16" t="s">
+      <c r="B162" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C162" s="16" t="s">
+      <c r="C162" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D162" s="16" t="s">
+      <c r="D162" s="15" t="s">
         <v>39</v>
       </c>
       <c r="E162">
         <v>12.93</v>
       </c>
-      <c r="G162" s="33"/>
+      <c r="G162" s="25"/>
     </row>
     <row r="163" spans="1:7" ht="15.75">
-      <c r="A163" s="16" t="s">
+      <c r="A163" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B163" s="16" t="s">
+      <c r="B163" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C163" s="16" t="s">
+      <c r="C163" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D163" s="16"/>
+      <c r="D163" s="15"/>
       <c r="E163">
         <v>18.03</v>
       </c>
-      <c r="G163" s="33"/>
+      <c r="G163" s="25"/>
     </row>
     <row r="164" spans="1:7" ht="15.75">
-      <c r="A164" s="16" t="s">
+      <c r="A164" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B164" s="16" t="s">
+      <c r="B164" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C164" s="16" t="s">
+      <c r="C164" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D164" s="16" t="s">
+      <c r="D164" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E164">
         <v>5.18</v>
       </c>
-      <c r="G164" s="33"/>
+      <c r="G164" s="25"/>
     </row>
     <row r="165" spans="1:7" ht="15.75">
-      <c r="A165" s="16" t="s">
+      <c r="A165" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="B165" s="16" t="s">
+      <c r="B165" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C165" s="16" t="s">
+      <c r="C165" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D165" s="16"/>
+      <c r="D165" s="15"/>
       <c r="E165">
         <v>9.2899999999999991</v>
       </c>
-      <c r="G165" s="33"/>
+      <c r="G165" s="25"/>
     </row>
     <row r="166" spans="1:7" ht="15.75">
-      <c r="A166" s="16" t="s">
+      <c r="A166" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B166" s="16" t="s">
+      <c r="B166" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C166" s="16" t="s">
+      <c r="C166" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D166" s="16" t="s">
+      <c r="D166" s="15" t="s">
         <v>28</v>
       </c>
       <c r="E166">
         <v>18.71</v>
       </c>
-      <c r="G166" s="33"/>
+      <c r="G166" s="25"/>
     </row>
     <row r="167" spans="1:7" ht="15.75">
-      <c r="A167" s="15" t="s">
+      <c r="A167" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B167" s="15" t="s">
+      <c r="B167" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C167" s="15" t="s">
+      <c r="C167" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D167" s="15" t="s">
+      <c r="D167" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E167">
         <v>2.2599999999999998</v>
       </c>
-      <c r="G167" s="33"/>
+      <c r="G167" s="25"/>
     </row>
     <row r="168" spans="1:7" ht="15.75">
-      <c r="A168" s="15" t="s">
+      <c r="A168" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="B168" s="15" t="s">
+      <c r="B168" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C168" s="15" t="s">
+      <c r="C168" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D168" s="15" t="s">
+      <c r="D168" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E168">
         <v>13.33</v>
       </c>
-      <c r="G168" s="33"/>
+      <c r="G168" s="25"/>
     </row>
     <row r="169" spans="1:7" ht="15.75">
-      <c r="A169" s="15" t="s">
+      <c r="A169" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B169" s="15" t="s">
+      <c r="B169" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C169" s="15" t="s">
+      <c r="C169" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D169" s="15" t="s">
+      <c r="D169" s="14" t="s">
         <v>18</v>
       </c>
       <c r="E169">
         <v>20</v>
       </c>
-      <c r="G169" s="33"/>
+      <c r="G169" s="25"/>
     </row>
     <row r="170" spans="1:7" ht="15.75">
-      <c r="A170" s="15" t="s">
+      <c r="A170" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B170" s="15" t="s">
+      <c r="B170" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C170" s="15" t="s">
+      <c r="C170" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D170" s="15" t="s">
+      <c r="D170" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E170">
         <v>0.59</v>
       </c>
-      <c r="G170" s="33"/>
+      <c r="G170" s="25"/>
     </row>
     <row r="171" spans="1:7" ht="15.75">
-      <c r="A171" s="15" t="s">
+      <c r="A171" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B171" s="15" t="s">
+      <c r="B171" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C171" s="15" t="s">
+      <c r="C171" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D171" s="15"/>
+      <c r="D171" s="14"/>
       <c r="E171">
         <v>14.45</v>
       </c>
-      <c r="G171" s="33"/>
+      <c r="G171" s="25"/>
     </row>
     <row r="172" spans="1:7" ht="15.75">
-      <c r="A172" s="15" t="s">
+      <c r="A172" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B172" s="15" t="s">
+      <c r="B172" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C172" s="15" t="s">
+      <c r="C172" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D172" s="15" t="s">
+      <c r="D172" s="14" t="s">
         <v>26</v>
       </c>
       <c r="E172">
         <v>3.91</v>
       </c>
-      <c r="G172" s="33"/>
+      <c r="G172" s="25"/>
     </row>
     <row r="173" spans="1:7" ht="15.75">
-      <c r="A173" s="15" t="s">
+      <c r="A173" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="B173" s="15" t="s">
+      <c r="B173" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C173" s="15" t="s">
+      <c r="C173" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D173" s="15" t="s">
+      <c r="D173" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E173">
         <v>9.74</v>
       </c>
-      <c r="G173" s="33"/>
+      <c r="G173" s="25"/>
     </row>
     <row r="174" spans="1:7" ht="15.75">
-      <c r="A174" s="15" t="s">
+      <c r="A174" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B174" s="15" t="s">
+      <c r="B174" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C174" s="15" t="s">
+      <c r="C174" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D174" s="15" t="s">
+      <c r="D174" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E174">
         <v>16.36</v>
       </c>
-      <c r="G174" s="33"/>
+      <c r="G174" s="25"/>
     </row>
     <row r="175" spans="1:7" ht="15.75">
-      <c r="A175" s="15" t="s">
+      <c r="A175" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="B175" s="15" t="s">
+      <c r="B175" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C175" s="15" t="s">
+      <c r="C175" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D175" s="15" t="s">
+      <c r="D175" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E175">
         <v>7.48</v>
       </c>
-      <c r="G175" s="33"/>
+      <c r="G175" s="25"/>
     </row>
     <row r="176" spans="1:7" ht="15.75">
-      <c r="A176" s="15" t="s">
+      <c r="A176" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="B176" s="15" t="s">
+      <c r="B176" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C176" s="15" t="s">
+      <c r="C176" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D176" s="15" t="s">
+      <c r="D176" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E176">
         <v>2.2599999999999998</v>
       </c>
-      <c r="G176" s="33"/>
+      <c r="G176" s="25"/>
     </row>
     <row r="177" spans="1:7" ht="15.75">
-      <c r="A177" s="15" t="s">
+      <c r="A177" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="B177" s="15" t="s">
+      <c r="B177" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C177" s="15" t="s">
+      <c r="C177" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D177" s="15" t="s">
+      <c r="D177" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E177">
         <v>12.93</v>
       </c>
-      <c r="G177" s="33"/>
+      <c r="G177" s="25"/>
     </row>
     <row r="178" spans="1:7" ht="15.75">
-      <c r="A178" s="15" t="s">
+      <c r="A178" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="B178" s="15" t="s">
+      <c r="B178" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C178" s="15" t="s">
+      <c r="C178" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D178" s="15" t="s">
+      <c r="D178" s="14" t="s">
         <v>39</v>
       </c>
       <c r="E178">
         <v>18.03</v>
       </c>
-      <c r="G178" s="33"/>
+      <c r="G178" s="25"/>
     </row>
     <row r="179" spans="1:7" ht="15.75">
-      <c r="A179" s="15" t="s">
+      <c r="A179" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="B179" s="15" t="s">
+      <c r="B179" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C179" s="15" t="s">
+      <c r="C179" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D179" s="15"/>
+      <c r="D179" s="14"/>
       <c r="E179">
         <v>5.18</v>
       </c>
-      <c r="G179" s="33"/>
+      <c r="G179" s="25"/>
     </row>
     <row r="180" spans="1:7" ht="15.75">
-      <c r="A180" s="15" t="s">
+      <c r="A180" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="B180" s="15" t="s">
+      <c r="B180" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C180" s="15" t="s">
+      <c r="C180" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D180" s="15"/>
+      <c r="D180" s="14"/>
       <c r="E180">
         <v>9.2899999999999991</v>
       </c>
-      <c r="G180" s="33"/>
+      <c r="G180" s="25"/>
     </row>
     <row r="181" spans="1:7" ht="15.75">
-      <c r="A181" s="15" t="s">
+      <c r="A181" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="B181" s="15" t="s">
+      <c r="B181" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C181" s="15" t="s">
+      <c r="C181" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D181" s="15" t="s">
+      <c r="D181" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E181">
         <v>18.71</v>
       </c>
-      <c r="G181" s="33"/>
+      <c r="G181" s="25"/>
     </row>
     <row r="182" spans="1:7" ht="15.75">
-      <c r="G182" s="32"/>
+      <c r="G182" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5077,7 +5089,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57C2BC9-9BEE-8147-9540-8AC7A6007D3E}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="2" max="2" width="15.625" bestFit="1" customWidth="1"/>
@@ -5095,32 +5107,32 @@
       <c r="A2" t="s">
         <v>210</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75">
       <c r="A3" t="s">
         <v>211</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
       <c r="A4" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75">
       <c r="A5" t="s">
         <v>213</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75">
@@ -5128,7 +5140,7 @@
         <v>214</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75">
@@ -5136,7 +5148,7 @@
         <v>215</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75">
@@ -5155,6 +5167,7 @@
     </row>
     <row r="11" spans="1:2" ht="15.75"/>
     <row r="12" spans="1:2" ht="15.75"/>
+    <row r="13" spans="1:2" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -5164,6 +5177,1580 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BECB35E5-687B-7F42-80A5-82F5DDEFA085}">
+  <sheetPr>
+    <tabColor rgb="FF008080"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75">
+      <c r="A1" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75">
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="26" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>West Indies</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Scotland</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75">
+      <c r="A9" s="3">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="26" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>South Africa</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Pakistan</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Scotland</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Netherlands</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Pakistan</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3">
+        <v>12</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Pakistan</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>India</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Netherlands</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75">
+      <c r="A21" s="3">
+        <v>16</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Bangladesh</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75">
+      <c r="A22" s="3">
+        <v>17</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75">
+      <c r="A23" s="3">
+        <v>18</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="26" t="str">
+        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>South Africa</v>
+      </c>
+      <c r="D23" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{F8FBDCC3-3111-DC4E-AF01-A0FD07E86895}">
+      <formula1>"Captain,Vice-Captain,None"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D030090-5C0F-BA4C-AA19-0E80536C4120}">
+          <x14:formula1>
+            <xm:f>Players!$A$2:$A$181</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6:B23</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DA2B3A-B487-394F-BDF2-46BC59A5DA4A}">
+  <sheetPr>
+    <tabColor rgb="FF301934"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75">
+      <c r="A1" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75">
+      <c r="A5" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>West Indies</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>West Indies</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75">
+      <c r="A9" s="3">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75">
+      <c r="A10" s="3">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Bangladesh</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Netherlands</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75">
+      <c r="A12" s="3">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>India</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Sri Lanka</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="26" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>West Indies</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>India</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75">
+      <c r="A17" s="3">
+        <v>12</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>New Zealand</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75">
+      <c r="A18" s="3">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75">
+      <c r="A19" s="3">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75">
+      <c r="A20" s="3">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C20" s="26" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>West Indies</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75">
+      <c r="A21" s="3">
+        <v>16</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="26" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>West Indies</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75">
+      <c r="A22" s="3">
+        <v>17</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>India</v>
+      </c>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75">
+      <c r="A23" s="3">
+        <v>18</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D23" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{537B20EA-C0AC-494B-BFDC-05B417DE60F6}">
+      <formula1>"Captain,Vice-Captain,None"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0E3C63E-EA25-5849-AC4A-F1A294A10FF6}">
+          <x14:formula1>
+            <xm:f>Players!$A$2:$A$181</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6:B23</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BD65943-13E5-9242-9220-52600D83C211}">
+  <sheetPr>
+    <tabColor rgb="FF800000"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75">
+      <c r="A1" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75">
+      <c r="A5" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="26" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>South Africa</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="26" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>West Indies</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75">
+      <c r="A9" s="3">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>India</v>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75">
+      <c r="A10" s="3">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>New Zealand</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75">
+      <c r="A12" s="3">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Pakistan</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Netherlands</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Netherlands</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75">
+      <c r="A17" s="3">
+        <v>12</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Bangladesh</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75">
+      <c r="A18" s="3">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="26" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Sri Lanka</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75">
+      <c r="A19" s="3">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Scotland</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75">
+      <c r="A20" s="3">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>New Zealand</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75">
+      <c r="A21" s="3">
+        <v>16</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Pakistan</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75">
+      <c r="A22" s="3">
+        <v>17</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Bangladesh</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75">
+      <c r="A23" s="3">
+        <v>18</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Bangladesh</v>
+      </c>
+      <c r="D23" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{F2CD0A4C-1D79-984B-95EA-91B04E387101}">
+      <formula1>"Captain,Vice-Captain,None"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{820AB018-EF87-7145-BE50-60BE0E869C31}">
+          <x14:formula1>
+            <xm:f>Players!$A$2:$A$181</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6:B23</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C1428CB-1528-634C-8C93-958DA6744960}">
+  <sheetPr>
+    <tabColor rgb="FFE759AC"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75">
+      <c r="A1" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>New Zealand</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Pakistan</v>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="26" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Sri Lanka</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C12" s="26" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>West Indies</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" s="26" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Sri Lanka</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Pakistan</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Netherlands</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3">
+        <v>12</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>South Africa</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Bangladesh</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Scotland</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75">
+      <c r="A21" s="3">
+        <v>16</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Pakistan</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75">
+      <c r="A22" s="3">
+        <v>17</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Pakistan</v>
+      </c>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75">
+      <c r="A23" s="3">
+        <v>18</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D23" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{4DA19308-650D-4849-A026-734DD25B26E1}">
+      <formula1>"Captain,Vice-Captain,None"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DB2A4319-3327-BA40-AFC7-86FBCD333A45}">
+          <x14:formula1>
+            <xm:f>Players!$A$2:$A$181</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6:B23</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11537018-E961-894E-9ED9-37ABF3951144}">
+  <sheetPr>
+    <tabColor rgb="FF0B0C10"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75">
+      <c r="A1" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75">
+      <c r="A5" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="26" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>West Indies</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Scotland</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>India</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Australia</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>New Zealand</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3">
+        <v>12</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>India</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>India</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="26" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>South Africa</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75">
+      <c r="A21" s="3">
+        <v>16</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="26" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Sri Lanka</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75">
+      <c r="A22" s="3">
+        <v>17</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Bangladesh</v>
+      </c>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75">
+      <c r="A23" s="3">
+        <v>18</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
+        <v>Netherlands</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{49F8774F-0262-B747-A0D4-0DFFCD394070}">
+      <formula1>"Captain,Vice-Captain,None"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{51EC2756-B05B-6E45-BD79-B03B65274D71}">
+          <x14:formula1>
+            <xm:f>Players!$A$2:$A$181</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6:B23</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94BE4582-B8F0-8041-9C55-BE8D3E61A737}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -5177,37 +6764,37 @@
     <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="14" t="s">
+    <row r="1" spans="1:4" ht="15.75">
+      <c r="A1" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75">
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75">
+      <c r="A5" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="33" t="s">
         <v>219</v>
       </c>
     </row>
@@ -5223,7 +6810,7 @@
         <v>India</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75">
@@ -5285,7 +6872,7 @@
       <c r="B11" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="34" t="str">
+      <c r="C11" s="26" t="str">
         <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
         <v>West Indies</v>
       </c>
@@ -5381,7 +6968,7 @@
         <v>India</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75">
@@ -5430,7 +7017,7 @@
       <c r="B22" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C22" s="34" t="str">
+      <c r="C22" s="26" t="str">
         <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
         <v>Sri Lanka</v>
       </c>
@@ -5443,7 +7030,7 @@
       <c r="B23" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C23" s="34" t="str">
+      <c r="C23" s="26" t="str">
         <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
         <v>West Indies</v>
       </c>
@@ -5477,1580 +7064,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BECB35E5-687B-7F42-80A5-82F5DDEFA085}">
-  <sheetPr>
-    <tabColor rgb="FF008080"/>
-  </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
-  <cols>
-    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C6" s="34" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75">
-      <c r="A9" s="3">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" s="34" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3">
-        <v>8</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3">
-        <v>10</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="3">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="3">
-        <v>12</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="3">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="3">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="3">
-        <v>15</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="3">
-        <v>16</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
-      <c r="A22" s="3">
-        <v>17</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
-      <c r="A23" s="3">
-        <v>18</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C23" s="34" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
-      <c r="D23" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{F8FBDCC3-3111-DC4E-AF01-A0FD07E86895}">
-      <formula1>"Captain,Vice-Captain,None"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D030090-5C0F-BA4C-AA19-0E80536C4120}">
-          <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
-          </x14:formula1>
-          <xm:sqref>B6:B23</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DA2B3A-B487-394F-BDF2-46BC59A5DA4A}">
-  <sheetPr>
-    <tabColor rgb="FF301934"/>
-  </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
-  <cols>
-    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75">
-      <c r="A5" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75">
-      <c r="A6" s="3">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75">
-      <c r="A7" s="3">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75">
-      <c r="A8" s="3">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75">
-      <c r="A9" s="3">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75">
-      <c r="A10" s="3">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.75">
-      <c r="A11" s="3">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75">
-      <c r="A12" s="3">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75">
-      <c r="A13" s="3">
-        <v>8</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75">
-      <c r="A14" s="3">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75">
-      <c r="A15" s="3">
-        <v>10</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C15" s="34" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75">
-      <c r="A16" s="3">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="3">
-        <v>12</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="3">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.75">
-      <c r="A19" s="3">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.75">
-      <c r="A20" s="3">
-        <v>15</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C20" s="34" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="3">
-        <v>16</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C21" s="34" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
-      <c r="A22" s="3">
-        <v>17</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
-      <c r="A23" s="3">
-        <v>18</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D23" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{537B20EA-C0AC-494B-BFDC-05B417DE60F6}">
-      <formula1>"Captain,Vice-Captain,None"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0E3C63E-EA25-5849-AC4A-F1A294A10FF6}">
-          <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
-          </x14:formula1>
-          <xm:sqref>B6:B23</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BD65943-13E5-9242-9220-52600D83C211}">
-  <sheetPr>
-    <tabColor rgb="FF800000"/>
-  </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
-  <cols>
-    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75">
-      <c r="A5" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75">
-      <c r="A6" s="3">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="34" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75">
-      <c r="A7" s="3">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C7" s="34" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75">
-      <c r="A8" s="3">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75">
-      <c r="A9" s="3">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75">
-      <c r="A10" s="3">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.75">
-      <c r="A11" s="3">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75">
-      <c r="A12" s="3">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75">
-      <c r="A13" s="3">
-        <v>8</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75">
-      <c r="A14" s="3">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75">
-      <c r="A15" s="3">
-        <v>10</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75">
-      <c r="A16" s="3">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="3">
-        <v>12</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="3">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" s="34" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.75">
-      <c r="A19" s="3">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.75">
-      <c r="A20" s="3">
-        <v>15</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="3">
-        <v>16</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
-      <c r="A22" s="3">
-        <v>17</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
-      <c r="A23" s="3">
-        <v>18</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D23" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{F2CD0A4C-1D79-984B-95EA-91B04E387101}">
-      <formula1>"Captain,Vice-Captain,None"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{820AB018-EF87-7145-BE50-60BE0E869C31}">
-          <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
-          </x14:formula1>
-          <xm:sqref>B6:B23</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C1428CB-1528-634C-8C93-958DA6744960}">
-  <sheetPr>
-    <tabColor rgb="FFE759AC"/>
-  </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
-  <cols>
-    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="34" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C12" s="34" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3">
-        <v>8</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C13" s="34" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3">
-        <v>10</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="3">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="3">
-        <v>12</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="3">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="3">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="3">
-        <v>15</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="3">
-        <v>16</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
-      <c r="A22" s="3">
-        <v>17</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
-      <c r="A23" s="3">
-        <v>18</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D23" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{4DA19308-650D-4849-A026-734DD25B26E1}">
-      <formula1>"Captain,Vice-Captain,None"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DB2A4319-3327-BA40-AFC7-86FBCD333A45}">
-          <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
-          </x14:formula1>
-          <xm:sqref>B6:B23</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11537018-E961-894E-9ED9-37ABF3951144}">
-  <sheetPr>
-    <tabColor rgb="FF0B0C10"/>
-  </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
-  <cols>
-    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75">
-      <c r="A5" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="34" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3">
-        <v>7</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3">
-        <v>8</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3">
-        <v>10</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="3">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="3">
-        <v>12</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="3">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="3">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="3">
-        <v>15</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C20" s="34" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="3">
-        <v>16</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="34" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
-      <c r="A22" s="3">
-        <v>17</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
-      <c r="A23" s="3">
-        <v>18</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{49F8774F-0262-B747-A0D4-0DFFCD394070}">
-      <formula1>"Captain,Vice-Captain,None"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{51EC2756-B05B-6E45-BD79-B03B65274D71}">
-          <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
-          </x14:formula1>
-          <xm:sqref>B6:B23</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F75295-3507-D241-BEB6-6189BD4BB574}">
   <sheetPr>
@@ -7066,36 +7079,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="19" t="s">
         <v>219</v>
       </c>
     </row>
@@ -7111,7 +7124,7 @@
         <v>Ireland</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75">
@@ -7243,7 +7256,7 @@
         <v>England</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
@@ -7253,7 +7266,7 @@
       <c r="B17" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C17" s="34" t="str">
+      <c r="C17" s="26" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
         <v>Sri Lanka</v>
       </c>
@@ -7271,7 +7284,7 @@
         <v>Netherlands</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -7307,7 +7320,7 @@
       <c r="B21" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="34" t="str">
+      <c r="C21" s="26" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
         <v>Sri Lanka</v>
       </c>
@@ -7320,7 +7333,7 @@
       <c r="B22" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C22" s="34" t="str">
+      <c r="C22" s="26" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
         <v>West Indies</v>
       </c>

--- a/dwl-fantasy-platform/backend/WWC_Config.xlsx
+++ b/dwl-fantasy-platform/backend/WWC_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kishan/Downloads/Delulu Leagues/DWL Delulu Women's League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC40D813-FAD6-49CE-8E95-F1785420A2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC14FA28-C2E2-46AA-9604-08A82F751395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="1" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="8" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="226">
   <si>
     <t>Player Name</t>
   </si>
@@ -73,630 +73,630 @@
     <t>Annabel Sutherland</t>
   </si>
   <si>
+    <t>Ashleigh Gardner</t>
+  </si>
+  <si>
+    <t>Beth Mooney</t>
+  </si>
+  <si>
+    <t>wicketkeeper</t>
+  </si>
+  <si>
+    <t>Ellyse Perry</t>
+  </si>
+  <si>
+    <t>Georgia Voll</t>
+  </si>
+  <si>
+    <t>batter</t>
+  </si>
+  <si>
+    <t>Georgia Wareham</t>
+  </si>
+  <si>
+    <t>bowler</t>
+  </si>
+  <si>
+    <t>Grace Harris</t>
+  </si>
+  <si>
+    <t>Kim Garth</t>
+  </si>
+  <si>
+    <t>Lucy Hamilton</t>
+  </si>
+  <si>
+    <t>Megan Schutt</t>
+  </si>
+  <si>
+    <t>Nicola Carey</t>
+  </si>
+  <si>
+    <t>Phoebe Litchfield</t>
+  </si>
+  <si>
+    <t>Sophie Molineux</t>
+  </si>
+  <si>
+    <t>Tahlia McGrath</t>
+  </si>
+  <si>
+    <t>Dilara Akter</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>Fahima Khatun</t>
+  </si>
+  <si>
+    <t>Fariha Trisna</t>
+  </si>
+  <si>
+    <t>Juairiya Ferdous</t>
+  </si>
+  <si>
+    <t>Marufa Akter</t>
+  </si>
+  <si>
+    <t>Nahida Akter</t>
+  </si>
+  <si>
+    <t>Nigar Sultana</t>
+  </si>
+  <si>
+    <t>Rabeya Khan</t>
+  </si>
+  <si>
+    <t>Ritu Moni</t>
+  </si>
+  <si>
+    <t>Sharmin Akhter</t>
+  </si>
+  <si>
+    <t>Shorna Akter</t>
+  </si>
+  <si>
+    <t>Sobhana Mostary</t>
+  </si>
+  <si>
+    <t>Sultana Khatun</t>
+  </si>
+  <si>
+    <t>Sumaiya Akther</t>
+  </si>
+  <si>
+    <t>Taj Nehar</t>
+  </si>
+  <si>
+    <t>Alice Capsey</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Amy Jones</t>
+  </si>
+  <si>
+    <t>Charlie Dean</t>
+  </si>
+  <si>
+    <t>Dani Gibson</t>
+  </si>
+  <si>
+    <t>Danni Wyatt-Hodge</t>
+  </si>
+  <si>
+    <t>Freya Kemp</t>
+  </si>
+  <si>
+    <t>Heather Knight</t>
+  </si>
+  <si>
+    <t>Issy Wong</t>
+  </si>
+  <si>
+    <t>Lauren Bell</t>
+  </si>
+  <si>
+    <t>Lauren Filer</t>
+  </si>
+  <si>
+    <t>Linsey Smith</t>
+  </si>
+  <si>
+    <t>Nat Sciver-Brunt</t>
+  </si>
+  <si>
+    <t>Sophia Dunkley</t>
+  </si>
+  <si>
+    <t>Sophie Ecclestone</t>
+  </si>
+  <si>
+    <t>Tilly Corteen-Coleman</t>
+  </si>
+  <si>
+    <t>Arundhati Reddy</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharti Fulmali</t>
+  </si>
+  <si>
+    <t>Deepti Sharma</t>
+  </si>
+  <si>
+    <t>Harmanpreet Kaur</t>
+  </si>
+  <si>
+    <t>Jemimah Rodrigues</t>
+  </si>
+  <si>
+    <t>Kranti Gaud</t>
+  </si>
+  <si>
+    <t>Nandani Sharma</t>
+  </si>
+  <si>
+    <t>Radha Yadav</t>
+  </si>
+  <si>
+    <t>Renuka Singh</t>
+  </si>
+  <si>
+    <t>Richa Ghosh</t>
+  </si>
+  <si>
+    <t>Shafali Verma</t>
+  </si>
+  <si>
+    <t>Shree Charani</t>
+  </si>
+  <si>
+    <t>Shreyanka Patil</t>
+  </si>
+  <si>
+    <t>Smriti Mandhana</t>
+  </si>
+  <si>
+    <t>Yastika Bhatia</t>
+  </si>
+  <si>
+    <t>Aimee Maguire</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Alana Dalzell</t>
+  </si>
+  <si>
+    <t>Amy Hunter</t>
+  </si>
+  <si>
+    <t>Arlene Kelly</t>
+  </si>
+  <si>
+    <t>Ava Canning</t>
+  </si>
+  <si>
+    <t>Cara Murray</t>
+  </si>
+  <si>
+    <t>Christina Coulter Reilly</t>
+  </si>
+  <si>
+    <t>Gaby Lewis</t>
+  </si>
+  <si>
+    <t>Georgina Dempsey</t>
+  </si>
+  <si>
+    <t>Lara McBride</t>
+  </si>
+  <si>
+    <t>Laura Delany</t>
+  </si>
+  <si>
+    <t>Leah Paul</t>
+  </si>
+  <si>
+    <t>Louise Little</t>
+  </si>
+  <si>
+    <t>Orla Prendergast</t>
+  </si>
+  <si>
+    <t>Rebecca Stokell</t>
+  </si>
+  <si>
+    <t>Babette de Leede</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Caroline de Lange</t>
+  </si>
+  <si>
+    <t>Frederique Overdijk</t>
+  </si>
+  <si>
+    <t>Hannah Landheer</t>
+  </si>
+  <si>
+    <t>Heather Siegers</t>
+  </si>
+  <si>
+    <t>Iris Zwilling</t>
+  </si>
+  <si>
+    <t>Isabel van der Woning</t>
+  </si>
+  <si>
+    <t>Lara Leemhuis</t>
+  </si>
+  <si>
+    <t>Myrthe van den Raad</t>
+  </si>
+  <si>
+    <t>Phebe Molkenboer</t>
+  </si>
+  <si>
+    <t>Robine Rijke</t>
+  </si>
+  <si>
+    <t>Rosalie Ann Lawrence</t>
+  </si>
+  <si>
+    <t>Sanya Khurana</t>
+  </si>
+  <si>
+    <t>Silver Siegers</t>
+  </si>
+  <si>
+    <t>Sterre Kalis</t>
+  </si>
+  <si>
+    <t>Bree Illing</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>Brooke Halliday</t>
+  </si>
+  <si>
+    <t>Flora Devonshire</t>
+  </si>
+  <si>
+    <t>Georgia Plimmer</t>
+  </si>
+  <si>
+    <t>Isabella Gaze</t>
+  </si>
+  <si>
+    <t>Izzy Sharp</t>
+  </si>
+  <si>
+    <t>Jess Kerr</t>
+  </si>
+  <si>
+    <t>Lea Tahuhu</t>
+  </si>
+  <si>
+    <t>Maddy Green</t>
+  </si>
+  <si>
+    <t>Melie Kerr</t>
+  </si>
+  <si>
+    <t>Nensi Patel</t>
+  </si>
+  <si>
+    <t>Polly Inglis</t>
+  </si>
+  <si>
+    <t>Rosemary Mair</t>
+  </si>
+  <si>
+    <t>Sophie Devine</t>
+  </si>
+  <si>
+    <t>Suzie Bates</t>
+  </si>
+  <si>
+    <t>Aliya Riaz</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>Ayesha Zafar</t>
+  </si>
+  <si>
+    <t>Diana Baig</t>
+  </si>
+  <si>
+    <t>Eyman Fatima</t>
+  </si>
+  <si>
+    <t>Fatima Sana</t>
+  </si>
+  <si>
+    <t>Gull Feroza</t>
+  </si>
+  <si>
+    <t>Iram Javed</t>
+  </si>
+  <si>
+    <t>Muneeba Ali</t>
+  </si>
+  <si>
+    <t>Nashra Sandhu</t>
+  </si>
+  <si>
+    <t>Natalia Pervaiz</t>
+  </si>
+  <si>
+    <t>Rameen Shamim</t>
+  </si>
+  <si>
+    <t>Sadia Iqbal</t>
+  </si>
+  <si>
+    <t>Saira Jabeen</t>
+  </si>
+  <si>
+    <t>Tasmia Rubab</t>
+  </si>
+  <si>
+    <t>Tuba Hassan</t>
+  </si>
+  <si>
+    <t>Abtaha Maqsood</t>
+  </si>
+  <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>Ailsa Lister</t>
+  </si>
+  <si>
+    <t>Chloe Abel</t>
+  </si>
+  <si>
+    <t>Darcey Carter</t>
+  </si>
+  <si>
+    <t>Gabriella Fontenla</t>
+  </si>
+  <si>
+    <t>Katherine Fraser</t>
+  </si>
+  <si>
+    <t>Kathryn Bryce</t>
+  </si>
+  <si>
+    <t>Kirstie Gordon</t>
+  </si>
+  <si>
+    <t>Maisie Maceira</t>
+  </si>
+  <si>
+    <t>Megan McColl</t>
+  </si>
+  <si>
+    <t>Olivia Bell</t>
+  </si>
+  <si>
+    <t>Pippa Sproul</t>
+  </si>
+  <si>
+    <t>Priyanaz Chatterji</t>
+  </si>
+  <si>
+    <t>Rachel Slater</t>
+  </si>
+  <si>
+    <t>Sarah Bryce</t>
+  </si>
+  <si>
+    <t>Annerie Dercksen</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>Ayabonga Khaka</t>
+  </si>
+  <si>
+    <t>Chloe Tryon</t>
+  </si>
+  <si>
+    <t>Dane van Niekerk</t>
+  </si>
+  <si>
+    <t>Karabo Meso</t>
+  </si>
+  <si>
+    <t>Kayla Reyneke</t>
+  </si>
+  <si>
+    <t>Laura Wolvaardt</t>
+  </si>
+  <si>
+    <t>Marizanne Kapp</t>
+  </si>
+  <si>
+    <t>Nadine de Klerk</t>
+  </si>
+  <si>
+    <t>Nonkululeko Mlaba</t>
+  </si>
+  <si>
+    <t>Shabnim Ismail</t>
+  </si>
+  <si>
+    <t>Sinalo Jafta</t>
+  </si>
+  <si>
+    <t>Sune Luus</t>
+  </si>
+  <si>
+    <t>Tazmin Brits</t>
+  </si>
+  <si>
+    <t>Tumi Sekhukhune</t>
+  </si>
+  <si>
+    <t>Chamari Athapaththu</t>
+  </si>
+  <si>
+    <t>Sri Lanka</t>
+  </si>
+  <si>
+    <t>Hansima Karunaratne</t>
+  </si>
+  <si>
+    <t>Harshitha Samarawickrama</t>
+  </si>
+  <si>
+    <t>Hasini Perera</t>
+  </si>
+  <si>
+    <t>Imesha Dulani</t>
+  </si>
+  <si>
+    <t>Kaushini Nuthyangana</t>
+  </si>
+  <si>
+    <t>Kavisha Dilhari</t>
+  </si>
+  <si>
+    <t>Kawya Kavindi</t>
+  </si>
+  <si>
+    <t>Malki Madara</t>
+  </si>
+  <si>
+    <t>Mithali Ayodhya</t>
+  </si>
+  <si>
+    <t>Nilakshika Silva</t>
+  </si>
+  <si>
+    <t>Nimasha Meepage</t>
+  </si>
+  <si>
+    <t>Shashini Gimhani</t>
+  </si>
+  <si>
+    <t>Sugandika Kumari</t>
+  </si>
+  <si>
+    <t>Vishmi Gunaratne</t>
+  </si>
+  <si>
+    <t>Aaliyah Alleyne</t>
+  </si>
+  <si>
+    <t>West Indies</t>
+  </si>
+  <si>
+    <t>Afy Fletcher</t>
+  </si>
+  <si>
+    <t>Ashmini Munisar</t>
+  </si>
+  <si>
+    <t>Chinelle Henry</t>
+  </si>
+  <si>
+    <t>Deandra Dottin</t>
+  </si>
+  <si>
+    <t>Hayley Matthews</t>
+  </si>
+  <si>
+    <t>Jahzara Claxton</t>
+  </si>
+  <si>
+    <t>Jannillea Glasgow</t>
+  </si>
+  <si>
+    <t>Karishma Ramharack</t>
+  </si>
+  <si>
+    <t>Mandy Mangru</t>
+  </si>
+  <si>
+    <t>Qiana Joseph</t>
+  </si>
+  <si>
+    <t>Shawnisha Hector</t>
+  </si>
+  <si>
+    <t>Shemaine Campbelle</t>
+  </si>
+  <si>
+    <t>Stafanie Taylor</t>
+  </si>
+  <si>
+    <t>Zaida James</t>
+  </si>
+  <si>
+    <t>Abbrv</t>
+  </si>
+  <si>
+    <t>Team Name</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
     <t>Gully Divas</t>
   </si>
   <si>
-    <t>Ashleigh Gardner</t>
-  </si>
-  <si>
-    <t>Beth Mooney</t>
-  </si>
-  <si>
-    <t>wicketkeeper</t>
+    <t>JR</t>
+  </si>
+  <si>
+    <t>Janaki Royals</t>
+  </si>
+  <si>
+    <t>KQ</t>
+  </si>
+  <si>
+    <t>Konkan Queens</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>Rajputana Ranis</t>
+  </si>
+  <si>
+    <t>SS</t>
   </si>
   <si>
     <t>Sarafa Strikers</t>
   </si>
   <si>
-    <t>Ellyse Perry</t>
-  </si>
-  <si>
-    <t>Janaki Royals</t>
-  </si>
-  <si>
-    <t>Georgia Voll</t>
-  </si>
-  <si>
-    <t>batter</t>
-  </si>
-  <si>
-    <t>Konkan Queens</t>
-  </si>
-  <si>
-    <t>Georgia Wareham</t>
-  </si>
-  <si>
-    <t>bowler</t>
-  </si>
-  <si>
-    <t>Grace Harris</t>
-  </si>
-  <si>
-    <t>Kim Garth</t>
-  </si>
-  <si>
-    <t>Lucy Hamilton</t>
-  </si>
-  <si>
-    <t>Megan Schutt</t>
-  </si>
-  <si>
-    <t>Nicola Carey</t>
-  </si>
-  <si>
-    <t>Rajputana Ranis</t>
-  </si>
-  <si>
-    <t>Phoebe Litchfield</t>
+    <t>SGS</t>
   </si>
   <si>
     <t>Singara Singapengal</t>
   </si>
   <si>
-    <t>Sophie Molineux</t>
-  </si>
-  <si>
-    <t>Tahlia McGrath</t>
-  </si>
-  <si>
-    <t>Dilara Akter</t>
-  </si>
-  <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
-    <t>Fahima Khatun</t>
-  </si>
-  <si>
-    <t>Fariha Trisna</t>
-  </si>
-  <si>
-    <t>Juairiya Ferdous</t>
-  </si>
-  <si>
-    <t>Marufa Akter</t>
-  </si>
-  <si>
-    <t>Nahida Akter</t>
-  </si>
-  <si>
-    <t>Nigar Sultana</t>
+    <t>VW</t>
   </si>
   <si>
     <t>Vanitha Warriors</t>
   </si>
   <si>
-    <t>Rabeya Khan</t>
-  </si>
-  <si>
-    <t>Ritu Moni</t>
-  </si>
-  <si>
-    <t>Sharmin Akhter</t>
-  </si>
-  <si>
-    <t>Shorna Akter</t>
-  </si>
-  <si>
-    <t>Sobhana Mostary</t>
-  </si>
-  <si>
-    <t>Sultana Khatun</t>
-  </si>
-  <si>
-    <t>Sumaiya Akther</t>
-  </si>
-  <si>
-    <t>Taj Nehar</t>
-  </si>
-  <si>
-    <t>Alice Capsey</t>
-  </si>
-  <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>Amy Jones</t>
-  </si>
-  <si>
-    <t>Charlie Dean</t>
-  </si>
-  <si>
-    <t>Dani Gibson</t>
-  </si>
-  <si>
-    <t>Danni Wyatt-Hodge</t>
-  </si>
-  <si>
-    <t>Freya Kemp</t>
-  </si>
-  <si>
-    <t>Heather Knight</t>
-  </si>
-  <si>
-    <t>Issy Wong</t>
-  </si>
-  <si>
-    <t>Lauren Bell</t>
-  </si>
-  <si>
-    <t>Lauren Filer</t>
-  </si>
-  <si>
-    <t>Linsey Smith</t>
-  </si>
-  <si>
-    <t>Nat Sciver-Brunt</t>
-  </si>
-  <si>
-    <t>Sophia Dunkley</t>
-  </si>
-  <si>
-    <t>Sophie Ecclestone</t>
-  </si>
-  <si>
-    <t>Tilly Corteen-Coleman</t>
-  </si>
-  <si>
-    <t>Arundhati Reddy</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharti Fulmali</t>
-  </si>
-  <si>
-    <t>Deepti Sharma</t>
-  </si>
-  <si>
-    <t>Harmanpreet Kaur</t>
-  </si>
-  <si>
-    <t>Jemimah Rodrigues</t>
-  </si>
-  <si>
-    <t>Kranti Gaud</t>
-  </si>
-  <si>
-    <t>Nandani Sharma</t>
-  </si>
-  <si>
-    <t>Radha Yadav</t>
-  </si>
-  <si>
-    <t>Renuka Singh</t>
-  </si>
-  <si>
-    <t>Richa Ghosh</t>
-  </si>
-  <si>
-    <t>Shafali Verma</t>
-  </si>
-  <si>
-    <t>Shree Charani</t>
-  </si>
-  <si>
-    <t>Shreyanka Patil</t>
-  </si>
-  <si>
-    <t>Smriti Mandhana</t>
-  </si>
-  <si>
-    <t>Yastika Bhatia</t>
-  </si>
-  <si>
-    <t>Aimee Maguire</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>Alana Dalzell</t>
-  </si>
-  <si>
-    <t>Amy Hunter</t>
-  </si>
-  <si>
-    <t>Arlene Kelly</t>
-  </si>
-  <si>
-    <t>Ava Canning</t>
-  </si>
-  <si>
-    <t>Cara Murray</t>
-  </si>
-  <si>
-    <t>Christina Coulter Reilly</t>
-  </si>
-  <si>
-    <t>Gaby Lewis</t>
-  </si>
-  <si>
-    <t>Georgina Dempsey</t>
-  </si>
-  <si>
-    <t>Lara McBride</t>
-  </si>
-  <si>
-    <t>Laura Delany</t>
-  </si>
-  <si>
-    <t>Leah Paul</t>
-  </si>
-  <si>
-    <t>Louise Little</t>
-  </si>
-  <si>
-    <t>Orla Prendergast</t>
-  </si>
-  <si>
-    <t>Rebecca Stokell</t>
-  </si>
-  <si>
-    <t>Babette de Leede</t>
-  </si>
-  <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
-    <t>Caroline de Lange</t>
-  </si>
-  <si>
-    <t>Frederique Overdijk</t>
-  </si>
-  <si>
-    <t>Hannah Landheer</t>
-  </si>
-  <si>
-    <t>Heather Siegers</t>
-  </si>
-  <si>
-    <t>Iris Zwilling</t>
-  </si>
-  <si>
-    <t>Isabel van der Woning</t>
-  </si>
-  <si>
-    <t>Lara Leemhuis</t>
-  </si>
-  <si>
-    <t>Myrthe van den Raad</t>
-  </si>
-  <si>
-    <t>Phebe Molkenboer</t>
-  </si>
-  <si>
-    <t>Robine Rijke</t>
-  </si>
-  <si>
-    <t>Rosalie Ann Lawrence</t>
-  </si>
-  <si>
-    <t>Sanya Khurana</t>
-  </si>
-  <si>
-    <t>Silver Siegers</t>
-  </si>
-  <si>
-    <t>Sterre Kalis</t>
-  </si>
-  <si>
-    <t>Bree Illing</t>
-  </si>
-  <si>
-    <t>New Zealand</t>
-  </si>
-  <si>
-    <t>Brooke Halliday</t>
-  </si>
-  <si>
-    <t>Flora Devonshire</t>
-  </si>
-  <si>
-    <t>Georgia Plimmer</t>
-  </si>
-  <si>
-    <t>Isabella Gaze</t>
-  </si>
-  <si>
-    <t>Izzy Sharp</t>
-  </si>
-  <si>
-    <t>Jess Kerr</t>
-  </si>
-  <si>
-    <t>Lea Tahuhu</t>
-  </si>
-  <si>
-    <t>Maddy Green</t>
-  </si>
-  <si>
-    <t>Melie Kerr</t>
-  </si>
-  <si>
-    <t>Nensi Patel</t>
-  </si>
-  <si>
-    <t>Polly Inglis</t>
-  </si>
-  <si>
-    <t>Rosemary Mair</t>
-  </si>
-  <si>
-    <t>Sophie Devine</t>
-  </si>
-  <si>
-    <t>Suzie Bates</t>
-  </si>
-  <si>
-    <t>Aliya Riaz</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>Ayesha Zafar</t>
-  </si>
-  <si>
-    <t>Diana Baig</t>
-  </si>
-  <si>
-    <t>Eyman Fatima</t>
-  </si>
-  <si>
-    <t>Fatima Sana</t>
-  </si>
-  <si>
-    <t>Gull Feroza</t>
-  </si>
-  <si>
-    <t>Iram Javed</t>
-  </si>
-  <si>
-    <t>Muneeba Ali</t>
-  </si>
-  <si>
-    <t>Nashra Sandhu</t>
-  </si>
-  <si>
-    <t>Natalia Pervaiz</t>
-  </si>
-  <si>
-    <t>Rameen Shamim</t>
-  </si>
-  <si>
-    <t>Sadia Iqbal</t>
-  </si>
-  <si>
-    <t>Saira Jabeen</t>
-  </si>
-  <si>
-    <t>Tasmia Rubab</t>
-  </si>
-  <si>
-    <t>Tuba Hassan</t>
-  </si>
-  <si>
-    <t>Abtaha Maqsood</t>
-  </si>
-  <si>
-    <t>Scotland</t>
-  </si>
-  <si>
-    <t>Ailsa Lister</t>
-  </si>
-  <si>
-    <t>Chloe Abel</t>
-  </si>
-  <si>
-    <t>Darcey Carter</t>
-  </si>
-  <si>
-    <t>Gabriella Fontenla</t>
-  </si>
-  <si>
-    <t>Katherine Fraser</t>
-  </si>
-  <si>
-    <t>Kathryn Bryce</t>
-  </si>
-  <si>
-    <t>Kirstie Gordon</t>
-  </si>
-  <si>
-    <t>Maisie Maceira</t>
-  </si>
-  <si>
-    <t>Megan McColl</t>
-  </si>
-  <si>
-    <t>Olivia Bell</t>
-  </si>
-  <si>
-    <t>Pippa Sproul</t>
-  </si>
-  <si>
-    <t>Priyanaz Chatterji</t>
-  </si>
-  <si>
-    <t>Rachel Slater</t>
-  </si>
-  <si>
-    <t>Sarah Bryce</t>
-  </si>
-  <si>
-    <t>Annerie Dercksen</t>
-  </si>
-  <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>Ayabonga Khaka</t>
-  </si>
-  <si>
-    <t>Chloe Tryon</t>
-  </si>
-  <si>
-    <t>Dane van Niekerk</t>
-  </si>
-  <si>
-    <t>Karabo Meso</t>
-  </si>
-  <si>
-    <t>Kayla Reyneke</t>
-  </si>
-  <si>
-    <t>Laura Wolvaardt</t>
-  </si>
-  <si>
-    <t>Marizanne Kapp</t>
-  </si>
-  <si>
-    <t>Nadine de Klerk</t>
-  </si>
-  <si>
-    <t>Nonkululeko Mlaba</t>
-  </si>
-  <si>
-    <t>Shabnim Ismail</t>
-  </si>
-  <si>
-    <t>Sinalo Jafta</t>
-  </si>
-  <si>
-    <t>Sune Luus</t>
-  </si>
-  <si>
-    <t>Tazmin Brits</t>
-  </si>
-  <si>
-    <t>Tumi Sekhukhune</t>
-  </si>
-  <si>
-    <t>Chamari Athapaththu</t>
-  </si>
-  <si>
-    <t>Sri Lanka</t>
-  </si>
-  <si>
-    <t>Hansima Karunaratne</t>
-  </si>
-  <si>
-    <t>Harshitha Samarawickrama</t>
-  </si>
-  <si>
-    <t>Hasini Perera</t>
-  </si>
-  <si>
-    <t>Imesha Dulani</t>
-  </si>
-  <si>
-    <t>Kaushini Nuthyangana</t>
-  </si>
-  <si>
-    <t>Kavisha Dilhari</t>
-  </si>
-  <si>
-    <t>Kawya Kavindi</t>
-  </si>
-  <si>
-    <t>Malki Madara</t>
-  </si>
-  <si>
-    <t>Mithali Ayodhya</t>
-  </si>
-  <si>
-    <t>Nilakshika Silva</t>
-  </si>
-  <si>
-    <t>Nimasha Meepage</t>
-  </si>
-  <si>
-    <t>Shashini Gimhani</t>
-  </si>
-  <si>
-    <t>Sugandika Kumari</t>
-  </si>
-  <si>
-    <t>Vishmi Gunaratne</t>
-  </si>
-  <si>
-    <t>Aaliyah Alleyne</t>
-  </si>
-  <si>
-    <t>West Indies</t>
-  </si>
-  <si>
-    <t>Afy Fletcher</t>
-  </si>
-  <si>
-    <t>Ashmini Munisar</t>
-  </si>
-  <si>
-    <t>Chinelle Henry</t>
-  </si>
-  <si>
-    <t>Deandra Dottin</t>
-  </si>
-  <si>
-    <t>Hayley Matthews</t>
-  </si>
-  <si>
-    <t>Jahzara Claxton</t>
-  </si>
-  <si>
-    <t>Jannillea Glasgow</t>
-  </si>
-  <si>
-    <t>Karishma Ramharack</t>
-  </si>
-  <si>
-    <t>Mandy Mangru</t>
-  </si>
-  <si>
-    <t>Qiana Joseph</t>
-  </si>
-  <si>
-    <t>Shawnisha Hector</t>
-  </si>
-  <si>
-    <t>Shemaine Campbelle</t>
-  </si>
-  <si>
-    <t>Stafanie Taylor</t>
-  </si>
-  <si>
-    <t>Zaida James</t>
-  </si>
-  <si>
-    <t>Abbrv</t>
-  </si>
-  <si>
-    <t>Team Name</t>
-  </si>
-  <si>
-    <t>GD</t>
-  </si>
-  <si>
-    <t>JR</t>
-  </si>
-  <si>
-    <t>KQ</t>
-  </si>
-  <si>
-    <t>RR</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>SGS</t>
-  </si>
-  <si>
-    <t>VW</t>
-  </si>
-  <si>
     <t>GULLY DIVAS</t>
   </si>
   <si>
@@ -706,16 +706,7 @@
     <t>Captain/ Vice-Captain</t>
   </si>
   <si>
-    <t>Vice-Captain</t>
-  </si>
-  <si>
-    <t>Captain</t>
-  </si>
-  <si>
     <t>JANAKI ROYALS</t>
-  </si>
-  <si>
-    <t>None</t>
   </si>
   <si>
     <t>KONKAN QUEENS</t>
@@ -1079,6 +1070,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1094,13 +1088,10 @@
     <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1475,9 +1466,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{08FE8A15-D3B6-DF4B-88B3-A051E62A20E6}" name="Team Player No." dataDxfId="39"/>
     <tableColumn id="2" xr3:uid="{4ECD4789-FFEE-F647-8611-EA766F1EEB38}" name="Player Name" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{E23434DC-5066-554A-A1F3-30A49F38C773}" name="Country" dataDxfId="37">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{E23434DC-5066-554A-A1F3-30A49F38C773}" name="Country" dataDxfId="37"/>
     <tableColumn id="4" xr3:uid="{B716E680-D978-7440-AE9C-6B18870AC674}" name="Captain/ Vice-Captain" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1493,9 +1482,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{9685E0E1-CFC1-4D4C-9DA8-9D0D67FFF359}" name="Team Player No." dataDxfId="33"/>
     <tableColumn id="2" xr3:uid="{4127652B-4321-704E-8135-B6E29F440927}" name="Player Name" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{7E01B81D-BAB5-574F-BBB7-719FC4E16DC4}" name="Country" dataDxfId="31">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{7E01B81D-BAB5-574F-BBB7-719FC4E16DC4}" name="Country" dataDxfId="31"/>
     <tableColumn id="4" xr3:uid="{0C3C6BB9-DD76-DD4A-97EF-189E0310831A}" name="Captain/ Vice-Captain" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1511,9 +1498,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{0D27ED80-3738-7F47-94AF-0A6B61961EB3}" name="Team Player No." dataDxfId="27"/>
     <tableColumn id="2" xr3:uid="{267FF8CD-F86C-DE4D-922E-8D12B710755E}" name="Player Name" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{20C938BF-DCD0-1941-ACC8-F620B1FDFF4A}" name="Country" dataDxfId="25">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{20C938BF-DCD0-1941-ACC8-F620B1FDFF4A}" name="Country" dataDxfId="25"/>
     <tableColumn id="4" xr3:uid="{BC210CBE-A244-1A47-9738-6D3C52D2F342}" name="Captain/ Vice-Captain" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1529,9 +1514,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{234B9EE4-D33E-1447-BB49-68C355C76983}" name="Team Player No." dataDxfId="21"/>
     <tableColumn id="2" xr3:uid="{F46522FB-98C6-BD44-8237-8D453678EEE8}" name="Player Name" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{420600D5-2F08-1849-A91C-2F03DFE81977}" name="Country" dataDxfId="19">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{420600D5-2F08-1849-A91C-2F03DFE81977}" name="Country" dataDxfId="19"/>
     <tableColumn id="4" xr3:uid="{F0D8CC44-F2B1-B443-B44A-5AE8610B9D3B}" name="Captain/ Vice-Captain" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1547,9 +1530,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{31A5AA7F-D358-494F-8889-0D3934B9DF61}" name="Team Player No." dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{196D6C69-3CAF-0A44-BF6D-64F1AC14B9D2}" name="Player Name" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{9DCA5DAF-0152-FA41-87A0-FBE7254C3CCC}" name="Country" dataDxfId="13">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{9DCA5DAF-0152-FA41-87A0-FBE7254C3CCC}" name="Country" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{E65D1282-79BC-3640-9D14-2CB9941E7D9C}" name="Captain/ Vice-Captain" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1565,9 +1546,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{74BA643C-B079-8B4F-8344-2C9B9BC12707}" name="Team Player No." dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{432B80D9-19D7-AF43-AB9E-82D1257517E4}" name="Player Name" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{AA077A69-6CDA-934A-8174-723FA3593002}" name="Country" dataDxfId="7">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{AA077A69-6CDA-934A-8174-723FA3593002}" name="Country" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{3A3DF73D-E88E-1644-A4F0-7B6F72118B2E}" name="Captain/ Vice-Captain" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1583,9 +1562,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{8DD4A9BF-D7CC-1249-82C8-0D9C5B5EC365}" name="Team Player No." dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{6C7C94F0-116B-6E4D-A181-898044122E61}" name="Player Name" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{0F8DB46C-16CD-4540-821F-2B7FB0541A01}" name="Country" dataDxfId="1">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{0F8DB46C-16CD-4540-821F-2B7FB0541A01}" name="Country" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{611FC6FE-DC81-EB47-AEEC-56717395E657}" name="Captain/ Vice-Captain" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1947,9 +1924,6 @@
         <v>7</v>
       </c>
       <c r="D2" s="4"/>
-      <c r="E2">
-        <v>0.98</v>
-      </c>
       <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:7" ht="15.75">
@@ -1962,17 +1936,12 @@
       <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>14.27</v>
-      </c>
+      <c r="D3" s="4"/>
       <c r="G3" s="25"/>
     </row>
     <row r="4" spans="1:7" ht="15.75">
       <c r="A4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>6</v>
@@ -1980,35 +1949,25 @@
       <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4">
-        <v>7.54</v>
-      </c>
+      <c r="D4" s="4"/>
       <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" ht="15.75">
       <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <v>19.12</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:7" ht="15.75">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>6</v>
@@ -2016,53 +1975,38 @@
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>3.86</v>
-      </c>
+      <c r="D6" s="4"/>
       <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" ht="15.75">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7">
-        <v>11.44</v>
-      </c>
+      <c r="D7" s="4"/>
       <c r="G7" s="25"/>
     </row>
     <row r="8" spans="1:7" ht="15.75">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>6.13</v>
-      </c>
+      <c r="D8" s="4"/>
       <c r="G8" s="25"/>
     </row>
     <row r="9" spans="1:7" ht="15.75">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>6</v>
@@ -2070,17 +2014,12 @@
       <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9">
-        <v>18.940000000000001</v>
-      </c>
+      <c r="D9" s="4"/>
       <c r="G9" s="25"/>
     </row>
     <row r="10" spans="1:7" ht="15.75">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>6</v>
@@ -2089,14 +2028,11 @@
         <v>7</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10">
-        <v>2.37</v>
-      </c>
       <c r="G10" s="25"/>
     </row>
     <row r="11" spans="1:7" ht="15.75">
       <c r="A11" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>6</v>
@@ -2104,71 +2040,51 @@
       <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11">
-        <v>9.65</v>
-      </c>
+      <c r="D11" s="4"/>
       <c r="G11" s="25"/>
     </row>
     <row r="12" spans="1:7" ht="15.75">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12">
-        <v>15.71</v>
-      </c>
+      <c r="D12" s="4"/>
       <c r="G12" s="25"/>
     </row>
     <row r="13" spans="1:7" ht="15.75">
       <c r="A13" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13">
-        <v>4.28</v>
-      </c>
+      <c r="D13" s="4"/>
       <c r="G13" s="25"/>
     </row>
     <row r="14" spans="1:7" ht="15.75">
       <c r="A14" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14">
-        <v>20</v>
-      </c>
+      <c r="D14" s="4"/>
       <c r="G14" s="25"/>
     </row>
     <row r="15" spans="1:7" ht="15.75">
       <c r="A15" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>6</v>
@@ -2177,14 +2093,11 @@
         <v>7</v>
       </c>
       <c r="D15" s="4"/>
-      <c r="E15">
-        <v>1.55</v>
-      </c>
       <c r="G15" s="25"/>
     </row>
     <row r="16" spans="1:7" ht="15.75">
       <c r="A16" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>6</v>
@@ -2192,2876 +2105,2148 @@
       <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16">
-        <v>13.09</v>
-      </c>
+      <c r="D16" s="4"/>
       <c r="G16" s="25"/>
     </row>
     <row r="17" spans="1:7" ht="15.75">
       <c r="A17" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17">
-        <v>8.42</v>
-      </c>
       <c r="G17" s="25"/>
     </row>
     <row r="18" spans="1:7" ht="15.75">
       <c r="A18" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18">
-        <v>17.829999999999998</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D18" s="5"/>
       <c r="G18" s="25"/>
     </row>
     <row r="19" spans="1:7" ht="15.75">
       <c r="A19" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19">
-        <v>5.61</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D19" s="5"/>
       <c r="G19" s="25"/>
     </row>
     <row r="20" spans="1:7" ht="15.75">
       <c r="A20" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20">
-        <v>10.97</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D20" s="5"/>
       <c r="G20" s="25"/>
     </row>
     <row r="21" spans="1:7" ht="15.75">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="E21">
-        <v>12.34</v>
-      </c>
       <c r="G21" s="25"/>
     </row>
     <row r="22" spans="1:7" ht="15.75">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E22">
-        <v>0.72</v>
-      </c>
+      <c r="D22" s="5"/>
       <c r="G22" s="25"/>
     </row>
     <row r="23" spans="1:7" ht="15.75">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23">
-        <v>16.48</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D23" s="5"/>
       <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D24" s="5"/>
-      <c r="E24">
-        <v>19.88</v>
-      </c>
       <c r="G24" s="25"/>
     </row>
     <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D25" s="5"/>
-      <c r="E25">
-        <v>3.15</v>
-      </c>
       <c r="G25" s="25"/>
     </row>
     <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D26" s="5"/>
-      <c r="E26">
-        <v>7.93</v>
-      </c>
       <c r="G26" s="25"/>
     </row>
     <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27">
-        <v>14.56</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D27" s="5"/>
       <c r="G27" s="25"/>
     </row>
     <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28">
-        <v>2.81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D28" s="5"/>
       <c r="G28" s="25"/>
     </row>
     <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29">
-        <v>9.19</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D29" s="5"/>
       <c r="G29" s="25"/>
     </row>
     <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30">
-        <v>18.27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D30" s="5"/>
       <c r="G30" s="25"/>
     </row>
     <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31">
-        <v>6.64</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D31" s="5"/>
       <c r="G31" s="25"/>
     </row>
     <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32">
-        <v>11.05</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D32" s="6"/>
       <c r="G32" s="25"/>
     </row>
     <row r="33" spans="1:7" ht="15.75">
       <c r="A33" s="6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33">
-        <v>20</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D33" s="6"/>
       <c r="G33" s="25"/>
     </row>
     <row r="34" spans="1:7" ht="15.75">
       <c r="A34" s="6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34">
-        <v>1.98</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D34" s="6"/>
       <c r="G34" s="25"/>
     </row>
     <row r="35" spans="1:7" ht="15.75">
       <c r="A35" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35">
-        <v>13.77</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D35" s="6"/>
       <c r="G35" s="25"/>
     </row>
     <row r="36" spans="1:7" ht="15.75">
       <c r="A36" s="6" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D36" s="6"/>
-      <c r="E36">
-        <v>4.91</v>
-      </c>
       <c r="G36" s="25"/>
     </row>
     <row r="37" spans="1:7" ht="15.75">
       <c r="A37" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37">
-        <v>8.0299999999999994</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D37" s="6"/>
       <c r="G37" s="25"/>
     </row>
     <row r="38" spans="1:7" ht="15.75">
       <c r="A38" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D38" s="6"/>
-      <c r="E38">
-        <v>16.22</v>
-      </c>
       <c r="G38" s="25"/>
     </row>
     <row r="39" spans="1:7" ht="15.75">
       <c r="A39" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39">
-        <v>0.5</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D39" s="6"/>
       <c r="G39" s="25"/>
     </row>
     <row r="40" spans="1:7" ht="15.75">
       <c r="A40" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D40" s="6"/>
-      <c r="E40">
-        <v>12.69</v>
-      </c>
       <c r="G40" s="25"/>
     </row>
     <row r="41" spans="1:7" ht="15.75">
       <c r="A41" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41">
-        <v>17.46</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D41" s="6"/>
       <c r="G41" s="25"/>
     </row>
     <row r="42" spans="1:7" ht="15.75">
       <c r="A42" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E42">
-        <v>5.32</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D42" s="6"/>
       <c r="G42" s="25"/>
     </row>
     <row r="43" spans="1:7" ht="15.75">
       <c r="A43" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43">
-        <v>19.309999999999999</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D43" s="6"/>
       <c r="G43" s="25"/>
     </row>
     <row r="44" spans="1:7" ht="15.75">
       <c r="A44" s="6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D44" s="6"/>
-      <c r="E44">
-        <v>10.5</v>
-      </c>
       <c r="G44" s="25"/>
     </row>
     <row r="45" spans="1:7" ht="15.75">
       <c r="A45" s="6" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45">
-        <v>3.48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D45" s="6"/>
       <c r="G45" s="25"/>
     </row>
     <row r="46" spans="1:7" ht="15.75">
       <c r="A46" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46">
-        <v>15.88</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D46" s="6"/>
       <c r="G46" s="25"/>
     </row>
     <row r="47" spans="1:7" ht="15.75">
       <c r="A47" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47">
-        <v>7.14</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D47" s="7"/>
       <c r="G47" s="25"/>
     </row>
     <row r="48" spans="1:7" ht="15.75">
       <c r="A48" s="7" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E48">
-        <v>2.09</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D48" s="7"/>
       <c r="G48" s="25"/>
     </row>
     <row r="49" spans="1:7" ht="15.75">
       <c r="A49" s="7" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49">
-        <v>18.649999999999999</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D49" s="7"/>
       <c r="G49" s="25"/>
     </row>
     <row r="50" spans="1:7" ht="15.75">
       <c r="A50" s="7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50">
-        <v>9.83</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D50" s="7"/>
       <c r="G50" s="25"/>
     </row>
     <row r="51" spans="1:7" ht="15.75">
       <c r="A51" s="7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51">
-        <v>14.12</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D51" s="7"/>
       <c r="G51" s="25"/>
     </row>
     <row r="52" spans="1:7" ht="15.75">
       <c r="A52" s="7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52">
-        <v>1.23</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D52" s="7"/>
       <c r="G52" s="25"/>
     </row>
     <row r="53" spans="1:7" ht="15.75">
       <c r="A53" s="7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53">
-        <v>20</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D53" s="7"/>
       <c r="G53" s="25"/>
     </row>
     <row r="54" spans="1:7" ht="15.75">
       <c r="A54" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54">
-        <v>6.91</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D54" s="7"/>
       <c r="G54" s="25"/>
     </row>
     <row r="55" spans="1:7" ht="15.75">
       <c r="A55" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D55" s="7"/>
-      <c r="E55">
-        <v>11.68</v>
-      </c>
       <c r="G55" s="25"/>
     </row>
     <row r="56" spans="1:7" ht="15.75">
       <c r="A56" s="7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56">
-        <v>4.03</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D56" s="7"/>
       <c r="G56" s="25"/>
     </row>
     <row r="57" spans="1:7" ht="15.75">
       <c r="A57" s="7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D57" s="7"/>
-      <c r="E57">
-        <v>16.79</v>
-      </c>
       <c r="G57" s="25"/>
     </row>
     <row r="58" spans="1:7" ht="15.75">
       <c r="A58" s="7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58">
-        <v>8.57</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D58" s="7"/>
       <c r="G58" s="25"/>
     </row>
     <row r="59" spans="1:7" ht="15.75">
       <c r="A59" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E59">
-        <v>0.86</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D59" s="7"/>
       <c r="G59" s="25"/>
     </row>
     <row r="60" spans="1:7" ht="15.75">
       <c r="A60" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E60">
-        <v>13.44</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D60" s="7"/>
       <c r="G60" s="25"/>
     </row>
     <row r="61" spans="1:7" ht="15.75">
       <c r="A61" s="7" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D61" s="7"/>
-      <c r="E61">
-        <v>19.559999999999999</v>
-      </c>
       <c r="G61" s="25"/>
     </row>
     <row r="62" spans="1:7" ht="15.75">
       <c r="A62" s="8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E62">
-        <v>3.77</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D62" s="8"/>
       <c r="G62" s="25"/>
     </row>
     <row r="63" spans="1:7" ht="15.75">
       <c r="A63" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63">
-        <v>10.23</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D63" s="8"/>
       <c r="G63" s="25"/>
     </row>
     <row r="64" spans="1:7" ht="15.75">
       <c r="A64" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D64" s="8"/>
-      <c r="E64">
-        <v>17.010000000000002</v>
-      </c>
       <c r="G64" s="25"/>
     </row>
     <row r="65" spans="1:7" ht="15.75">
       <c r="A65" s="8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65">
-        <v>2.65</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D65" s="8"/>
       <c r="G65" s="25"/>
     </row>
     <row r="66" spans="1:7" ht="15.75">
       <c r="A66" s="8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E66">
-        <v>14.89</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D66" s="8"/>
       <c r="G66" s="25"/>
     </row>
     <row r="67" spans="1:7" ht="15.75">
       <c r="A67" s="8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67">
-        <v>5.97</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D67" s="8"/>
       <c r="G67" s="25"/>
     </row>
     <row r="68" spans="1:7" ht="15.75">
       <c r="A68" s="8" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D68" s="8"/>
-      <c r="E68">
-        <v>12.5</v>
-      </c>
       <c r="G68" s="25"/>
     </row>
     <row r="69" spans="1:7" ht="15.75">
       <c r="A69" s="8" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E69">
-        <v>0.94</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D69" s="8"/>
       <c r="G69" s="25"/>
     </row>
     <row r="70" spans="1:7" ht="15.75">
       <c r="A70" s="8" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70">
-        <v>18.18</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D70" s="8"/>
       <c r="G70" s="25"/>
     </row>
     <row r="71" spans="1:7" ht="15.75">
       <c r="A71" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E71">
-        <v>7.36</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D71" s="8"/>
       <c r="G71" s="25"/>
     </row>
     <row r="72" spans="1:7" ht="15.75">
       <c r="A72" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E72">
-        <v>15.22</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D72" s="8"/>
       <c r="G72" s="25"/>
     </row>
     <row r="73" spans="1:7" ht="15.75">
       <c r="A73" s="8" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73">
-        <v>4.72</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D73" s="8"/>
       <c r="G73" s="25"/>
     </row>
     <row r="74" spans="1:7" ht="15.75">
       <c r="A74" s="8" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74">
-        <v>9.08</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D74" s="8"/>
       <c r="G74" s="25"/>
     </row>
     <row r="75" spans="1:7" ht="15.75">
       <c r="A75" s="8" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75">
-        <v>19.75</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D75" s="8"/>
       <c r="G75" s="25"/>
     </row>
     <row r="76" spans="1:7" ht="15.75">
       <c r="A76" s="8" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76">
-        <v>1.87</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D76" s="8"/>
       <c r="G76" s="25"/>
     </row>
     <row r="77" spans="1:7" ht="15.75">
       <c r="A77" s="9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E77">
-        <v>11.32</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D77" s="9"/>
       <c r="G77" s="25"/>
     </row>
     <row r="78" spans="1:7" ht="15.75">
       <c r="A78" s="9" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D78" s="9"/>
-      <c r="E78">
-        <v>20</v>
-      </c>
       <c r="G78" s="25"/>
     </row>
     <row r="79" spans="1:7" ht="15.75">
       <c r="A79" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E79">
-        <v>3.49</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D79" s="9"/>
       <c r="G79" s="25"/>
     </row>
     <row r="80" spans="1:7" ht="15.75">
       <c r="A80" s="9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E80">
-        <v>16.03</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D80" s="9"/>
       <c r="G80" s="25"/>
     </row>
     <row r="81" spans="1:7" ht="15.75">
       <c r="A81" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81">
-        <v>6.28</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D81" s="9"/>
       <c r="G81" s="25"/>
     </row>
     <row r="82" spans="1:7" ht="15.75">
       <c r="A82" s="9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82">
-        <v>13.91</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D82" s="9"/>
       <c r="G82" s="25"/>
     </row>
     <row r="83" spans="1:7" ht="15.75">
       <c r="A83" s="9" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E83">
-        <v>8.7899999999999991</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D83" s="9"/>
       <c r="G83" s="25"/>
     </row>
     <row r="84" spans="1:7" ht="15.75">
       <c r="A84" s="9" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84">
-        <v>0.68</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D84" s="9"/>
       <c r="G84" s="25"/>
     </row>
     <row r="85" spans="1:7" ht="15.75">
       <c r="A85" s="9" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E85">
-        <v>17.579999999999998</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D85" s="9"/>
       <c r="G85" s="25"/>
     </row>
     <row r="86" spans="1:7" ht="15.75">
       <c r="A86" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E86">
-        <v>2.14</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D86" s="9"/>
       <c r="G86" s="25"/>
     </row>
     <row r="87" spans="1:7" ht="15.75">
       <c r="A87" s="9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87">
-        <v>10.41</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D87" s="9"/>
       <c r="G87" s="25"/>
     </row>
     <row r="88" spans="1:7" ht="15.75">
       <c r="A88" s="9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D88" s="9"/>
-      <c r="E88">
-        <v>14.77</v>
-      </c>
       <c r="G88" s="25"/>
     </row>
     <row r="89" spans="1:7" ht="15.75">
       <c r="A89" s="9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D89" s="9"/>
-      <c r="E89">
-        <v>5.03</v>
-      </c>
       <c r="G89" s="25"/>
     </row>
     <row r="90" spans="1:7" ht="15.75">
       <c r="A90" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D90" s="9"/>
-      <c r="E90">
-        <v>18.420000000000002</v>
-      </c>
       <c r="G90" s="25"/>
     </row>
     <row r="91" spans="1:7" ht="15.75">
       <c r="A91" s="9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91">
-        <v>7.69</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D91" s="9"/>
       <c r="G91" s="25"/>
     </row>
     <row r="92" spans="1:7" ht="15.75">
       <c r="A92" s="10" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E92">
-        <v>1.34</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D92" s="10"/>
       <c r="G92" s="25"/>
     </row>
     <row r="93" spans="1:7" ht="15.75">
       <c r="A93" s="10" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E93">
-        <v>12.15</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D93" s="10"/>
       <c r="G93" s="25"/>
     </row>
     <row r="94" spans="1:7" ht="15.75">
       <c r="A94" s="10" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E94">
-        <v>4.59</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D94" s="10"/>
       <c r="G94" s="25"/>
     </row>
     <row r="95" spans="1:7" ht="15.75">
       <c r="A95" s="10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E95">
-        <v>9.91</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D95" s="10"/>
       <c r="G95" s="25"/>
     </row>
     <row r="96" spans="1:7" ht="15.75">
       <c r="A96" s="10" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D96" s="10"/>
-      <c r="E96">
-        <v>20</v>
-      </c>
       <c r="G96" s="25"/>
     </row>
     <row r="97" spans="1:7" ht="15.75">
       <c r="A97" s="10" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D97" s="10"/>
-      <c r="E97">
-        <v>15.44</v>
-      </c>
       <c r="G97" s="25"/>
     </row>
     <row r="98" spans="1:7" ht="15.75">
       <c r="A98" s="10" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E98">
-        <v>3.02</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D98" s="10"/>
       <c r="G98" s="25"/>
     </row>
     <row r="99" spans="1:7" ht="15.75">
       <c r="A99" s="10" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D99" s="10"/>
-      <c r="E99">
-        <v>11.86</v>
-      </c>
       <c r="G99" s="25"/>
     </row>
     <row r="100" spans="1:7" ht="15.75">
       <c r="A100" s="10" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D100" s="10"/>
-      <c r="E100">
-        <v>6.57</v>
-      </c>
       <c r="G100" s="25"/>
     </row>
     <row r="101" spans="1:7" ht="15.75">
       <c r="A101" s="10" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101">
-        <v>0.77</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D101" s="10"/>
       <c r="G101" s="25"/>
     </row>
     <row r="102" spans="1:7" ht="15.75">
       <c r="A102" s="10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D102" s="10"/>
-      <c r="E102">
-        <v>17.34</v>
-      </c>
       <c r="G102" s="25"/>
     </row>
     <row r="103" spans="1:7" ht="15.75">
       <c r="A103" s="10" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E103">
-        <v>8.2100000000000009</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D103" s="10"/>
       <c r="G103" s="25"/>
     </row>
     <row r="104" spans="1:7" ht="15.75">
       <c r="A104" s="10" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E104">
-        <v>13.66</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D104" s="10"/>
       <c r="G104" s="25"/>
     </row>
     <row r="105" spans="1:7" ht="15.75">
       <c r="A105" s="10" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D105" s="10"/>
-      <c r="E105">
-        <v>2.4300000000000002</v>
-      </c>
       <c r="G105" s="25"/>
     </row>
     <row r="106" spans="1:7" ht="15.75">
       <c r="A106" s="10" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D106" s="10"/>
-      <c r="E106">
-        <v>19.23</v>
-      </c>
       <c r="G106" s="25"/>
     </row>
     <row r="107" spans="1:7" ht="15.75">
       <c r="A107" s="11" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D107" s="11"/>
-      <c r="E107">
-        <v>4.18</v>
-      </c>
       <c r="G107" s="25"/>
     </row>
     <row r="108" spans="1:7" ht="15.75">
       <c r="A108" s="11" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D108" s="11"/>
-      <c r="E108">
-        <v>10.72</v>
-      </c>
       <c r="G108" s="25"/>
     </row>
     <row r="109" spans="1:7" ht="15.75">
       <c r="A109" s="11" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D109" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109">
-        <v>16.97</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D109" s="11"/>
       <c r="G109" s="25"/>
     </row>
     <row r="110" spans="1:7" ht="15.75">
       <c r="A110" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D110" s="11"/>
-      <c r="E110">
-        <v>1.1100000000000001</v>
-      </c>
       <c r="G110" s="25"/>
     </row>
     <row r="111" spans="1:7" ht="15.75">
       <c r="A111" s="11" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E111">
-        <v>7.85</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D111" s="11"/>
       <c r="G111" s="25"/>
     </row>
     <row r="112" spans="1:7" ht="15.75">
       <c r="A112" s="11" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E112">
-        <v>14.08</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D112" s="11"/>
       <c r="G112" s="25"/>
     </row>
     <row r="113" spans="1:7" ht="15.75">
       <c r="A113" s="11" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E113">
-        <v>20</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D113" s="11"/>
       <c r="G113" s="25"/>
     </row>
     <row r="114" spans="1:7" ht="15.75">
       <c r="A114" s="11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114">
-        <v>5.46</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D114" s="11"/>
       <c r="G114" s="25"/>
     </row>
     <row r="115" spans="1:7" ht="15.75">
       <c r="A115" s="11" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E115">
-        <v>12.81</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D115" s="11"/>
       <c r="G115" s="25"/>
     </row>
     <row r="116" spans="1:7" ht="15.75">
       <c r="A116" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116">
-        <v>3.63</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D116" s="11"/>
       <c r="G116" s="25"/>
     </row>
     <row r="117" spans="1:7" ht="15.75">
       <c r="A117" s="11" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D117" s="11"/>
-      <c r="E117">
-        <v>9.2899999999999991</v>
-      </c>
       <c r="G117" s="25"/>
     </row>
     <row r="118" spans="1:7" ht="15.75">
       <c r="A118" s="11" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E118">
-        <v>18.71</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D118" s="11"/>
       <c r="G118" s="25"/>
     </row>
     <row r="119" spans="1:7" ht="15.75">
       <c r="A119" s="11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E119">
-        <v>0.63</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D119" s="11"/>
       <c r="G119" s="25"/>
     </row>
     <row r="120" spans="1:7" ht="15.75">
       <c r="A120" s="11" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E120">
-        <v>15.6</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D120" s="11"/>
       <c r="G120" s="25"/>
     </row>
     <row r="121" spans="1:7" ht="15.75">
       <c r="A121" s="11" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D121" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E121">
-        <v>2.98</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D121" s="11"/>
       <c r="G121" s="25"/>
     </row>
     <row r="122" spans="1:7" ht="15.75">
       <c r="A122" s="12" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122">
-        <v>8.8800000000000008</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D122" s="12"/>
       <c r="G122" s="25"/>
     </row>
     <row r="123" spans="1:7" ht="15.75">
       <c r="A123" s="12" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D123" s="12"/>
-      <c r="E123">
-        <v>1.76</v>
-      </c>
       <c r="G123" s="25"/>
     </row>
     <row r="124" spans="1:7" ht="15.75">
       <c r="A124" s="12" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D124" s="12"/>
-      <c r="E124">
-        <v>19.04</v>
-      </c>
       <c r="G124" s="25"/>
     </row>
     <row r="125" spans="1:7" ht="15.75">
       <c r="A125" s="12" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B125" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D125" s="12"/>
-      <c r="E125">
-        <v>4.37</v>
-      </c>
       <c r="G125" s="25"/>
     </row>
     <row r="126" spans="1:7" ht="15.75">
       <c r="A126" s="12" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B126" s="12"/>
       <c r="C126" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D126" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126">
-        <v>11.19</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D126" s="12"/>
       <c r="G126" s="25"/>
     </row>
     <row r="127" spans="1:7" ht="15.75">
       <c r="A127" s="12" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B127" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127">
-        <v>17.22</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D127" s="12"/>
       <c r="G127" s="25"/>
     </row>
     <row r="128" spans="1:7" ht="15.75">
       <c r="A128" s="12" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D128" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E128">
-        <v>6.82</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D128" s="12"/>
       <c r="G128" s="25"/>
     </row>
     <row r="129" spans="1:7" ht="15.75">
       <c r="A129" s="12" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D129" s="12"/>
-      <c r="E129">
-        <v>13.33</v>
-      </c>
       <c r="G129" s="25"/>
     </row>
     <row r="130" spans="1:7" ht="15.75">
       <c r="A130" s="12" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D130" s="12"/>
-      <c r="E130">
-        <v>20</v>
-      </c>
       <c r="G130" s="25"/>
     </row>
     <row r="131" spans="1:7" ht="15.75">
       <c r="A131" s="12" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D131" s="12"/>
-      <c r="E131">
-        <v>0.59</v>
-      </c>
       <c r="G131" s="25"/>
     </row>
     <row r="132" spans="1:7" ht="15.75">
       <c r="A132" s="12" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B132" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D132" s="12"/>
-      <c r="E132">
-        <v>14.45</v>
-      </c>
       <c r="G132" s="25"/>
     </row>
     <row r="133" spans="1:7" ht="15.75">
       <c r="A133" s="12" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D133" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E133">
-        <v>3.91</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D133" s="12"/>
       <c r="G133" s="25"/>
     </row>
     <row r="134" spans="1:7" ht="15.75">
       <c r="A134" s="12" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B134" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D134" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E134">
-        <v>9.74</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D134" s="12"/>
       <c r="G134" s="25"/>
     </row>
     <row r="135" spans="1:7" ht="15.75">
       <c r="A135" s="12" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D135" s="12"/>
-      <c r="E135">
-        <v>16.36</v>
-      </c>
       <c r="G135" s="25"/>
     </row>
     <row r="136" spans="1:7" ht="15.75">
       <c r="A136" s="12" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D136" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E136">
-        <v>7.48</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D136" s="12"/>
       <c r="G136" s="25"/>
     </row>
     <row r="137" spans="1:7" ht="15.75">
       <c r="A137" s="13" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B137" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E137">
-        <v>2.2599999999999998</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D137" s="13"/>
       <c r="G137" s="25"/>
     </row>
     <row r="138" spans="1:7" ht="15.75">
       <c r="A138" s="13" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E138">
-        <v>13.33</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D138" s="13"/>
       <c r="G138" s="25"/>
     </row>
     <row r="139" spans="1:7" ht="15.75">
       <c r="A139" s="13" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B139" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D139" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E139">
-        <v>20</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D139" s="13"/>
       <c r="G139" s="25"/>
     </row>
     <row r="140" spans="1:7" ht="15.75">
       <c r="A140" s="13" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B140" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D140" s="13"/>
-      <c r="E140">
-        <v>0.59</v>
-      </c>
       <c r="G140" s="25"/>
     </row>
     <row r="141" spans="1:7" ht="15.75">
       <c r="A141" s="13" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E141">
-        <v>14.45</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D141" s="13"/>
       <c r="G141" s="25"/>
     </row>
     <row r="142" spans="1:7" ht="15.75">
       <c r="A142" s="13" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B142" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D142" s="13"/>
-      <c r="E142">
-        <v>3.91</v>
-      </c>
       <c r="G142" s="25"/>
     </row>
     <row r="143" spans="1:7" ht="15.75">
       <c r="A143" s="13" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E143">
-        <v>9.74</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D143" s="13"/>
       <c r="G143" s="25"/>
     </row>
     <row r="144" spans="1:7" ht="15.75">
       <c r="A144" s="13" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B144" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D144" s="13"/>
-      <c r="E144">
-        <v>16.36</v>
-      </c>
       <c r="G144" s="25"/>
     </row>
     <row r="145" spans="1:7" ht="15.75">
       <c r="A145" s="13" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B145" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E145">
-        <v>7.48</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D145" s="13"/>
       <c r="G145" s="25"/>
     </row>
     <row r="146" spans="1:7" ht="15.75">
       <c r="A146" s="13" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D146" s="13"/>
-      <c r="E146">
-        <v>2.2599999999999998</v>
-      </c>
       <c r="G146" s="25"/>
     </row>
     <row r="147" spans="1:7" ht="15.75">
       <c r="A147" s="13" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D147" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E147">
-        <v>12.93</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D147" s="13"/>
       <c r="G147" s="25"/>
     </row>
     <row r="148" spans="1:7" ht="15.75">
       <c r="A148" s="13" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E148">
-        <v>18.03</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D148" s="13"/>
       <c r="G148" s="25"/>
     </row>
     <row r="149" spans="1:7" ht="15.75">
       <c r="A149" s="13" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B149" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D149" s="13"/>
-      <c r="E149">
-        <v>5.18</v>
-      </c>
       <c r="G149" s="25"/>
     </row>
     <row r="150" spans="1:7" ht="15.75">
       <c r="A150" s="13" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D150" s="13"/>
-      <c r="E150">
-        <v>9.2899999999999991</v>
-      </c>
       <c r="G150" s="25"/>
     </row>
     <row r="151" spans="1:7" ht="15.75">
       <c r="A151" s="13" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151">
-        <v>18.71</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="D151" s="13"/>
       <c r="G151" s="25"/>
     </row>
     <row r="152" spans="1:7" ht="15.75">
       <c r="A152" s="15" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B152" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D152" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E152">
-        <v>2.2599999999999998</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D152" s="15"/>
       <c r="G152" s="25"/>
     </row>
     <row r="153" spans="1:7" ht="15.75">
       <c r="A153" s="15" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D153" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E153">
-        <v>13.33</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D153" s="15"/>
       <c r="G153" s="25"/>
     </row>
     <row r="154" spans="1:7" ht="15.75">
       <c r="A154" s="15" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D154" s="15"/>
-      <c r="E154">
-        <v>20</v>
-      </c>
       <c r="G154" s="25"/>
     </row>
     <row r="155" spans="1:7" ht="15.75">
       <c r="A155" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D155" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E155">
-        <v>0.59</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D155" s="15"/>
       <c r="G155" s="25"/>
     </row>
     <row r="156" spans="1:7" ht="15.75">
       <c r="A156" s="15" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D156" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E156">
-        <v>14.45</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D156" s="15"/>
       <c r="G156" s="25"/>
     </row>
     <row r="157" spans="1:7" ht="15.75">
       <c r="A157" s="15" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D157" s="15"/>
-      <c r="E157">
-        <v>3.91</v>
-      </c>
       <c r="G157" s="25"/>
     </row>
     <row r="158" spans="1:7" ht="15.75">
       <c r="A158" s="15" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B158" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D158" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E158">
-        <v>9.74</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D158" s="15"/>
       <c r="G158" s="25"/>
     </row>
     <row r="159" spans="1:7" ht="15.75">
       <c r="A159" s="15" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D159" s="15"/>
-      <c r="E159">
-        <v>16.36</v>
-      </c>
       <c r="G159" s="25"/>
     </row>
     <row r="160" spans="1:7" ht="15.75">
       <c r="A160" s="15" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D160" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E160">
-        <v>7.48</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D160" s="15"/>
       <c r="G160" s="25"/>
     </row>
     <row r="161" spans="1:7" ht="15.75">
       <c r="A161" s="15" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D161" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E161">
-        <v>2.2599999999999998</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D161" s="15"/>
       <c r="G161" s="25"/>
     </row>
     <row r="162" spans="1:7" ht="15.75">
       <c r="A162" s="15" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D162" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E162">
-        <v>12.93</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D162" s="15"/>
       <c r="G162" s="25"/>
     </row>
     <row r="163" spans="1:7" ht="15.75">
       <c r="A163" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D163" s="15"/>
-      <c r="E163">
-        <v>18.03</v>
-      </c>
       <c r="G163" s="25"/>
     </row>
     <row r="164" spans="1:7" ht="15.75">
       <c r="A164" s="15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D164" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E164">
-        <v>5.18</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D164" s="15"/>
       <c r="G164" s="25"/>
     </row>
     <row r="165" spans="1:7" ht="15.75">
       <c r="A165" s="15" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D165" s="15"/>
-      <c r="E165">
-        <v>9.2899999999999991</v>
-      </c>
       <c r="G165" s="25"/>
     </row>
     <row r="166" spans="1:7" ht="15.75">
       <c r="A166" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D166" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E166">
-        <v>18.71</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D166" s="15"/>
       <c r="G166" s="25"/>
     </row>
     <row r="167" spans="1:7" ht="15.75">
       <c r="A167" s="14" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B167" s="14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D167" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E167">
-        <v>2.2599999999999998</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D167" s="14"/>
       <c r="G167" s="25"/>
     </row>
     <row r="168" spans="1:7" ht="15.75">
       <c r="A168" s="14" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D168" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E168">
-        <v>13.33</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D168" s="14"/>
       <c r="G168" s="25"/>
     </row>
     <row r="169" spans="1:7" ht="15.75">
       <c r="A169" s="14" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B169" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D169" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E169">
-        <v>20</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D169" s="14"/>
       <c r="G169" s="25"/>
     </row>
     <row r="170" spans="1:7" ht="15.75">
       <c r="A170" s="14" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D170" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E170">
-        <v>0.59</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D170" s="14"/>
       <c r="G170" s="25"/>
     </row>
     <row r="171" spans="1:7" ht="15.75">
       <c r="A171" s="14" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B171" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D171" s="14"/>
-      <c r="E171">
-        <v>14.45</v>
-      </c>
       <c r="G171" s="25"/>
     </row>
     <row r="172" spans="1:7" ht="15.75">
       <c r="A172" s="14" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D172" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E172">
-        <v>3.91</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D172" s="14"/>
       <c r="G172" s="25"/>
     </row>
     <row r="173" spans="1:7" ht="15.75">
       <c r="A173" s="14" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B173" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D173" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E173">
-        <v>9.74</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D173" s="14"/>
       <c r="G173" s="25"/>
     </row>
     <row r="174" spans="1:7" ht="15.75">
       <c r="A174" s="14" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D174" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E174">
-        <v>16.36</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D174" s="14"/>
       <c r="G174" s="25"/>
     </row>
     <row r="175" spans="1:7" ht="15.75">
       <c r="A175" s="14" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B175" s="14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D175" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E175">
-        <v>7.48</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D175" s="14"/>
       <c r="G175" s="25"/>
     </row>
     <row r="176" spans="1:7" ht="15.75">
       <c r="A176" s="14" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B176" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D176" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E176">
-        <v>2.2599999999999998</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D176" s="14"/>
       <c r="G176" s="25"/>
     </row>
     <row r="177" spans="1:7" ht="15.75">
       <c r="A177" s="14" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B177" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D177" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E177">
-        <v>12.93</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D177" s="14"/>
       <c r="G177" s="25"/>
     </row>
     <row r="178" spans="1:7" ht="15.75">
       <c r="A178" s="14" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B178" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D178" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E178">
-        <v>18.03</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D178" s="14"/>
       <c r="G178" s="25"/>
     </row>
     <row r="179" spans="1:7" ht="15.75">
       <c r="A179" s="14" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D179" s="14"/>
-      <c r="E179">
-        <v>5.18</v>
-      </c>
       <c r="G179" s="25"/>
     </row>
     <row r="180" spans="1:7" ht="15.75">
       <c r="A180" s="14" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B180" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D180" s="14"/>
-      <c r="E180">
-        <v>9.2899999999999991</v>
-      </c>
       <c r="G180" s="25"/>
     </row>
     <row r="181" spans="1:7" ht="15.75">
       <c r="A181" s="14" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B181" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D181" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E181">
-        <v>18.71</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="D181" s="14"/>
       <c r="G181" s="25"/>
     </row>
     <row r="182" spans="1:7" ht="15.75">
@@ -5097,66 +4282,66 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75">
       <c r="A8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75">
@@ -5191,24 +4376,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
     </row>
     <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="21" t="s">
@@ -5228,238 +4413,144 @@
       <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C6" s="26" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" s="26" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3">
         <v>12</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3">
         <v>14</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C23" s="26" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="3"/>
     </row>
   </sheetData>
@@ -5505,24 +4596,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="A1" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
     </row>
     <row r="5" spans="1:4" ht="15.75">
       <c r="A5" s="20" t="s">
@@ -5542,240 +4633,144 @@
       <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C15" s="26" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>223</v>
-      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C20" s="26" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="26"/>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C21" s="26" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="26"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
   </sheetData>
@@ -5821,24 +4816,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
     </row>
     <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
     </row>
     <row r="5" spans="1:4" ht="15.75">
       <c r="A5" s="16" t="s">
@@ -5858,238 +4853,144 @@
       <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="26" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C7" s="26" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" s="26" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="26"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
   </sheetData>
@@ -6135,24 +5036,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="A1" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
     </row>
     <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="18" t="s">
@@ -6172,240 +5073,144 @@
       <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="26" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C12" s="26" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C13" s="26" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3">
         <v>12</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>223</v>
-      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3">
         <v>14</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
   </sheetData>
@@ -6451,24 +5256,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="5" spans="1:4" ht="15.75">
       <c r="A5" s="17" t="s">
@@ -6488,239 +5293,145 @@
       <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="26" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3">
         <v>12</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3">
         <v>14</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C20" s="26" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="26"/>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="26" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="26"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6765,36 +5476,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="34" t="s">
-        <v>227</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
+      <c r="A1" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
     </row>
     <row r="5" spans="1:4" ht="15.75">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="27" t="s">
         <v>219</v>
       </c>
     </row>
@@ -6802,238 +5513,144 @@
       <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11" s="26" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Australia</v>
-      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C22" s="26" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C23" s="26" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="3"/>
     </row>
   </sheetData>
@@ -7079,24 +5696,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
+      <c r="A1" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
     </row>
     <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
     </row>
     <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="19" t="s">
@@ -7116,240 +5733,144 @@
       <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Ireland</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>New Zealand</v>
-      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Scotland</v>
-      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>South Africa</v>
-      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C17" s="26" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="26"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Netherlands</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>223</v>
-      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3">
         <v>14</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Pakistan</v>
-      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Bangladesh</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C21" s="26" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>Sri Lanka</v>
-      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="26"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C22" s="26" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>West Indies</v>
-      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],WWC_Players_All[#All],3,0),"")</f>
-        <v>India</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
   </sheetData>

--- a/dwl-fantasy-platform/backend/WWC_Config.xlsx
+++ b/dwl-fantasy-platform/backend/WWC_Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kishan/Downloads/Delulu Leagues/DWL Delulu Women's League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86805392-6D4E-49F3-9229-5EF7F3965973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2ADAD03D-6589-40CA-BDAB-6A7C1E0434ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="5" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="226">
   <si>
     <t>Player Name</t>
   </si>
@@ -1425,7 +1425,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}" name="WWC_Players_All" displayName="WWC_Players_All" ref="A1:E181" totalsRowShown="0">
-  <autoFilter ref="A1:E181" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}"/>
+  <autoFilter ref="A1:E181" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Rajputana Ranis"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E181">
     <sortCondition ref="A1:A181"/>
   </sortState>
@@ -1925,7 +1931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" hidden="1">
       <c r="A2" s="14" t="s">
         <v>5</v>
       </c>
@@ -1943,7 +1949,7 @@
       </c>
       <c r="F2" s="27"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" hidden="1">
       <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
@@ -1961,7 +1967,7 @@
       </c>
       <c r="F3" s="27"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" hidden="1">
       <c r="A4" s="14" t="s">
         <v>12</v>
       </c>
@@ -1979,7 +1985,7 @@
       </c>
       <c r="F4" s="27"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" hidden="1">
       <c r="A5" s="12" t="s">
         <v>14</v>
       </c>
@@ -1993,7 +1999,7 @@
       <c r="E5" s="26"/>
       <c r="F5" s="27"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" hidden="1">
       <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
@@ -2007,7 +2013,7 @@
       <c r="E6" s="26"/>
       <c r="F6" s="27"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" hidden="1">
       <c r="A7" s="8" t="s">
         <v>18</v>
       </c>
@@ -2021,7 +2027,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="27"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" hidden="1">
       <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
@@ -2057,7 +2063,7 @@
       </c>
       <c r="F9" s="27"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" hidden="1">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
@@ -2071,7 +2077,7 @@
       <c r="E10" s="26"/>
       <c r="F10" s="27"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" hidden="1">
       <c r="A11" s="8" t="s">
         <v>27</v>
       </c>
@@ -2089,7 +2095,7 @@
       </c>
       <c r="F11" s="27"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" hidden="1">
       <c r="A12" s="6" t="s">
         <v>28</v>
       </c>
@@ -2107,7 +2113,7 @@
       </c>
       <c r="F12" s="27"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" hidden="1">
       <c r="A13" s="4" t="s">
         <v>30</v>
       </c>
@@ -2125,7 +2131,7 @@
       </c>
       <c r="F13" s="27"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" hidden="1">
       <c r="A14" s="13" t="s">
         <v>31</v>
       </c>
@@ -2143,7 +2149,7 @@
       </c>
       <c r="F14" s="27"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" hidden="1">
       <c r="A15" s="8" t="s">
         <v>33</v>
       </c>
@@ -2175,7 +2181,7 @@
       </c>
       <c r="F16" s="27"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17" s="4" t="s">
         <v>36</v>
       </c>
@@ -2193,7 +2199,7 @@
       </c>
       <c r="F17" s="27"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18" s="14" t="s">
         <v>38</v>
       </c>
@@ -2207,7 +2213,7 @@
       <c r="E18" s="26"/>
       <c r="F18" s="27"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" hidden="1">
       <c r="A19" s="8" t="s">
         <v>39</v>
       </c>
@@ -2239,7 +2245,7 @@
       </c>
       <c r="F20" s="27"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21" s="11" t="s">
         <v>41</v>
       </c>
@@ -2257,7 +2263,7 @@
       </c>
       <c r="F21" s="27"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" hidden="1">
       <c r="A22" s="9" t="s">
         <v>43</v>
       </c>
@@ -2271,7 +2277,7 @@
       <c r="E22" s="26"/>
       <c r="F22" s="27"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23" s="4" t="s">
         <v>45</v>
       </c>
@@ -2289,7 +2295,7 @@
       </c>
       <c r="F23" s="27"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" hidden="1">
       <c r="A24" s="7" t="s">
         <v>46</v>
       </c>
@@ -2307,7 +2313,7 @@
       </c>
       <c r="F24" s="27"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" hidden="1">
       <c r="A25" s="10" t="s">
         <v>47</v>
       </c>
@@ -2325,7 +2331,7 @@
       </c>
       <c r="F25" s="27"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" hidden="1">
       <c r="A26" s="10" t="s">
         <v>49</v>
       </c>
@@ -2343,7 +2349,7 @@
       </c>
       <c r="F26" s="27"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" hidden="1">
       <c r="A27" s="8" t="s">
         <v>50</v>
       </c>
@@ -2361,7 +2367,7 @@
       </c>
       <c r="F27" s="27"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" hidden="1">
       <c r="A28" s="9" t="s">
         <v>51</v>
       </c>
@@ -2393,7 +2399,7 @@
       </c>
       <c r="F29" s="27"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" hidden="1">
       <c r="A30" s="6" t="s">
         <v>54</v>
       </c>
@@ -2411,7 +2417,7 @@
       </c>
       <c r="F30" s="27"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" hidden="1">
       <c r="A31" s="14" t="s">
         <v>55</v>
       </c>
@@ -2429,7 +2435,7 @@
       </c>
       <c r="F31" s="27"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" hidden="1">
       <c r="A32" s="12" t="s">
         <v>57</v>
       </c>
@@ -2443,7 +2449,7 @@
       <c r="E32" s="26"/>
       <c r="F32" s="27"/>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" hidden="1">
       <c r="A33" s="13" t="s">
         <v>58</v>
       </c>
@@ -2461,7 +2467,7 @@
       </c>
       <c r="F33" s="27"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" hidden="1">
       <c r="A34" s="8" t="s">
         <v>59</v>
       </c>
@@ -2475,7 +2481,7 @@
       <c r="E34" s="26"/>
       <c r="F34" s="27"/>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" hidden="1">
       <c r="A35" s="13" t="s">
         <v>60</v>
       </c>
@@ -2493,7 +2499,7 @@
       </c>
       <c r="F35" s="27"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" hidden="1">
       <c r="A36" s="6" t="s">
         <v>61</v>
       </c>
@@ -2507,7 +2513,7 @@
       <c r="E36" s="26"/>
       <c r="F36" s="27"/>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" hidden="1">
       <c r="A37" s="6" t="s">
         <v>62</v>
       </c>
@@ -2525,7 +2531,7 @@
       </c>
       <c r="F37" s="27"/>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" hidden="1">
       <c r="A38" s="12" t="s">
         <v>63</v>
       </c>
@@ -2539,7 +2545,7 @@
       <c r="E38" s="26"/>
       <c r="F38" s="27"/>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" hidden="1">
       <c r="A39" s="14" t="s">
         <v>64</v>
       </c>
@@ -2557,7 +2563,7 @@
       </c>
       <c r="F39" s="27"/>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" hidden="1">
       <c r="A40" s="7" t="s">
         <v>65</v>
       </c>
@@ -2575,7 +2581,7 @@
       </c>
       <c r="F40" s="27"/>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" hidden="1">
       <c r="A41" s="11" t="s">
         <v>66</v>
       </c>
@@ -2589,7 +2595,7 @@
       <c r="E41" s="26"/>
       <c r="F41" s="27"/>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" hidden="1">
       <c r="A42" s="5" t="s">
         <v>67</v>
       </c>
@@ -2603,7 +2609,7 @@
       <c r="E42" s="26"/>
       <c r="F42" s="27"/>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" hidden="1">
       <c r="A43" s="4" t="s">
         <v>69</v>
       </c>
@@ -2621,7 +2627,7 @@
       </c>
       <c r="F43" s="27"/>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" hidden="1">
       <c r="A44" s="11" t="s">
         <v>70</v>
       </c>
@@ -2635,7 +2641,7 @@
       <c r="E44" s="26"/>
       <c r="F44" s="27"/>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" hidden="1">
       <c r="A45" s="5" t="s">
         <v>71</v>
       </c>
@@ -2649,7 +2655,7 @@
       <c r="E45" s="26"/>
       <c r="F45" s="27"/>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" hidden="1">
       <c r="A46" s="5" t="s">
         <v>72</v>
       </c>
@@ -2663,7 +2669,7 @@
       <c r="E46" s="26"/>
       <c r="F46" s="27"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" hidden="1">
       <c r="A47" s="11" t="s">
         <v>73</v>
       </c>
@@ -2681,7 +2687,7 @@
       </c>
       <c r="F47" s="27"/>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" hidden="1">
       <c r="A48" s="10" t="s">
         <v>74</v>
       </c>
@@ -2695,7 +2701,7 @@
       <c r="E48" s="26"/>
       <c r="F48" s="27"/>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" hidden="1">
       <c r="A49" s="9" t="s">
         <v>75</v>
       </c>
@@ -2709,7 +2715,7 @@
       <c r="E49" s="26"/>
       <c r="F49" s="27"/>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" hidden="1">
       <c r="A50" s="6" t="s">
         <v>76</v>
       </c>
@@ -2727,7 +2733,7 @@
       </c>
       <c r="F50" s="27"/>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" hidden="1">
       <c r="A51" s="12" t="s">
         <v>77</v>
       </c>
@@ -2739,7 +2745,7 @@
       <c r="E51" s="26"/>
       <c r="F51" s="27"/>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" hidden="1">
       <c r="A52" s="8" t="s">
         <v>78</v>
       </c>
@@ -2757,7 +2763,7 @@
       </c>
       <c r="F52" s="27"/>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" hidden="1">
       <c r="A53" s="10" t="s">
         <v>79</v>
       </c>
@@ -2811,7 +2817,7 @@
       </c>
       <c r="F55" s="27"/>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" hidden="1">
       <c r="A56" s="8" t="s">
         <v>82</v>
       </c>
@@ -2825,7 +2831,7 @@
       <c r="E56" s="26"/>
       <c r="F56" s="27"/>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" hidden="1">
       <c r="A57" s="4" t="s">
         <v>83</v>
       </c>
@@ -2843,7 +2849,7 @@
       </c>
       <c r="F57" s="27"/>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" hidden="1">
       <c r="A58" s="11" t="s">
         <v>84</v>
       </c>
@@ -2857,7 +2863,7 @@
       <c r="E58" s="26"/>
       <c r="F58" s="27"/>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" hidden="1">
       <c r="A59" s="9" t="s">
         <v>85</v>
       </c>
@@ -2871,7 +2877,7 @@
       <c r="E59" s="26"/>
       <c r="F59" s="27"/>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" hidden="1">
       <c r="A60" s="15" t="s">
         <v>86</v>
       </c>
@@ -2885,7 +2891,7 @@
       <c r="E60" s="26"/>
       <c r="F60" s="27"/>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" hidden="1">
       <c r="A61" s="7" t="s">
         <v>87</v>
       </c>
@@ -2903,7 +2909,7 @@
       </c>
       <c r="F61" s="27"/>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" hidden="1">
       <c r="A62" s="15" t="s">
         <v>88</v>
       </c>
@@ -2921,7 +2927,7 @@
       </c>
       <c r="F62" s="27"/>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" hidden="1">
       <c r="A63" s="15" t="s">
         <v>89</v>
       </c>
@@ -2935,7 +2941,7 @@
       <c r="E63" s="26"/>
       <c r="F63" s="27"/>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" hidden="1">
       <c r="A64" s="14" t="s">
         <v>90</v>
       </c>
@@ -2953,7 +2959,7 @@
       </c>
       <c r="F64" s="27"/>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" hidden="1">
       <c r="A65" s="6" t="s">
         <v>91</v>
       </c>
@@ -2971,7 +2977,7 @@
       </c>
       <c r="F65" s="27"/>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" hidden="1">
       <c r="A66" s="9" t="s">
         <v>92</v>
       </c>
@@ -2985,7 +2991,7 @@
       <c r="E66" s="26"/>
       <c r="F66" s="27"/>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" hidden="1">
       <c r="A67" s="15" t="s">
         <v>93</v>
       </c>
@@ -2999,7 +3005,7 @@
       <c r="E67" s="26"/>
       <c r="F67" s="27"/>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" hidden="1">
       <c r="A68" s="11" t="s">
         <v>94</v>
       </c>
@@ -3013,7 +3019,7 @@
       <c r="E68" s="26"/>
       <c r="F68" s="27"/>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" hidden="1">
       <c r="A69" s="9" t="s">
         <v>95</v>
       </c>
@@ -3027,7 +3033,7 @@
       <c r="E69" s="26"/>
       <c r="F69" s="27"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" hidden="1">
       <c r="A70" s="9" t="s">
         <v>96</v>
       </c>
@@ -3041,7 +3047,7 @@
       <c r="E70" s="26"/>
       <c r="F70" s="27"/>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" hidden="1">
       <c r="A71" s="10" t="s">
         <v>97</v>
       </c>
@@ -3055,7 +3061,7 @@
       <c r="E71" s="26"/>
       <c r="F71" s="27"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" hidden="1">
       <c r="A72" s="6" t="s">
         <v>98</v>
       </c>
@@ -3073,7 +3079,7 @@
       </c>
       <c r="F72" s="27"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" hidden="1">
       <c r="A73" s="10" t="s">
         <v>99</v>
       </c>
@@ -3091,7 +3097,7 @@
       </c>
       <c r="F73" s="27"/>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" hidden="1">
       <c r="A74" s="14" t="s">
         <v>100</v>
       </c>
@@ -3105,7 +3111,7 @@
       <c r="E74" s="26"/>
       <c r="F74" s="27"/>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" hidden="1">
       <c r="A75" s="14" t="s">
         <v>101</v>
       </c>
@@ -3155,7 +3161,7 @@
       </c>
       <c r="F77" s="27"/>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" hidden="1">
       <c r="A78" s="5" t="s">
         <v>104</v>
       </c>
@@ -3169,7 +3175,7 @@
       <c r="E78" s="26"/>
       <c r="F78" s="27"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" hidden="1">
       <c r="A79" s="13" t="s">
         <v>105</v>
       </c>
@@ -3187,7 +3193,7 @@
       </c>
       <c r="F79" s="27"/>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" hidden="1">
       <c r="A80" s="14" t="s">
         <v>106</v>
       </c>
@@ -3205,7 +3211,7 @@
       </c>
       <c r="F80" s="27"/>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" hidden="1">
       <c r="A81" s="12" t="s">
         <v>107</v>
       </c>
@@ -3219,7 +3225,7 @@
       <c r="E81" s="26"/>
       <c r="F81" s="27"/>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" hidden="1">
       <c r="A82" s="12" t="s">
         <v>108</v>
       </c>
@@ -3237,7 +3243,7 @@
       </c>
       <c r="F82" s="27"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" hidden="1">
       <c r="A83" s="15" t="s">
         <v>109</v>
       </c>
@@ -3251,7 +3257,7 @@
       <c r="E83" s="26"/>
       <c r="F83" s="27"/>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" hidden="1">
       <c r="A84" s="15" t="s">
         <v>110</v>
       </c>
@@ -3265,7 +3271,7 @@
       <c r="E84" s="26"/>
       <c r="F84" s="27"/>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" hidden="1">
       <c r="A85" s="15" t="s">
         <v>111</v>
       </c>
@@ -3279,7 +3285,7 @@
       <c r="E85" s="26"/>
       <c r="F85" s="27"/>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" hidden="1">
       <c r="A86" s="13" t="s">
         <v>112</v>
       </c>
@@ -3297,7 +3303,7 @@
       </c>
       <c r="F86" s="27"/>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" hidden="1">
       <c r="A87" s="4" t="s">
         <v>113</v>
       </c>
@@ -3315,7 +3321,7 @@
       </c>
       <c r="F87" s="27"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" hidden="1">
       <c r="A88" s="12" t="s">
         <v>114</v>
       </c>
@@ -3347,7 +3353,7 @@
       </c>
       <c r="F89" s="27"/>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" hidden="1">
       <c r="A90" s="9" t="s">
         <v>116</v>
       </c>
@@ -3361,7 +3367,7 @@
       <c r="E90" s="26"/>
       <c r="F90" s="27"/>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" hidden="1">
       <c r="A91" s="8" t="s">
         <v>117</v>
       </c>
@@ -3373,7 +3379,7 @@
       <c r="E91" s="26"/>
       <c r="F91" s="27"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" hidden="1">
       <c r="A92" s="8" t="s">
         <v>118</v>
       </c>
@@ -3387,7 +3393,7 @@
       <c r="E92" s="26"/>
       <c r="F92" s="27"/>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" hidden="1">
       <c r="A93" s="13" t="s">
         <v>119</v>
       </c>
@@ -3405,7 +3411,7 @@
       </c>
       <c r="F93" s="27"/>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" hidden="1">
       <c r="A94" s="6" t="s">
         <v>120</v>
       </c>
@@ -3423,7 +3429,7 @@
       </c>
       <c r="F94" s="27"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" hidden="1">
       <c r="A95" s="6" t="s">
         <v>121</v>
       </c>
@@ -3441,7 +3447,7 @@
       </c>
       <c r="F95" s="27"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" hidden="1">
       <c r="A96" s="10" t="s">
         <v>122</v>
       </c>
@@ -3459,7 +3465,7 @@
       </c>
       <c r="F96" s="27"/>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" hidden="1">
       <c r="A97" s="8" t="s">
         <v>123</v>
       </c>
@@ -3477,7 +3483,7 @@
       </c>
       <c r="F97" s="27"/>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" hidden="1">
       <c r="A98" s="6" t="s">
         <v>124</v>
       </c>
@@ -3495,7 +3501,7 @@
       </c>
       <c r="F98" s="27"/>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" hidden="1">
       <c r="A99" s="8" t="s">
         <v>125</v>
       </c>
@@ -3509,7 +3515,7 @@
       <c r="E99" s="26"/>
       <c r="F99" s="27"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" hidden="1">
       <c r="A100" s="4" t="s">
         <v>126</v>
       </c>
@@ -3527,7 +3533,7 @@
       </c>
       <c r="F100" s="27"/>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" hidden="1">
       <c r="A101" s="10" t="s">
         <v>127</v>
       </c>
@@ -3541,7 +3547,7 @@
       <c r="E101" s="26"/>
       <c r="F101" s="27"/>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" hidden="1">
       <c r="A102" s="12" t="s">
         <v>128</v>
       </c>
@@ -3555,7 +3561,7 @@
       <c r="E102" s="26"/>
       <c r="F102" s="27"/>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" hidden="1">
       <c r="A103" s="15" t="s">
         <v>129</v>
       </c>
@@ -3569,7 +3575,7 @@
       <c r="E103" s="26"/>
       <c r="F103" s="27"/>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" hidden="1">
       <c r="A104" s="14" t="s">
         <v>130</v>
       </c>
@@ -3583,7 +3589,7 @@
       <c r="E104" s="26"/>
       <c r="F104" s="27"/>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" hidden="1">
       <c r="A105" s="13" t="s">
         <v>131</v>
       </c>
@@ -3601,7 +3607,7 @@
       </c>
       <c r="F105" s="27"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" hidden="1">
       <c r="A106" s="5" t="s">
         <v>132</v>
       </c>
@@ -3615,7 +3621,7 @@
       <c r="E106" s="26"/>
       <c r="F106" s="27"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" hidden="1">
       <c r="A107" s="12" t="s">
         <v>133</v>
       </c>
@@ -3629,7 +3635,7 @@
       <c r="E107" s="26"/>
       <c r="F107" s="27"/>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" hidden="1">
       <c r="A108" s="4" t="s">
         <v>134</v>
       </c>
@@ -3647,7 +3653,7 @@
       </c>
       <c r="F108" s="27"/>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" hidden="1">
       <c r="A109" s="10" t="s">
         <v>135</v>
       </c>
@@ -3665,7 +3671,7 @@
       </c>
       <c r="F109" s="27"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" hidden="1">
       <c r="A110" s="15" t="s">
         <v>136</v>
       </c>
@@ -3679,7 +3685,7 @@
       <c r="E110" s="26"/>
       <c r="F110" s="27"/>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" hidden="1">
       <c r="A111" s="11" t="s">
         <v>137</v>
       </c>
@@ -3697,7 +3703,7 @@
       </c>
       <c r="F111" s="27"/>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" hidden="1">
       <c r="A112" s="9" t="s">
         <v>138</v>
       </c>
@@ -3711,7 +3717,7 @@
       <c r="E112" s="26"/>
       <c r="F112" s="27"/>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" hidden="1">
       <c r="A113" s="13" t="s">
         <v>139</v>
       </c>
@@ -3729,7 +3735,7 @@
       </c>
       <c r="F113" s="27"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" hidden="1">
       <c r="A114" s="5" t="s">
         <v>140</v>
       </c>
@@ -3747,7 +3753,7 @@
       </c>
       <c r="F114" s="27"/>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" hidden="1">
       <c r="A115" s="7" t="s">
         <v>141</v>
       </c>
@@ -3775,11 +3781,15 @@
       <c r="C116" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D116" s="11"/>
-      <c r="E116" s="26"/>
+      <c r="D116" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E116" s="26">
+        <v>7</v>
+      </c>
       <c r="F116" s="27"/>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" hidden="1">
       <c r="A117" s="6" t="s">
         <v>143</v>
       </c>
@@ -3797,7 +3807,7 @@
       </c>
       <c r="F117" s="27"/>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" hidden="1">
       <c r="A118" s="11" t="s">
         <v>144</v>
       </c>
@@ -3811,7 +3821,7 @@
       <c r="E118" s="26"/>
       <c r="F118" s="27"/>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" hidden="1">
       <c r="A119" s="10" t="s">
         <v>145</v>
       </c>
@@ -3825,7 +3835,7 @@
       <c r="E119" s="26"/>
       <c r="F119" s="27"/>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" hidden="1">
       <c r="A120" s="4" t="s">
         <v>146</v>
       </c>
@@ -3843,7 +3853,7 @@
       </c>
       <c r="F120" s="27"/>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" hidden="1">
       <c r="A121" s="5" t="s">
         <v>147</v>
       </c>
@@ -3861,7 +3871,7 @@
       </c>
       <c r="F121" s="27"/>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" hidden="1">
       <c r="A122" s="15" t="s">
         <v>148</v>
       </c>
@@ -3875,7 +3885,7 @@
       <c r="E122" s="26"/>
       <c r="F122" s="27"/>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" hidden="1">
       <c r="A123" s="15" t="s">
         <v>149</v>
       </c>
@@ -3889,7 +3899,7 @@
       <c r="E123" s="26"/>
       <c r="F123" s="27"/>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" hidden="1">
       <c r="A124" s="13" t="s">
         <v>150</v>
       </c>
@@ -3907,7 +3917,7 @@
       </c>
       <c r="F124" s="27"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" hidden="1">
       <c r="A125" s="12" t="s">
         <v>151</v>
       </c>
@@ -3921,7 +3931,7 @@
       <c r="E125" s="26"/>
       <c r="F125" s="27"/>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" hidden="1">
       <c r="A126" s="8" t="s">
         <v>152</v>
       </c>
@@ -3939,7 +3949,7 @@
       </c>
       <c r="F126" s="27"/>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" hidden="1">
       <c r="A127" s="9" t="s">
         <v>153</v>
       </c>
@@ -3953,7 +3963,7 @@
       <c r="E127" s="26"/>
       <c r="F127" s="27"/>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" hidden="1">
       <c r="A128" s="4" t="s">
         <v>154</v>
       </c>
@@ -3971,7 +3981,7 @@
       </c>
       <c r="F128" s="27"/>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" hidden="1">
       <c r="A129" s="12" t="s">
         <v>155</v>
       </c>
@@ -3989,7 +3999,7 @@
       </c>
       <c r="F129" s="27"/>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" hidden="1">
       <c r="A130" s="10" t="s">
         <v>156</v>
       </c>
@@ -4007,7 +4017,7 @@
       </c>
       <c r="F130" s="27"/>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" hidden="1">
       <c r="A131" s="12" t="s">
         <v>157</v>
       </c>
@@ -4021,7 +4031,7 @@
       <c r="E131" s="26"/>
       <c r="F131" s="27"/>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" hidden="1">
       <c r="A132" s="14" t="s">
         <v>158</v>
       </c>
@@ -4035,7 +4045,7 @@
       <c r="E132" s="26"/>
       <c r="F132" s="27"/>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" hidden="1">
       <c r="A133" s="5" t="s">
         <v>159</v>
       </c>
@@ -4049,7 +4059,7 @@
       <c r="E133" s="26"/>
       <c r="F133" s="27"/>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" hidden="1">
       <c r="A134" s="12" t="s">
         <v>160</v>
       </c>
@@ -4063,7 +4073,7 @@
       <c r="E134" s="26"/>
       <c r="F134" s="27"/>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" hidden="1">
       <c r="A135" s="7" t="s">
         <v>161</v>
       </c>
@@ -4081,7 +4091,7 @@
       </c>
       <c r="F135" s="27"/>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" hidden="1">
       <c r="A136" s="11" t="s">
         <v>162</v>
       </c>
@@ -4095,7 +4105,7 @@
       <c r="E136" s="26"/>
       <c r="F136" s="27"/>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" hidden="1">
       <c r="A137" s="8" t="s">
         <v>163</v>
       </c>
@@ -4109,7 +4119,7 @@
       <c r="E137" s="26"/>
       <c r="F137" s="27"/>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" hidden="1">
       <c r="A138" s="7" t="s">
         <v>164</v>
       </c>
@@ -4127,7 +4137,7 @@
       </c>
       <c r="F138" s="27"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" hidden="1">
       <c r="A139" s="7" t="s">
         <v>165</v>
       </c>
@@ -4145,7 +4155,7 @@
       </c>
       <c r="F139" s="27"/>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" hidden="1">
       <c r="A140" s="5" t="s">
         <v>166</v>
       </c>
@@ -4159,7 +4169,7 @@
       <c r="E140" s="26"/>
       <c r="F140" s="27"/>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" hidden="1">
       <c r="A141" s="9" t="s">
         <v>167</v>
       </c>
@@ -4177,7 +4187,7 @@
       </c>
       <c r="F141" s="27"/>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" hidden="1">
       <c r="A142" s="9" t="s">
         <v>168</v>
       </c>
@@ -4191,7 +4201,7 @@
       <c r="E142" s="26"/>
       <c r="F142" s="27"/>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" hidden="1">
       <c r="A143" s="10" t="s">
         <v>169</v>
       </c>
@@ -4209,7 +4219,7 @@
       </c>
       <c r="F143" s="27"/>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" hidden="1">
       <c r="A144" s="11" t="s">
         <v>170</v>
       </c>
@@ -4227,7 +4237,7 @@
       </c>
       <c r="F144" s="27"/>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" hidden="1">
       <c r="A145" s="11" t="s">
         <v>171</v>
       </c>
@@ -4241,7 +4251,7 @@
       <c r="E145" s="26"/>
       <c r="F145" s="27"/>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" hidden="1">
       <c r="A146" s="9" t="s">
         <v>172</v>
       </c>
@@ -4255,7 +4265,7 @@
       <c r="E146" s="26"/>
       <c r="F146" s="27"/>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" hidden="1">
       <c r="A147" s="12" t="s">
         <v>173</v>
       </c>
@@ -4291,7 +4301,7 @@
       </c>
       <c r="F148" s="27"/>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" hidden="1">
       <c r="A149" s="7" t="s">
         <v>175</v>
       </c>
@@ -4309,7 +4319,7 @@
       </c>
       <c r="F149" s="27"/>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" hidden="1">
       <c r="A150" s="5" t="s">
         <v>176</v>
       </c>
@@ -4323,7 +4333,7 @@
       <c r="E150" s="26"/>
       <c r="F150" s="27"/>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" hidden="1">
       <c r="A151" s="15" t="s">
         <v>177</v>
       </c>
@@ -4337,7 +4347,7 @@
       <c r="E151" s="26"/>
       <c r="F151" s="27"/>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" hidden="1">
       <c r="A152" s="14" t="s">
         <v>178</v>
       </c>
@@ -4351,7 +4361,7 @@
       <c r="E152" s="26"/>
       <c r="F152" s="27"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" hidden="1">
       <c r="A153" s="14" t="s">
         <v>179</v>
       </c>
@@ -4369,7 +4379,7 @@
       </c>
       <c r="F153" s="27"/>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" hidden="1">
       <c r="A154" s="5" t="s">
         <v>180</v>
       </c>
@@ -4383,7 +4393,7 @@
       <c r="E154" s="26"/>
       <c r="F154" s="27"/>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" hidden="1">
       <c r="A155" s="7" t="s">
         <v>181</v>
       </c>
@@ -4401,7 +4411,7 @@
       </c>
       <c r="F155" s="27"/>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" hidden="1">
       <c r="A156" s="7" t="s">
         <v>182</v>
       </c>
@@ -4419,7 +4429,7 @@
       </c>
       <c r="F156" s="27"/>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" hidden="1">
       <c r="A157" s="9" t="s">
         <v>183</v>
       </c>
@@ -4433,7 +4443,7 @@
       <c r="E157" s="26"/>
       <c r="F157" s="27"/>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" hidden="1">
       <c r="A158" s="13" t="s">
         <v>184</v>
       </c>
@@ -4451,7 +4461,7 @@
       </c>
       <c r="F158" s="27"/>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" hidden="1">
       <c r="A159" s="7" t="s">
         <v>185</v>
       </c>
@@ -4469,7 +4479,7 @@
       </c>
       <c r="F159" s="27"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" hidden="1">
       <c r="A160" s="5" t="s">
         <v>186</v>
       </c>
@@ -4483,7 +4493,7 @@
       <c r="E160" s="26"/>
       <c r="F160" s="27"/>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" hidden="1">
       <c r="A161" s="6" t="s">
         <v>187</v>
       </c>
@@ -4519,7 +4529,7 @@
       </c>
       <c r="F162" s="27"/>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" hidden="1">
       <c r="A163" s="6" t="s">
         <v>189</v>
       </c>
@@ -4537,7 +4547,7 @@
       </c>
       <c r="F163" s="27"/>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" hidden="1">
       <c r="A164" s="4" t="s">
         <v>190</v>
       </c>
@@ -4555,7 +4565,7 @@
       </c>
       <c r="F164" s="27"/>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" hidden="1">
       <c r="A165" s="14" t="s">
         <v>191</v>
       </c>
@@ -4573,7 +4583,7 @@
       </c>
       <c r="F165" s="27"/>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" hidden="1">
       <c r="A166" s="9" t="s">
         <v>192</v>
       </c>
@@ -4591,7 +4601,7 @@
       </c>
       <c r="F166" s="27"/>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" hidden="1">
       <c r="A167" s="15" t="s">
         <v>193</v>
       </c>
@@ -4609,7 +4619,7 @@
       </c>
       <c r="F167" s="27"/>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" hidden="1">
       <c r="A168" s="5" t="s">
         <v>194</v>
       </c>
@@ -4623,7 +4633,7 @@
       <c r="E168" s="26"/>
       <c r="F168" s="27"/>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" hidden="1">
       <c r="A169" s="5" t="s">
         <v>195</v>
       </c>
@@ -4655,7 +4665,7 @@
       </c>
       <c r="F170" s="27"/>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" hidden="1">
       <c r="A171" s="10" t="s">
         <v>197</v>
       </c>
@@ -4673,7 +4683,7 @@
       </c>
       <c r="F171" s="27"/>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" hidden="1">
       <c r="A172" s="4" t="s">
         <v>198</v>
       </c>
@@ -4691,7 +4701,7 @@
       </c>
       <c r="F172" s="27"/>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" hidden="1">
       <c r="A173" s="5" t="s">
         <v>199</v>
       </c>
@@ -4705,7 +4715,7 @@
       <c r="E173" s="26"/>
       <c r="F173" s="27"/>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" hidden="1">
       <c r="A174" s="11" t="s">
         <v>200</v>
       </c>
@@ -4719,7 +4729,7 @@
       <c r="E174" s="26"/>
       <c r="F174" s="27"/>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" hidden="1">
       <c r="A175" s="13" t="s">
         <v>201</v>
       </c>
@@ -4737,7 +4747,7 @@
       </c>
       <c r="F175" s="27"/>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" hidden="1">
       <c r="A176" s="6" t="s">
         <v>202</v>
       </c>
@@ -4755,7 +4765,7 @@
       </c>
       <c r="F176" s="27"/>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" hidden="1">
       <c r="A177" s="11" t="s">
         <v>203</v>
       </c>
@@ -4769,7 +4779,7 @@
       <c r="E177" s="26"/>
       <c r="F177" s="27"/>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" hidden="1">
       <c r="A178" s="13" t="s">
         <v>204</v>
       </c>
@@ -4783,7 +4793,7 @@
       <c r="E178" s="26"/>
       <c r="F178" s="27"/>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" hidden="1">
       <c r="A179" s="15" t="s">
         <v>205</v>
       </c>
@@ -4819,7 +4829,7 @@
       </c>
       <c r="F180" s="27"/>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" hidden="1">
       <c r="A181" s="14" t="s">
         <v>207</v>
       </c>
@@ -6033,11 +6043,11 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>South Africa</v>
+        <v>Pakistan</v>
       </c>
       <c r="D15" s="3"/>
     </row>
@@ -6046,11 +6056,11 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>New Zealand</v>
+        <v>South Africa</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -6059,11 +6069,11 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>South Africa</v>
+        <v>New Zealand</v>
       </c>
       <c r="D17" s="3"/>
     </row>
@@ -6072,11 +6082,11 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>India</v>
+        <v>South Africa</v>
       </c>
       <c r="D18" s="3"/>
     </row>
@@ -6084,10 +6094,12 @@
       <c r="A19" s="3">
         <v>14</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C19" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v/>
+        <v>India</v>
       </c>
       <c r="D19" s="3"/>
     </row>

--- a/dwl-fantasy-platform/backend/WWC_Config.xlsx
+++ b/dwl-fantasy-platform/backend/WWC_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kishan/Downloads/Delulu Leagues/DWL Delulu Women's League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{892421C0-D99D-4573-B068-428FA91966A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B058914F-5528-4256-BD0F-552B59F8E1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="8" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="232">
   <si>
     <t>Player Name</t>
   </si>
@@ -61,6 +61,9 @@
     <t>Sold Price</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Alana King</t>
   </si>
   <si>
@@ -484,6 +487,9 @@
     <t>Scotland</t>
   </si>
   <si>
+    <t>Injured</t>
+  </si>
+  <si>
     <t>Ailsa Lister</t>
   </si>
   <si>
@@ -494,6 +500,12 @@
   </si>
   <si>
     <t>Gabriella Fontenla</t>
+  </si>
+  <si>
+    <t>Hannah Rainey</t>
+  </si>
+  <si>
+    <t>Replacement</t>
   </si>
   <si>
     <t>Katherine Fraser</t>
@@ -1021,7 +1033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1071,6 +1083,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1092,14 +1110,15 @@
     <xf numFmtId="0" fontId="14" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="53">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1139,6 +1158,10 @@
           <bgColor rgb="FFD4B631"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1183,6 +1206,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1208,6 +1235,10 @@
           <bgColor rgb="FFF5D37A"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1252,6 +1283,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1293,6 +1328,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1331,6 +1370,10 @@
           <bgColor rgb="FFFAEBC8"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1399,6 +1442,26 @@
       </font>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center"/>
     </dxf>
@@ -1430,17 +1493,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}" name="WWC_Players_All" displayName="WWC_Players_All" ref="A1:E181" totalsRowShown="0">
-  <autoFilter ref="A1:E181" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E181">
-    <sortCondition ref="C1:C181"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}" name="WWC_Players_All" displayName="WWC_Players_All" ref="A1:F182" totalsRowShown="0">
+  <autoFilter ref="A1:F182" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E182">
+    <sortCondition ref="C1:C182"/>
   </sortState>
-  <tableColumns count="5">
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9375827B-7F58-154E-8A6D-89BE21277304}" name="Player Name"/>
     <tableColumn id="2" xr3:uid="{F0A76870-728A-A74E-B950-90FF8E0725ED}" name="Role"/>
     <tableColumn id="3" xr3:uid="{3BB180DF-A277-B143-96FC-14A3A8D2DBBE}" name="Country"/>
     <tableColumn id="4" xr3:uid="{443289CA-3294-5145-B407-E557FD9FF3E7}" name="DWL Team"/>
-    <tableColumn id="5" xr3:uid="{75621D58-A8A6-4E62-BDA9-66A239157A91}" name="Sold Price" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{75621D58-A8A6-4E62-BDA9-66A239157A91}" name="Sold Price" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{085904BA-F0EF-4E5D-A886-B7C3DE1C35BF}" name="Status" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1454,133 +1518,154 @@
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{2002ACC4-D887-2C44-9678-BD7731D9CCFA}" name="Abbrv"/>
-    <tableColumn id="2" xr3:uid="{2DFF7EF3-7DF4-7D43-861B-67FB1F8F4D9E}" name="Team Name" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{2DFF7EF3-7DF4-7D43-861B-67FB1F8F4D9E}" name="Team Name" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}" name="BL" displayName="BL" ref="A5:D23" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41" tableBorderDxfId="40">
-  <autoFilter ref="A5:D23" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}" name="GD" displayName="GD" ref="A5:E23" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48" tableBorderDxfId="47">
+  <autoFilter ref="A5:E23" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{08FE8A15-D3B6-DF4B-88B3-A051E62A20E6}" name="Team Player No." dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{4ECD4789-FFEE-F647-8611-EA766F1EEB38}" name="Player Name" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{E23434DC-5066-554A-A1F3-30A49F38C773}" name="Country" dataDxfId="37">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{08FE8A15-D3B6-DF4B-88B3-A051E62A20E6}" name="Team Player No." dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{4ECD4789-FFEE-F647-8611-EA766F1EEB38}" name="Player Name" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{E23434DC-5066-554A-A1F3-30A49F38C773}" name="Country" dataDxfId="44">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B716E680-D978-7440-AE9C-6B18870AC674}" name="Captain/ Vice-Captain" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{B716E680-D978-7440-AE9C-6B18870AC674}" name="Captain/ Vice-Captain" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{F7B09C99-8D55-4A36-BDE6-081088F33D6B}" name="Status" dataDxfId="42">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{BA0A3757-C1BF-6F4E-8593-2BAF45FE9FDE}" name="NR" displayName="NR" ref="A5:D23" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
-  <autoFilter ref="A5:D23" xr:uid="{BA0A3757-C1BF-6F4E-8593-2BAF45FE9FDE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{BA0A3757-C1BF-6F4E-8593-2BAF45FE9FDE}" name="JR" displayName="JR" ref="A5:E23" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+  <autoFilter ref="A5:E23" xr:uid="{BA0A3757-C1BF-6F4E-8593-2BAF45FE9FDE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9685E0E1-CFC1-4D4C-9DA8-9D0D67FFF359}" name="Team Player No." dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{4127652B-4321-704E-8135-B6E29F440927}" name="Player Name" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{7E01B81D-BAB5-574F-BBB7-719FC4E16DC4}" name="Country" dataDxfId="31">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{9685E0E1-CFC1-4D4C-9DA8-9D0D67FFF359}" name="Team Player No." dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{4127652B-4321-704E-8135-B6E29F440927}" name="Player Name" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{7E01B81D-BAB5-574F-BBB7-719FC4E16DC4}" name="Country" dataDxfId="37">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0C3C6BB9-DD76-DD4A-97EF-189E0310831A}" name="Captain/ Vice-Captain" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{0C3C6BB9-DD76-DD4A-97EF-189E0310831A}" name="Captain/ Vice-Captain" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{FF728CA9-5A84-4ADA-8803-4CD4F59AFA8E}" name="Status" dataDxfId="35">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}" name="MB" displayName="MB" ref="A5:D23" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A5:D23" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}" name="KQ" displayName="KQ" ref="A5:E23" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+  <autoFilter ref="A5:E23" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0D27ED80-3738-7F47-94AF-0A6B61961EB3}" name="Team Player No." dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{267FF8CD-F86C-DE4D-922E-8D12B710755E}" name="Player Name" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{20C938BF-DCD0-1941-ACC8-F620B1FDFF4A}" name="Country" dataDxfId="25">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{0D27ED80-3738-7F47-94AF-0A6B61961EB3}" name="Team Player No." dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{267FF8CD-F86C-DE4D-922E-8D12B710755E}" name="Player Name" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{20C938BF-DCD0-1941-ACC8-F620B1FDFF4A}" name="Country" dataDxfId="30">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BC210CBE-A244-1A47-9738-6D3C52D2F342}" name="Captain/ Vice-Captain" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{BC210CBE-A244-1A47-9738-6D3C52D2F342}" name="Captain/ Vice-Captain" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{CB9E0E92-B905-4960-84CA-9CDD10473379}" name="Status" dataDxfId="28">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{695645B6-531C-9947-BD49-AB7DD4777E06}" name="RR" displayName="RR" ref="A5:D23" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
-  <autoFilter ref="A5:D23" xr:uid="{695645B6-531C-9947-BD49-AB7DD4777E06}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{695645B6-531C-9947-BD49-AB7DD4777E06}" name="RR" displayName="RR" ref="A5:E23" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A5:E23" xr:uid="{695645B6-531C-9947-BD49-AB7DD4777E06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{234B9EE4-D33E-1447-BB49-68C355C76983}" name="Team Player No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{F46522FB-98C6-BD44-8237-8D453678EEE8}" name="Player Name" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{420600D5-2F08-1849-A91C-2F03DFE81977}" name="Country" dataDxfId="19">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{234B9EE4-D33E-1447-BB49-68C355C76983}" name="Team Player No." dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{F46522FB-98C6-BD44-8237-8D453678EEE8}" name="Player Name" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{420600D5-2F08-1849-A91C-2F03DFE81977}" name="Country" dataDxfId="23">
       <calculatedColumnFormula>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F0D8CC44-F2B1-B443-B44A-5AE8610B9D3B}" name="Captain/ Vice-Captain" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{F0D8CC44-F2B1-B443-B44A-5AE8610B9D3B}" name="Captain/ Vice-Captain" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{517E5FAB-EF90-44E4-A11D-B492670D7D75}" name="Status" dataDxfId="21">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{649331E8-BE4C-7A4A-8F63-4638AD1C1FDD}" name="KKR" displayName="KKR" ref="A5:D23" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A5:D23" xr:uid="{649331E8-BE4C-7A4A-8F63-4638AD1C1FDD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{649331E8-BE4C-7A4A-8F63-4638AD1C1FDD}" name="SS" displayName="SS" ref="A5:E23" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A5:E23" xr:uid="{649331E8-BE4C-7A4A-8F63-4638AD1C1FDD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{31A5AA7F-D358-494F-8889-0D3934B9DF61}" name="Team Player No." dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{196D6C69-3CAF-0A44-BF6D-64F1AC14B9D2}" name="Player Name" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{9DCA5DAF-0152-FA41-87A0-FBE7254C3CCC}" name="Country" dataDxfId="13">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{31A5AA7F-D358-494F-8889-0D3934B9DF61}" name="Team Player No." dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{196D6C69-3CAF-0A44-BF6D-64F1AC14B9D2}" name="Player Name" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{9DCA5DAF-0152-FA41-87A0-FBE7254C3CCC}" name="Country" dataDxfId="16">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E65D1282-79BC-3640-9D14-2CB9941E7D9C}" name="Captain/ Vice-Captain" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{E65D1282-79BC-3640-9D14-2CB9941E7D9C}" name="Captain/ Vice-Captain" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{86BDAD13-D9A5-4591-8814-2EE9356EAAA3}" name="Status" dataDxfId="14">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FF09F066-F6AA-4643-AA12-841C9478CEE4}" name="CT" displayName="CT" ref="A5:D23" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A5:D23" xr:uid="{FF09F066-F6AA-4643-AA12-841C9478CEE4}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FF09F066-F6AA-4643-AA12-841C9478CEE4}" name="SGS" displayName="SGS" ref="A5:E23" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A5:E23" xr:uid="{FF09F066-F6AA-4643-AA12-841C9478CEE4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:E23">
     <sortCondition ref="B5:B23"/>
   </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{74BA643C-B079-8B4F-8344-2C9B9BC12707}" name="Team Player No." dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{432B80D9-19D7-AF43-AB9E-82D1257517E4}" name="Player Name" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{AA077A69-6CDA-934A-8174-723FA3593002}" name="Country" dataDxfId="7">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{74BA643C-B079-8B4F-8344-2C9B9BC12707}" name="Team Player No." dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{432B80D9-19D7-AF43-AB9E-82D1257517E4}" name="Player Name" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{AA077A69-6CDA-934A-8174-723FA3593002}" name="Country" dataDxfId="9">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3A3DF73D-E88E-1644-A4F0-7B6F72118B2E}" name="Captain/ Vice-Captain" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{3A3DF73D-E88E-1644-A4F0-7B6F72118B2E}" name="Captain/ Vice-Captain" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{9CF9114D-3B1F-4C9E-91B8-639A688B3C9E}" name="Status" dataDxfId="7">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D2D09985-BEF9-0242-9733-F0E6C95B1A50}" name="KT" displayName="KT" ref="A5:D23" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A5:D23" xr:uid="{D2D09985-BEF9-0242-9733-F0E6C95B1A50}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D2D09985-BEF9-0242-9733-F0E6C95B1A50}" name="KT" displayName="KT" ref="A5:E23" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A5:E23" xr:uid="{D2D09985-BEF9-0242-9733-F0E6C95B1A50}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
     <sortCondition ref="B5:B23"/>
   </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8DD4A9BF-D7CC-1249-82C8-0D9C5B5EC365}" name="Team Player No." dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{6C7C94F0-116B-6E4D-A181-898044122E61}" name="Player Name" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{0F8DB46C-16CD-4540-821F-2B7FB0541A01}" name="Country" dataDxfId="1">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{8DD4A9BF-D7CC-1249-82C8-0D9C5B5EC365}" name="Team Player No." dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{6C7C94F0-116B-6E4D-A181-898044122E61}" name="Player Name" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{0F8DB46C-16CD-4540-821F-2B7FB0541A01}" name="Country" dataDxfId="2">
       <calculatedColumnFormula>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{611FC6FE-DC81-EB47-AEEC-56717395E657}" name="Captain/ Vice-Captain" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{611FC6FE-DC81-EB47-AEEC-56717395E657}" name="Captain/ Vice-Captain" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{07CD9CAF-C77E-4876-99E1-873F5AB8D139}" name="Status" dataDxfId="0">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1903,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7675FD65-5A90-8049-AA35-694183767B48}">
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
@@ -1930,19 +2015,22 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="25">
         <v>14.5</v>
@@ -1951,16 +2039,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="25">
         <v>13.5</v>
@@ -1969,16 +2057,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="25">
         <v>25</v>
@@ -1987,16 +2075,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="25">
         <v>18</v>
@@ -2005,16 +2093,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="25">
         <v>27.5</v>
@@ -2023,16 +2111,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="25">
         <v>4</v>
@@ -2041,16 +2129,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="E8" s="25">
         <v>4</v>
@@ -2059,16 +2147,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="25">
         <v>5</v>
@@ -2077,16 +2165,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="25">
         <v>7.5</v>
@@ -2095,16 +2183,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="E11" s="25">
         <v>0.5</v>
@@ -2113,16 +2201,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="25">
         <v>14.5</v>
@@ -2131,16 +2219,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" s="25">
         <v>2.5</v>
@@ -2149,16 +2237,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" s="25">
         <v>13</v>
@@ -2167,16 +2255,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="25">
         <v>5</v>
@@ -2185,16 +2273,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16" s="25">
         <v>10.5</v>
@@ -2203,13 +2291,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="25"/>
@@ -2217,13 +2305,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="25"/>
@@ -2231,13 +2319,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="25"/>
@@ -2245,13 +2333,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="25"/>
@@ -2259,13 +2347,13 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="25"/>
@@ -2273,16 +2361,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" s="25">
         <v>1</v>
@@ -2291,16 +2379,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" s="25">
         <v>1</v>
@@ -2309,13 +2397,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="25"/>
@@ -2323,13 +2411,13 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="25"/>
@@ -2337,13 +2425,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="25"/>
@@ -2351,13 +2439,13 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="25"/>
@@ -2365,13 +2453,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="25"/>
@@ -2379,13 +2467,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="25"/>
@@ -2393,13 +2481,13 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="25"/>
@@ -2407,13 +2495,13 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="25"/>
@@ -2421,16 +2509,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E32" s="25">
         <v>16</v>
@@ -2439,16 +2527,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="D33" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33" s="25">
         <v>9</v>
@@ -2457,16 +2545,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34" s="25">
         <v>13</v>
@@ -2475,13 +2563,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="25"/>
@@ -2489,16 +2577,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" s="25">
         <v>9</v>
@@ -2507,16 +2595,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E37" s="25">
         <v>1</v>
@@ -2525,16 +2613,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E38" s="25">
         <v>4</v>
@@ -2543,16 +2631,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E39" s="25">
         <v>2</v>
@@ -2561,16 +2649,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E40" s="25">
         <v>19</v>
@@ -2579,16 +2667,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E41" s="25">
         <v>1</v>
@@ -2597,16 +2685,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E42" s="25">
         <v>3</v>
@@ -2615,16 +2703,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E43" s="25">
         <v>37</v>
@@ -2633,16 +2721,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E44" s="25">
         <v>6</v>
@@ -2651,16 +2739,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E45" s="25">
         <v>21.5</v>
@@ -2669,16 +2757,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E46" s="25">
         <v>0.5</v>
@@ -2687,16 +2775,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E47" s="25">
         <v>5</v>
@@ -2705,16 +2793,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="D48" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48" s="25">
         <v>0.5</v>
@@ -2723,16 +2811,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E49" s="25">
         <v>21.5</v>
@@ -2741,16 +2829,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E50" s="25">
         <v>21.5</v>
@@ -2759,16 +2847,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E51" s="25">
         <v>15</v>
@@ -2777,16 +2865,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E52" s="25">
         <v>0.5</v>
@@ -2795,16 +2883,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E53" s="25">
         <v>0.5</v>
@@ -2813,16 +2901,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E54" s="25">
         <v>15.5</v>
@@ -2831,16 +2919,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E55" s="25">
         <v>13</v>
@@ -2849,16 +2937,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E56" s="25">
         <v>25</v>
@@ -2867,16 +2955,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E57" s="25">
         <v>14.5</v>
@@ -2885,16 +2973,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E58" s="25">
         <v>0.5</v>
@@ -2903,16 +2991,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E59" s="25">
         <v>3</v>
@@ -2921,16 +3009,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E60" s="25">
         <v>18.5</v>
@@ -2939,16 +3027,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E61" s="25">
         <v>13.5</v>
@@ -2957,13 +3045,13 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="25"/>
@@ -2971,13 +3059,13 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="25"/>
@@ -2985,16 +3073,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E64" s="25">
         <v>4.5</v>
@@ -3003,13 +3091,13 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="25"/>
@@ -3017,13 +3105,13 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="25"/>
@@ -3031,16 +3119,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" s="25">
         <v>0.5</v>
@@ -3049,13 +3137,13 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="25"/>
@@ -3063,16 +3151,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E69" s="25">
         <v>6</v>
@@ -3081,13 +3169,13 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D70" s="8"/>
       <c r="E70" s="25"/>
@@ -3095,11 +3183,11 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="25"/>
@@ -3107,13 +3195,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D72" s="8"/>
       <c r="E72" s="25"/>
@@ -3121,16 +3209,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E73" s="25">
         <v>0.5</v>
@@ -3139,13 +3227,13 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="25"/>
@@ -3153,16 +3241,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E75" s="25">
         <v>9.5</v>
@@ -3171,13 +3259,13 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D76" s="8"/>
       <c r="E76" s="25"/>
@@ -3185,13 +3273,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="25"/>
@@ -3199,13 +3287,13 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>97</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="25"/>
@@ -3213,13 +3301,13 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="25"/>
@@ -3227,13 +3315,13 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="25"/>
@@ -3241,13 +3329,13 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="25"/>
@@ -3255,13 +3343,13 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="25"/>
@@ -3269,13 +3357,13 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="25"/>
@@ -3283,13 +3371,13 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="25"/>
@@ -3297,13 +3385,13 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="25"/>
@@ -3311,13 +3399,13 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="25"/>
@@ -3325,16 +3413,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E87" s="25">
         <v>1</v>
@@ -3343,13 +3431,13 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="25"/>
@@ -3357,13 +3445,13 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D89" s="9"/>
       <c r="E89" s="25"/>
@@ -3371,13 +3459,13 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D90" s="9"/>
       <c r="E90" s="25"/>
@@ -3385,16 +3473,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E91" s="25">
         <v>1</v>
@@ -3403,16 +3491,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E92" s="25">
         <v>1</v>
@@ -3421,16 +3509,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B93" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>113</v>
-      </c>
       <c r="D93" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E93" s="25">
         <v>1</v>
@@ -3439,13 +3527,13 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D94" s="10"/>
       <c r="E94" s="25"/>
@@ -3453,16 +3541,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E95" s="25">
         <v>1</v>
@@ -3471,13 +3559,13 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D96" s="10"/>
       <c r="E96" s="25"/>
@@ -3485,16 +3573,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E97" s="25">
         <v>1</v>
@@ -3503,16 +3591,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E98" s="25">
         <v>6</v>
@@ -3521,16 +3609,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E99" s="25">
         <v>10.5</v>
@@ -3539,13 +3627,13 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D100" s="10"/>
       <c r="E100" s="25"/>
@@ -3553,16 +3641,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E101" s="25">
         <v>40</v>
@@ -3571,13 +3659,13 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D102" s="10"/>
       <c r="E102" s="25"/>
@@ -3585,16 +3673,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E103" s="25">
         <v>1</v>
@@ -3603,16 +3691,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E104" s="25">
         <v>2</v>
@@ -3621,16 +3709,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E105" s="25">
         <v>13</v>
@@ -3639,16 +3727,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E106" s="25">
         <v>13</v>
@@ -3657,13 +3745,13 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D107" s="11"/>
       <c r="E107" s="25"/>
@@ -3671,16 +3759,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C108" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B108" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>129</v>
-      </c>
       <c r="D108" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E108" s="25">
         <v>1</v>
@@ -3689,13 +3777,13 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D109" s="11"/>
       <c r="E109" s="25"/>
@@ -3703,13 +3791,13 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D110" s="11"/>
       <c r="E110" s="25"/>
@@ -3717,16 +3805,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E111" s="25">
         <v>8</v>
@@ -3735,13 +3823,13 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D112" s="11"/>
       <c r="E112" s="25"/>
@@ -3749,13 +3837,13 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D113" s="11"/>
       <c r="E113" s="25"/>
@@ -3763,16 +3851,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E114" s="25">
         <v>2</v>
@@ -3781,16 +3869,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E115" s="25">
         <v>7</v>
@@ -3799,13 +3887,13 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D116" s="11"/>
       <c r="E116" s="25"/>
@@ -3813,13 +3901,13 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D117" s="11"/>
       <c r="E117" s="25"/>
@@ -3827,16 +3915,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E118" s="25">
         <v>9.5</v>
@@ -3845,13 +3933,13 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D119" s="11"/>
       <c r="E119" s="25"/>
@@ -3859,13 +3947,13 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D120" s="11"/>
       <c r="E120" s="25"/>
@@ -3873,13 +3961,13 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D121" s="11"/>
       <c r="E121" s="25"/>
@@ -3887,31 +3975,33 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E122" s="25">
         <v>2</v>
       </c>
-      <c r="F122" s="26"/>
+      <c r="F122" s="26" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="B123" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C123" s="12" t="s">
-        <v>145</v>
       </c>
       <c r="D123" s="12"/>
       <c r="E123" s="25"/>
@@ -3919,13 +4009,13 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D124" s="12"/>
       <c r="E124" s="25"/>
@@ -3933,13 +4023,13 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D125" s="12"/>
       <c r="E125" s="25"/>
@@ -3947,11 +4037,11 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B126" s="12"/>
       <c r="C126" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D126" s="12"/>
       <c r="E126" s="25"/>
@@ -3959,59 +4049,65 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D127" s="12"/>
-      <c r="E127" s="25"/>
-      <c r="F127" s="26"/>
+        <v>146</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="25">
+        <v>0</v>
+      </c>
+      <c r="F127" s="26" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D128" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E128" s="25">
-        <v>8.5</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="D128" s="12"/>
+      <c r="E128" s="25"/>
       <c r="F128" s="26"/>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D129" s="12"/>
-      <c r="E129" s="25"/>
+        <v>146</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E129" s="25">
+        <v>8.5</v>
+      </c>
       <c r="F129" s="26"/>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D130" s="12"/>
       <c r="E130" s="25"/>
@@ -4019,13 +4115,13 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D131" s="12"/>
       <c r="E131" s="25"/>
@@ -4033,13 +4129,13 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D132" s="12"/>
       <c r="E132" s="25"/>
@@ -4047,45 +4143,45 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D133" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E133" s="25">
-        <v>0.5</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="D133" s="12"/>
+      <c r="E133" s="25"/>
       <c r="F133" s="26"/>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D134" s="12"/>
-      <c r="E134" s="25"/>
+        <v>146</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="25">
+        <v>0.5</v>
+      </c>
       <c r="F134" s="26"/>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D135" s="12"/>
       <c r="E135" s="25"/>
@@ -4093,361 +4189,361 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D136" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E136" s="25">
+        <v>146</v>
+      </c>
+      <c r="D136" s="12"/>
+      <c r="E136" s="25"/>
+      <c r="F136" s="26"/>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" s="25">
         <v>2</v>
-      </c>
-      <c r="F136" s="26"/>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="B137" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C137" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E137" s="25">
-        <v>4.5</v>
       </c>
       <c r="F137" s="26"/>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E138" s="25">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="F138" s="26"/>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E139" s="25">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="F139" s="26"/>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E140" s="25">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="F140" s="26"/>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B141" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B141" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C141" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="D141" s="13" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E141" s="25">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F141" s="26"/>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E142" s="25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F142" s="26"/>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E143" s="25">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F143" s="26"/>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E144" s="25">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="F144" s="26"/>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E145" s="25">
-        <v>8.5</v>
+        <v>20.5</v>
       </c>
       <c r="F145" s="26"/>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E146" s="25">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="F146" s="26"/>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E147" s="25">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F147" s="26"/>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B148" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E148" s="25">
         <v>14</v>
-      </c>
-      <c r="C148" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E148" s="25">
-        <v>1</v>
       </c>
       <c r="F148" s="26"/>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E149" s="25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F149" s="26"/>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E150" s="25">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="F150" s="26"/>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D151" s="13"/>
-      <c r="E151" s="25"/>
+        <v>165</v>
+      </c>
+      <c r="D151" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E151" s="25">
+        <v>6.5</v>
+      </c>
       <c r="F151" s="26"/>
     </row>
     <row r="152" spans="1:6">
-      <c r="A152" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="B152" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C152" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D152" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E152" s="25">
-        <v>10</v>
-      </c>
+      <c r="A152" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B152" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D152" s="13"/>
+      <c r="E152" s="25"/>
       <c r="F152" s="26"/>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D153" s="15"/>
-      <c r="E153" s="25"/>
+        <v>181</v>
+      </c>
+      <c r="D153" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E153" s="25">
+        <v>10</v>
+      </c>
       <c r="F153" s="26"/>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D154" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E154" s="25">
-        <v>1</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="D154" s="15"/>
+      <c r="E154" s="25"/>
       <c r="F154" s="26"/>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D155" s="15"/>
-      <c r="E155" s="25"/>
+        <v>181</v>
+      </c>
+      <c r="D155" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="25">
+        <v>1</v>
+      </c>
       <c r="F155" s="26"/>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B156" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C156" s="15" t="s">
         <v>181</v>
-      </c>
-      <c r="B156" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C156" s="15" t="s">
-        <v>177</v>
       </c>
       <c r="D156" s="15"/>
       <c r="E156" s="25"/>
@@ -4455,13 +4551,13 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="15" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D157" s="15"/>
       <c r="E157" s="25"/>
@@ -4469,13 +4565,13 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D158" s="15"/>
       <c r="E158" s="25"/>
@@ -4483,13 +4579,13 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D159" s="15"/>
       <c r="E159" s="25"/>
@@ -4497,13 +4593,13 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D160" s="15"/>
       <c r="E160" s="25"/>
@@ -4511,13 +4607,13 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="15" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D161" s="15"/>
       <c r="E161" s="25"/>
@@ -4525,13 +4621,13 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="15" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D162" s="15"/>
       <c r="E162" s="25"/>
@@ -4539,13 +4635,13 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D163" s="15"/>
       <c r="E163" s="25"/>
@@ -4553,13 +4649,13 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D164" s="15"/>
       <c r="E164" s="25"/>
@@ -4567,167 +4663,167 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D165" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E165" s="25">
-        <v>1</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="D165" s="15"/>
+      <c r="E165" s="25"/>
       <c r="F165" s="26"/>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E166" s="25">
+        <v>1</v>
+      </c>
+      <c r="F166" s="26"/>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="B167" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C167" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D167" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E167" s="25">
         <v>2</v>
-      </c>
-      <c r="F166" s="26"/>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="B167" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C167" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D167" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E167" s="25">
-        <v>1</v>
       </c>
       <c r="F167" s="26"/>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E168" s="25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F168" s="26"/>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="14" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D169" s="14"/>
-      <c r="E169" s="25"/>
+        <v>197</v>
+      </c>
+      <c r="D169" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E169" s="25">
+        <v>10</v>
+      </c>
       <c r="F169" s="26"/>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D170" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E170" s="25">
-        <v>3.5</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="D170" s="14"/>
+      <c r="E170" s="25"/>
       <c r="F170" s="26"/>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B171" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B171" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C171" s="14" t="s">
-        <v>193</v>
-      </c>
       <c r="D171" s="14" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E171" s="25">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="F171" s="26"/>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E172" s="25">
-        <v>18.5</v>
+        <v>9</v>
       </c>
       <c r="F172" s="26"/>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D173" s="14"/>
-      <c r="E173" s="25"/>
+        <v>197</v>
+      </c>
+      <c r="D173" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E173" s="25">
+        <v>18.5</v>
+      </c>
       <c r="F173" s="26"/>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D174" s="14"/>
       <c r="E174" s="25"/>
@@ -4735,45 +4831,45 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B175" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D175" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E175" s="25">
-        <v>3</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="D175" s="14"/>
+      <c r="E175" s="25"/>
       <c r="F175" s="26"/>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="14" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B176" s="14" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D176" s="14"/>
-      <c r="E176" s="25"/>
+        <v>197</v>
+      </c>
+      <c r="D176" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="25">
+        <v>3</v>
+      </c>
       <c r="F176" s="26"/>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="14" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D177" s="14"/>
       <c r="E177" s="25"/>
@@ -4781,13 +4877,13 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="14" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D178" s="14"/>
       <c r="E178" s="25"/>
@@ -4795,61 +4891,75 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E179" s="25">
-        <v>2</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="D179" s="14"/>
+      <c r="E179" s="25"/>
       <c r="F179" s="26"/>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E180" s="25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F180" s="26"/>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B181" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D181" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" s="25">
         <v>6</v>
       </c>
-      <c r="C181" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D181" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E181" s="25">
+      <c r="F181" s="26"/>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B182" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C182" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D182" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E182" s="25">
         <v>1</v>
       </c>
-      <c r="F181" s="26"/>
-    </row>
-    <row r="182" spans="1:6"/>
+      <c r="F182" s="26"/>
+    </row>
     <row r="183" spans="1:6"/>
     <row r="184" spans="1:6"/>
+    <row r="185" spans="1:6"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4862,7 +4972,7 @@
           <x14:formula1>
             <xm:f>DWLTeams!$B$2:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D181</xm:sqref>
+          <xm:sqref>D2:D182</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4880,66 +4990,66 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75">
       <c r="A8" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75">
@@ -4964,7 +5074,7 @@
   <sheetPr>
     <tabColor rgb="FF008080"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -4973,29 +5083,33 @@
     <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-    </row>
-    <row r="5" spans="1:4">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75"/>
+    <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="20" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>0</v>
@@ -5004,248 +5118,323 @@
         <v>2</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>223</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="23" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>224</v>
+      </c>
+      <c r="E6" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75">
+      <c r="E8" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>West Indies</v>
       </c>
       <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Pakistan</v>
       </c>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C11" s="23" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>225</v>
+      </c>
+      <c r="E12" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Bangladesh</v>
       </c>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Bangladesh</v>
       </c>
       <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Scotland</v>
       </c>
       <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Scotland</v>
       </c>
       <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
+      <c r="E20" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Netherlands</v>
       </c>
       <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
+      <c r="E21" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
+      <c r="E22" s="23">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="23" t="str">
-        <f>IFERROR(VLOOKUP(BL[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D23" s="3"/>
+      <c r="E23" s="23" t="str">
+        <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="A1:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{F8FBDCC3-3111-DC4E-AF01-A0FD07E86895}">
@@ -5261,7 +5450,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D030090-5C0F-BA4C-AA19-0E80536C4120}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
+            <xm:f>Players!$A$2:$A$182</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -5276,7 +5465,7 @@
   <sheetPr>
     <tabColor rgb="FF301934"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -5285,29 +5474,33 @@
     <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75"/>
+    <row r="5" spans="1:5" ht="15.75">
+      <c r="A5" s="19" t="s">
         <v>222</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75">
-      <c r="A5" s="19" t="s">
-        <v>218</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>0</v>
@@ -5316,246 +5509,321 @@
         <v>2</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75">
+        <v>223</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>West Indies</v>
       </c>
       <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75">
+      <c r="E6" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>West Indies</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75">
+        <v>224</v>
+      </c>
+      <c r="E7" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75">
+      <c r="E8" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75">
+      <c r="E9" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Scotland</v>
       </c>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.75">
+      <c r="E10" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75">
+      <c r="E11" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75">
+      <c r="E12" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75">
+      <c r="E13" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Pakistan</v>
       </c>
       <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75">
+      <c r="E14" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="23" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75">
+        <v>225</v>
+      </c>
+      <c r="E15" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Netherlands</v>
       </c>
       <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.75">
+      <c r="E16" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Sri Lanka</v>
       </c>
       <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.75">
+      <c r="E17" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.75">
+      <c r="E18" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.75">
+      <c r="E19" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C20" s="23" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Sri Lanka</v>
       </c>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
+      <c r="E20" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C21" s="23" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>West Indies</v>
       </c>
       <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
+      <c r="E21" s="3">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
+      <c r="E22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(NR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D23" s="3"/>
+      <c r="E23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="A1:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{537B20EA-C0AC-494B-BFDC-05B417DE60F6}">
@@ -5571,7 +5839,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0E3C63E-EA25-5849-AC4A-F1A294A10FF6}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
+            <xm:f>Players!$A$2:$A$182</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -5586,7 +5854,7 @@
   <sheetPr>
     <tabColor rgb="FF800000"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -5595,29 +5863,33 @@
     <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75"/>
+    <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="16" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>0</v>
@@ -5626,240 +5898,315 @@
         <v>2</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75">
+        <v>223</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C6" s="23" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>West Indies</v>
       </c>
       <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75">
+      <c r="E6" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C7" s="23" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75">
+      <c r="E7" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75">
+        <v>224</v>
+      </c>
+      <c r="E8" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Ireland</v>
       </c>
       <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75">
+      <c r="E9" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.75">
+      <c r="E10" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75">
+      <c r="E11" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75">
+      <c r="E12" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75">
+      <c r="E13" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75">
+      <c r="E14" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75">
+      <c r="E15" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.75">
+      <c r="E16" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75">
+        <v>225</v>
+      </c>
+      <c r="E17" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="23" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.75">
+      <c r="E18" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.75">
+      <c r="E19" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
+      <c r="E20" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
+      <c r="E21" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
+      <c r="E22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(MB[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D23" s="3"/>
+      <c r="E23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="A1:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{F2CD0A4C-1D79-984B-95EA-91B04E387101}">
@@ -5875,7 +6222,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{820AB018-EF87-7145-BE50-60BE0E869C31}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
+            <xm:f>Players!$A$2:$A$182</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -5890,7 +6237,7 @@
   <sheetPr>
     <tabColor rgb="FFE759AC"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -5899,29 +6246,33 @@
     <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-    </row>
-    <row r="5" spans="1:4">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75"/>
+    <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="18" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>0</v>
@@ -5930,196 +6281,255 @@
         <v>2</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>223</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C8" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Sri Lanka</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>225</v>
+      </c>
+      <c r="E9" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="23" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" s="23" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="23" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Pakistan</v>
       </c>
       <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>224</v>
+      </c>
+      <c r="E17" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="3">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -6129,8 +6539,12 @@
         <v/>
       </c>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
+      <c r="E20" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -6140,8 +6554,12 @@
         <v/>
       </c>
       <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
+      <c r="E21" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -6151,8 +6569,12 @@
         <v/>
       </c>
       <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
+      <c r="E22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -6162,10 +6584,14 @@
         <v/>
       </c>
       <c r="D23" s="3"/>
+      <c r="E23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="A1:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{4DA19308-650D-4849-A026-734DD25B26E1}">
@@ -6181,7 +6607,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DB2A4319-3327-BA40-AFC7-86FBCD333A45}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
+            <xm:f>Players!$A$2:$A$182</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -6196,7 +6622,7 @@
   <sheetPr>
     <tabColor rgb="FF0B0C10"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -6205,29 +6631,33 @@
     <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75"/>
+    <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="17" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>0</v>
@@ -6236,244 +6666,319 @@
         <v>2</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>223</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" s="23" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>West Indies</v>
       </c>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>224</v>
+      </c>
+      <c r="E14" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>England</v>
       </c>
       <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>225</v>
+      </c>
+      <c r="E16" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Ireland</v>
       </c>
       <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C20" s="23" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>West Indies</v>
       </c>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
+      <c r="E20" s="3">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="23" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
+      <c r="E21" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
+      <c r="E22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KKR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D23" s="3"/>
+      <c r="E23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="A1:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{49F8774F-0262-B747-A0D4-0DFFCD394070}">
@@ -6489,7 +6994,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{51EC2756-B05B-6E45-BD79-B03B65274D71}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
+            <xm:f>Players!$A$2:$A$182</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -6504,7 +7009,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -6513,29 +7018,33 @@
     <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75"/>
+    <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="24" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>0</v>
@@ -6544,142 +7053,185 @@
         <v>2</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75">
+        <v>223</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Scotland</v>
       </c>
       <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75">
+      <c r="E6" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>Injured</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75">
+      <c r="E7" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75">
+      <c r="E8" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75">
+      <c r="E9" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Ireland</v>
       </c>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.75">
+      <c r="E10" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="23" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>Sri Lanka</v>
+        <v>152</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <v>Scotland</v>
       </c>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75">
+      <c r="E11" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>Replacement</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>England</v>
+        <v>183</v>
+      </c>
+      <c r="C12" s="23" t="str">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <v>Sri Lanka</v>
       </c>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75">
+      <c r="E12" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="C13" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>Ireland</v>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <v>England</v>
       </c>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75">
+      <c r="E13" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>168</v>
+        <v>93</v>
       </c>
       <c r="C14" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>South Africa</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <v>Ireland</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="C15" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <v>South Africa</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -6687,95 +7239,129 @@
         <v>75</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75">
+      <c r="D16" s="3"/>
+      <c r="E16" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>205</v>
+        <v>76</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>West Indies</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.75">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <v>India</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>209</v>
+      </c>
       <c r="C18" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v/>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <v>West Indies</v>
       </c>
       <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.75">
+      <c r="E18" s="3">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.75">
+      <c r="E19" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
+      <c r="E20" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
+      <c r="E21" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="23" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
+      <c r="E22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="23" t="str">
-        <f>IFERROR(VLOOKUP(CT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v/>
       </c>
       <c r="D23" s="3"/>
+      <c r="E23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="A1:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{97976402-F241-C347-AB16-6F7C94EE9217}">
@@ -6791,7 +7377,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CE6FA05C-0077-3B42-8DF8-DE46C05DBD3F}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
+            <xm:f>Players!$A$2:$A$182</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -6806,7 +7392,7 @@
   <sheetPr>
     <tabColor rgb="FF046307"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -6815,214 +7401,273 @@
     <col min="4" max="4" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34" t="s">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75"/>
+    <row r="5" spans="1:5" ht="15.75">
+      <c r="A5" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="34" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75">
+      <c r="D5" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C6" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>West Indies</v>
       </c>
       <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75">
+      <c r="E6" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="3">
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Ireland</v>
       </c>
       <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75">
+      <c r="E7" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="3">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C8" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75">
+      <c r="E8" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75">
       <c r="A9" s="3">
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Pakistan</v>
       </c>
       <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75">
+      <c r="E9" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="3">
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75">
+        <v>224</v>
+      </c>
+      <c r="E10" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75">
       <c r="A11" s="3">
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75">
+      <c r="E11" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75">
       <c r="A12" s="3">
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75">
+        <v>225</v>
+      </c>
+      <c r="E12" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="3">
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C13" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75">
+      <c r="E13" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="3">
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75">
+      <c r="E14" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="3">
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
       <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75">
+      <c r="E15" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="3">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.75">
+      <c r="E16" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75">
       <c r="A17" s="3">
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="23" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Pakistan</v>
       </c>
       <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="3">
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="3">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -7032,8 +7677,12 @@
         <v/>
       </c>
       <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -7043,8 +7692,12 @@
         <v/>
       </c>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
+      <c r="E20" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -7054,8 +7707,12 @@
         <v/>
       </c>
       <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
+      <c r="E21" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -7065,8 +7722,12 @@
         <v/>
       </c>
       <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
+      <c r="E22" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -7076,10 +7737,14 @@
         <v/>
       </c>
       <c r="D23" s="3"/>
+      <c r="E23" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="A1:E3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D23" xr:uid="{EEC09B6C-3F7E-7949-8628-B712B6AF6D47}">
@@ -7095,7 +7760,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5307CA3B-82D8-A448-BD97-BBAFE8855CF8}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$181</xm:f>
+            <xm:f>Players!$A$2:$A$182</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>

--- a/dwl-fantasy-platform/backend/WWC_Config.xlsx
+++ b/dwl-fantasy-platform/backend/WWC_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kishan/Downloads/Delulu Leagues/DWL Delulu Women's League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B058914F-5528-4256-BD0F-552B59F8E1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A490ACC9-F00A-4D73-812D-C8B09ED39343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="8" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="4" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="233">
   <si>
     <t>Player Name</t>
   </si>
@@ -265,6 +265,12 @@
     <t>Nandani Sharma</t>
   </si>
   <si>
+    <t>Prema Rawat</t>
+  </si>
+  <si>
+    <t>Replacement</t>
+  </si>
+  <si>
     <t>Radha Yadav</t>
   </si>
   <si>
@@ -283,6 +289,9 @@
     <t>Shreyanka Patil</t>
   </si>
   <si>
+    <t>Injured</t>
+  </si>
+  <si>
     <t>Smriti Mandhana</t>
   </si>
   <si>
@@ -487,9 +496,6 @@
     <t>Scotland</t>
   </si>
   <si>
-    <t>Injured</t>
-  </si>
-  <si>
     <t>Ailsa Lister</t>
   </si>
   <si>
@@ -503,9 +509,6 @@
   </si>
   <si>
     <t>Hannah Rainey</t>
-  </si>
-  <si>
-    <t>Replacement</t>
   </si>
   <si>
     <t>Katherine Fraser</t>
@@ -1493,10 +1496,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}" name="WWC_Players_All" displayName="WWC_Players_All" ref="A1:F182" totalsRowShown="0">
-  <autoFilter ref="A1:F182" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E182">
-    <sortCondition ref="C1:C182"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}" name="WWC_Players_All" displayName="WWC_Players_All" ref="A1:F183" totalsRowShown="0">
+  <autoFilter ref="A1:F183" xr:uid="{D6C0CFBB-B781-B648-9D72-EBCEFAF7AED5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E183">
+    <sortCondition ref="C1:C183"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9375827B-7F58-154E-8A6D-89BE21277304}" name="Player Name"/>
@@ -1569,7 +1572,7 @@
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}" name="KQ" displayName="KQ" ref="A5:E23" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
   <autoFilter ref="A5:E23" xr:uid="{61129C46-FAC5-6246-92A2-AEAD87339477}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:E23">
     <sortCondition ref="B5:B23"/>
   </sortState>
   <tableColumns count="5">
@@ -1988,7 +1991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7675FD65-5A90-8049-AA35-694183767B48}">
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
@@ -2910,16 +2913,18 @@
         <v>66</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E54" s="25">
-        <v>15.5</v>
-      </c>
-      <c r="F54" s="26"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="26" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>27</v>
@@ -2928,37 +2933,37 @@
         <v>66</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E55" s="25">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="F55" s="26"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>66</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E56" s="25">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F56" s="26"/>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>66</v>
@@ -2967,34 +2972,34 @@
         <v>9</v>
       </c>
       <c r="E57" s="25">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="F57" s="26"/>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>66</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E58" s="25">
-        <v>0.5</v>
+        <v>14.5</v>
       </c>
       <c r="F58" s="26"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>66</v>
@@ -3003,69 +3008,75 @@
         <v>13</v>
       </c>
       <c r="E59" s="25">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="F59" s="26"/>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>66</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E60" s="25">
-        <v>18.5</v>
-      </c>
-      <c r="F60" s="26"/>
+        <v>3</v>
+      </c>
+      <c r="F60" s="26" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>66</v>
       </c>
       <c r="D61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="25">
+        <v>18.5</v>
+      </c>
+      <c r="F61" s="26"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="25">
+      <c r="E62" s="25">
         <v>13.5</v>
       </c>
-      <c r="F61" s="26"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="25"/>
       <c r="F62" s="26"/>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="25"/>
@@ -3073,45 +3084,45 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="25">
-        <v>4.5</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" s="25"/>
       <c r="F64" s="26"/>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D65" s="8"/>
-      <c r="E65" s="25"/>
+      <c r="D65" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="25">
+        <v>4.5</v>
+      </c>
       <c r="F65" s="26"/>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="25"/>
@@ -3119,75 +3130,77 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="25">
-        <v>0.5</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D67" s="8"/>
+      <c r="E67" s="25"/>
       <c r="F67" s="26"/>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="25"/>
+        <v>85</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="25">
+        <v>0.5</v>
+      </c>
       <c r="F68" s="26"/>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E69" s="25">
-        <v>6</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D69" s="8"/>
+      <c r="E69" s="25"/>
       <c r="F69" s="26"/>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D70" s="8"/>
-      <c r="E70" s="25"/>
+        <v>85</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="25">
+        <v>6</v>
+      </c>
       <c r="F70" s="26"/>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B71" s="8"/>
+        <v>93</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>7</v>
+      </c>
       <c r="C71" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="25"/>
@@ -3195,13 +3208,11 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>7</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B72" s="8"/>
       <c r="C72" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D72" s="8"/>
       <c r="E72" s="25"/>
@@ -3209,91 +3220,91 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="25">
-        <v>0.5</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D73" s="8"/>
+      <c r="E73" s="25"/>
       <c r="F73" s="26"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D74" s="8"/>
-      <c r="E74" s="25"/>
+        <v>85</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="25">
+        <v>0.5</v>
+      </c>
       <c r="F74" s="26"/>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" s="25">
-        <v>9.5</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="25"/>
       <c r="F75" s="26"/>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B76" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="25">
+        <v>9.5</v>
+      </c>
+      <c r="F76" s="26"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D76" s="8"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="26"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D77" s="9"/>
+      <c r="C77" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D77" s="8"/>
       <c r="E77" s="25"/>
       <c r="F77" s="26"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="25"/>
@@ -3301,13 +3312,13 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="25"/>
@@ -3315,13 +3326,13 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>98</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="25"/>
@@ -3329,13 +3340,13 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="25"/>
@@ -3343,13 +3354,13 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="25"/>
@@ -3357,13 +3368,13 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="25"/>
@@ -3371,13 +3382,13 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="25"/>
@@ -3385,13 +3396,13 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="25"/>
@@ -3399,13 +3410,13 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="25"/>
@@ -3413,45 +3424,45 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87" s="25">
-        <v>1</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D87" s="9"/>
+      <c r="E87" s="25"/>
       <c r="F87" s="26"/>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D88" s="9"/>
-      <c r="E88" s="25"/>
+        <v>101</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E88" s="25">
+        <v>1</v>
+      </c>
       <c r="F88" s="26"/>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D89" s="9"/>
       <c r="E89" s="25"/>
@@ -3459,13 +3470,13 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D90" s="9"/>
       <c r="E90" s="25"/>
@@ -3473,34 +3484,30 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B91" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D91" s="9"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="26"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B92" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C91" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D91" s="9" t="s">
+      <c r="C92" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D92" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="E91" s="25">
-        <v>1</v>
-      </c>
-      <c r="F91" s="26"/>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B92" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>11</v>
       </c>
       <c r="E92" s="25">
         <v>1</v>
@@ -3509,16 +3516,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E93" s="25">
         <v>1</v>
@@ -3527,216 +3534,216 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D94" s="10"/>
-      <c r="E94" s="25"/>
+        <v>117</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="25">
+        <v>1</v>
+      </c>
       <c r="F94" s="26"/>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C95" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E95" s="25">
-        <v>1</v>
-      </c>
+      <c r="D95" s="10"/>
+      <c r="E95" s="25"/>
       <c r="F95" s="26"/>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D96" s="10"/>
-      <c r="E96" s="25"/>
+        <v>117</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="25">
+        <v>1</v>
+      </c>
       <c r="F96" s="26"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E97" s="25">
-        <v>1</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D97" s="10"/>
+      <c r="E97" s="25"/>
       <c r="F97" s="26"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E98" s="25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F98" s="26"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E99" s="25">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="F99" s="26"/>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D100" s="10"/>
-      <c r="E100" s="25"/>
+        <v>117</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E100" s="25">
+        <v>10.5</v>
+      </c>
       <c r="F100" s="26"/>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="25">
-        <v>40</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D101" s="10"/>
+      <c r="E101" s="25"/>
       <c r="F101" s="26"/>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D102" s="10"/>
-      <c r="E102" s="25"/>
+        <v>117</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="25">
+        <v>40</v>
+      </c>
       <c r="F102" s="26"/>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E103" s="25">
-        <v>1</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D103" s="10"/>
+      <c r="E103" s="25"/>
       <c r="F103" s="26"/>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E104" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="26"/>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E105" s="25">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F105" s="26"/>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E106" s="25">
         <v>13</v>
@@ -3744,60 +3751,64 @@
       <c r="F106" s="26"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B107" s="11" t="s">
+      <c r="A107" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B107" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C107" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D107" s="11"/>
-      <c r="E107" s="25"/>
+      <c r="C107" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="25">
+        <v>13</v>
+      </c>
       <c r="F107" s="26"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D108" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E108" s="25">
-        <v>1</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D108" s="11"/>
+      <c r="E108" s="25"/>
       <c r="F108" s="26"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D109" s="11"/>
-      <c r="E109" s="25"/>
+        <v>133</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109" s="25">
+        <v>1</v>
+      </c>
       <c r="F109" s="26"/>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110" s="11" t="s">
         <v>133</v>
-      </c>
-      <c r="B110" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C110" s="11" t="s">
-        <v>130</v>
       </c>
       <c r="D110" s="11"/>
       <c r="E110" s="25"/>
@@ -3805,45 +3816,45 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" s="25">
-        <v>8</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D111" s="11"/>
+      <c r="E111" s="25"/>
       <c r="F111" s="26"/>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D112" s="11"/>
-      <c r="E112" s="25"/>
+        <v>133</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="25">
+        <v>8</v>
+      </c>
       <c r="F112" s="26"/>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D113" s="11"/>
       <c r="E113" s="25"/>
@@ -3851,63 +3862,63 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E114" s="25">
-        <v>2</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D114" s="11"/>
+      <c r="E114" s="25"/>
       <c r="F114" s="26"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E115" s="25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F115" s="26"/>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B116" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E116" s="25">
         <v>7</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D116" s="11"/>
-      <c r="E116" s="25"/>
       <c r="F116" s="26"/>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D117" s="11"/>
       <c r="E117" s="25"/>
@@ -3915,45 +3926,45 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E118" s="25">
-        <v>9.5</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D118" s="11"/>
+      <c r="E118" s="25"/>
       <c r="F118" s="26"/>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="25"/>
+        <v>133</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="25">
+        <v>9.5</v>
+      </c>
       <c r="F119" s="26"/>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D120" s="11"/>
       <c r="E120" s="25"/>
@@ -3961,61 +3972,61 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D121" s="11"/>
       <c r="E121" s="25"/>
       <c r="F121" s="26"/>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="B122" s="12" t="s">
+      <c r="A122" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B122" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C122" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="25">
-        <v>2</v>
-      </c>
-      <c r="F122" s="26" t="s">
-        <v>147</v>
-      </c>
+      <c r="C122" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D122" s="11"/>
+      <c r="E122" s="25"/>
+      <c r="F122" s="26"/>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="12" t="s">
         <v>148</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D123" s="12"/>
-      <c r="E123" s="25"/>
-      <c r="F123" s="26"/>
+        <v>149</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="25">
+        <v>2</v>
+      </c>
+      <c r="F123" s="26" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="B124" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C124" s="12" t="s">
-        <v>146</v>
       </c>
       <c r="D124" s="12"/>
       <c r="E124" s="25"/>
@@ -4023,13 +4034,13 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D125" s="12"/>
       <c r="E125" s="25"/>
@@ -4037,11 +4048,13 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B126" s="12"/>
+        <v>152</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="C126" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D126" s="12"/>
       <c r="E126" s="25"/>
@@ -4049,37 +4062,35 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B127" s="12" t="s">
-        <v>27</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="B127" s="12"/>
       <c r="C127" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" s="25">
-        <v>0</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>153</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="D127" s="12"/>
+      <c r="E127" s="25"/>
+      <c r="F127" s="26"/>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="12" t="s">
         <v>154</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D128" s="12"/>
-      <c r="E128" s="25"/>
-      <c r="F128" s="26"/>
+        <v>149</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="25">
+        <v>0</v>
+      </c>
+      <c r="F128" s="26" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="12" t="s">
@@ -4089,14 +4100,10 @@
         <v>7</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D129" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E129" s="25">
-        <v>8.5</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="D129" s="12"/>
+      <c r="E129" s="25"/>
       <c r="F129" s="26"/>
     </row>
     <row r="130" spans="1:6">
@@ -4104,13 +4111,17 @@
         <v>156</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D130" s="12"/>
-      <c r="E130" s="25"/>
+        <v>149</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E130" s="25">
+        <v>8.5</v>
+      </c>
       <c r="F130" s="26"/>
     </row>
     <row r="131" spans="1:6">
@@ -4121,7 +4132,7 @@
         <v>27</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D131" s="12"/>
       <c r="E131" s="25"/>
@@ -4132,10 +4143,10 @@
         <v>158</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D132" s="12"/>
       <c r="E132" s="25"/>
@@ -4146,10 +4157,10 @@
         <v>159</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D133" s="12"/>
       <c r="E133" s="25"/>
@@ -4160,17 +4171,13 @@
         <v>160</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D134" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E134" s="25">
-        <v>0.5</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="D134" s="12"/>
+      <c r="E134" s="25"/>
       <c r="F134" s="26"/>
     </row>
     <row r="135" spans="1:6">
@@ -4178,13 +4185,17 @@
         <v>161</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D135" s="12"/>
-      <c r="E135" s="25"/>
+        <v>149</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" s="25">
+        <v>0.5</v>
+      </c>
       <c r="F135" s="26"/>
     </row>
     <row r="136" spans="1:6">
@@ -4192,10 +4203,10 @@
         <v>162</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D136" s="12"/>
       <c r="E136" s="25"/>
@@ -4206,52 +4217,48 @@
         <v>163</v>
       </c>
       <c r="B137" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D137" s="12"/>
+      <c r="E137" s="25"/>
+      <c r="F137" s="26"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B138" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C137" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D137" s="12" t="s">
+      <c r="C138" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D138" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E137" s="25">
+      <c r="E138" s="25">
         <v>2</v>
-      </c>
-      <c r="F137" s="26"/>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="B138" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C138" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E138" s="25">
-        <v>4.5</v>
       </c>
       <c r="F138" s="26"/>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B139" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B139" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C139" s="13" t="s">
-        <v>165</v>
-      </c>
       <c r="D139" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E139" s="25">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="F139" s="26"/>
     </row>
@@ -4260,16 +4267,16 @@
         <v>167</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E140" s="25">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="F140" s="26"/>
     </row>
@@ -4281,13 +4288,13 @@
         <v>7</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E141" s="25">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="F141" s="26"/>
     </row>
@@ -4296,16 +4303,16 @@
         <v>169</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E142" s="25">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F142" s="26"/>
     </row>
@@ -4314,16 +4321,16 @@
         <v>170</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E143" s="25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F143" s="26"/>
     </row>
@@ -4332,16 +4339,16 @@
         <v>171</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E144" s="25">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F144" s="26"/>
     </row>
@@ -4350,16 +4357,16 @@
         <v>172</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E145" s="25">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="F145" s="26"/>
     </row>
@@ -4371,13 +4378,13 @@
         <v>7</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E146" s="25">
-        <v>8.5</v>
+        <v>20.5</v>
       </c>
       <c r="F146" s="26"/>
     </row>
@@ -4386,16 +4393,16 @@
         <v>174</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E147" s="25">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="F147" s="26"/>
     </row>
@@ -4407,13 +4414,13 @@
         <v>27</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E148" s="25">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F148" s="26"/>
     </row>
@@ -4422,16 +4429,16 @@
         <v>176</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E149" s="25">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F149" s="26"/>
     </row>
@@ -4440,16 +4447,16 @@
         <v>177</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E150" s="25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F150" s="26"/>
     </row>
@@ -4458,16 +4465,16 @@
         <v>178</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E151" s="25">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="F151" s="26"/>
     </row>
@@ -4476,45 +4483,49 @@
         <v>179</v>
       </c>
       <c r="B152" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E152" s="25">
+        <v>6.5</v>
+      </c>
+      <c r="F152" s="26"/>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B153" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C152" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D152" s="13"/>
-      <c r="E152" s="25"/>
-      <c r="F152" s="26"/>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B153" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C153" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D153" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E153" s="25">
-        <v>10</v>
-      </c>
+      <c r="C153" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D153" s="13"/>
+      <c r="E153" s="25"/>
       <c r="F153" s="26"/>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B154" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="B154" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C154" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D154" s="15"/>
-      <c r="E154" s="25"/>
+      <c r="D154" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E154" s="25">
+        <v>10</v>
+      </c>
       <c r="F154" s="26"/>
     </row>
     <row r="155" spans="1:6">
@@ -4525,14 +4536,10 @@
         <v>19</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D155" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" s="25">
-        <v>1</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D155" s="15"/>
+      <c r="E155" s="25"/>
       <c r="F155" s="26"/>
     </row>
     <row r="156" spans="1:6">
@@ -4543,10 +4550,14 @@
         <v>19</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D156" s="15"/>
-      <c r="E156" s="25"/>
+        <v>182</v>
+      </c>
+      <c r="D156" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="25">
+        <v>1</v>
+      </c>
       <c r="F156" s="26"/>
     </row>
     <row r="157" spans="1:6">
@@ -4557,7 +4568,7 @@
         <v>19</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D157" s="15"/>
       <c r="E157" s="25"/>
@@ -4568,10 +4579,10 @@
         <v>186</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D158" s="15"/>
       <c r="E158" s="25"/>
@@ -4582,10 +4593,10 @@
         <v>187</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D159" s="15"/>
       <c r="E159" s="25"/>
@@ -4596,10 +4607,10 @@
         <v>188</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D160" s="15"/>
       <c r="E160" s="25"/>
@@ -4613,7 +4624,7 @@
         <v>27</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D161" s="15"/>
       <c r="E161" s="25"/>
@@ -4627,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D162" s="15"/>
       <c r="E162" s="25"/>
@@ -4638,10 +4649,10 @@
         <v>191</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D163" s="15"/>
       <c r="E163" s="25"/>
@@ -4652,10 +4663,10 @@
         <v>192</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D164" s="15"/>
       <c r="E164" s="25"/>
@@ -4669,7 +4680,7 @@
         <v>27</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D165" s="15"/>
       <c r="E165" s="25"/>
@@ -4683,14 +4694,10 @@
         <v>27</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D166" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E166" s="25">
-        <v>1</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D166" s="15"/>
+      <c r="E166" s="25"/>
       <c r="F166" s="26"/>
     </row>
     <row r="167" spans="1:6">
@@ -4698,52 +4705,52 @@
         <v>195</v>
       </c>
       <c r="B167" s="15" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D167" s="15" t="s">
         <v>28</v>
       </c>
       <c r="E167" s="25">
+        <v>1</v>
+      </c>
+      <c r="F167" s="26"/>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B168" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C168" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D168" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E168" s="25">
         <v>2</v>
-      </c>
-      <c r="F167" s="26"/>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="B168" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C168" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D168" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E168" s="25">
-        <v>1</v>
       </c>
       <c r="F168" s="26"/>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B169" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E169" s="25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F169" s="26"/>
     </row>
@@ -4752,13 +4759,17 @@
         <v>199</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D170" s="14"/>
-      <c r="E170" s="25"/>
+        <v>198</v>
+      </c>
+      <c r="D170" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E170" s="25">
+        <v>10</v>
+      </c>
       <c r="F170" s="26"/>
     </row>
     <row r="171" spans="1:6">
@@ -4769,14 +4780,10 @@
         <v>7</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D171" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E171" s="25">
-        <v>3.5</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="D171" s="14"/>
+      <c r="E171" s="25"/>
       <c r="F171" s="26"/>
     </row>
     <row r="172" spans="1:6">
@@ -4787,13 +4794,13 @@
         <v>7</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E172" s="25">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="F172" s="26"/>
     </row>
@@ -4802,16 +4809,16 @@
         <v>202</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E173" s="25">
-        <v>18.5</v>
+        <v>9</v>
       </c>
       <c r="F173" s="26"/>
     </row>
@@ -4820,13 +4827,17 @@
         <v>203</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D174" s="14"/>
-      <c r="E174" s="25"/>
+        <v>198</v>
+      </c>
+      <c r="D174" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E174" s="25">
+        <v>18.5</v>
+      </c>
       <c r="F174" s="26"/>
     </row>
     <row r="175" spans="1:6">
@@ -4834,10 +4845,10 @@
         <v>204</v>
       </c>
       <c r="B175" s="14" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D175" s="14"/>
       <c r="E175" s="25"/>
@@ -4851,14 +4862,10 @@
         <v>27</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D176" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E176" s="25">
-        <v>3</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="D176" s="14"/>
+      <c r="E176" s="25"/>
       <c r="F176" s="26"/>
     </row>
     <row r="177" spans="1:6">
@@ -4866,13 +4873,17 @@
         <v>206</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D177" s="14"/>
-      <c r="E177" s="25"/>
+        <v>198</v>
+      </c>
+      <c r="D177" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="25">
+        <v>3</v>
+      </c>
       <c r="F177" s="26"/>
     </row>
     <row r="178" spans="1:6">
@@ -4883,7 +4894,7 @@
         <v>7</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D178" s="14"/>
       <c r="E178" s="25"/>
@@ -4897,7 +4908,7 @@
         <v>7</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D179" s="14"/>
       <c r="E179" s="25"/>
@@ -4908,17 +4919,13 @@
         <v>209</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D180" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E180" s="25">
-        <v>2</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="D180" s="14"/>
+      <c r="E180" s="25"/>
       <c r="F180" s="26"/>
     </row>
     <row r="181" spans="1:6">
@@ -4926,16 +4933,16 @@
         <v>210</v>
       </c>
       <c r="B181" s="14" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E181" s="25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F181" s="26"/>
     </row>
@@ -4947,19 +4954,37 @@
         <v>7</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D182" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" s="25">
+        <v>6</v>
+      </c>
+      <c r="F182" s="26"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B183" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D183" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E182" s="25">
+      <c r="E183" s="25">
         <v>1</v>
       </c>
-      <c r="F182" s="26"/>
-    </row>
-    <row r="183" spans="1:6"/>
+      <c r="F183" s="26"/>
+    </row>
     <row r="184" spans="1:6"/>
     <row r="185" spans="1:6"/>
+    <row r="186" spans="1:6"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4972,7 +4997,7 @@
           <x14:formula1>
             <xm:f>DWLTeams!$B$2:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D182</xm:sqref>
+          <xm:sqref>D2:D183</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4990,15 +5015,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>13</v>
@@ -5006,7 +5031,7 @@
     </row>
     <row r="3" spans="1:2" ht="15.75">
       <c r="A3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>28</v>
@@ -5014,7 +5039,7 @@
     </row>
     <row r="4" spans="1:2" ht="15.75">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>24</v>
@@ -5022,7 +5047,7 @@
     </row>
     <row r="5" spans="1:2" ht="15.75">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -5030,7 +5055,7 @@
     </row>
     <row r="6" spans="1:2" ht="15.75">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
@@ -5038,7 +5063,7 @@
     </row>
     <row r="7" spans="1:2" ht="15.75">
       <c r="A7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
@@ -5046,7 +5071,7 @@
     </row>
     <row r="8" spans="1:2" ht="15.75">
       <c r="A8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
@@ -5085,7 +5110,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="29" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -5109,7 +5134,7 @@
     <row r="4" spans="1:5" ht="15.75"/>
     <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>0</v>
@@ -5118,7 +5143,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="28" t="s">
         <v>5</v>
@@ -5136,7 +5161,7 @@
         <v>Australia</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E6" s="23">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -5165,7 +5190,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5182,7 +5207,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5199,7 +5224,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C10" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5216,7 +5241,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C11" s="23" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5233,14 +5258,14 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C12" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E12" s="23">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -5303,7 +5328,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5320,7 +5345,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5337,7 +5362,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5354,16 +5379,16 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C19" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="23">
+      <c r="E19" s="23" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
-        <v>0</v>
+        <v>Injured</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75">
@@ -5388,7 +5413,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C21" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5450,7 +5475,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D030090-5C0F-BA4C-AA19-0E80536C4120}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$182</xm:f>
+            <xm:f>Players!$A$2:$A$183</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -5476,7 +5501,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -5500,7 +5525,7 @@
     <row r="4" spans="1:5" ht="15.75"/>
     <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>0</v>
@@ -5509,7 +5534,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>5</v>
@@ -5520,7 +5545,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C6" s="3" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5537,14 +5562,14 @@
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>West Indies</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E7" s="3">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -5573,7 +5598,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5590,7 +5615,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C10" s="3" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5624,7 +5649,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C12" s="3" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5658,7 +5683,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5682,7 +5707,7 @@
         <v>England</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E15" s="3">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -5694,7 +5719,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5711,7 +5736,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5745,7 +5770,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19" s="3" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5762,7 +5787,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C20" s="23" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5779,7 +5804,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="23" t="str">
         <f>IFERROR(VLOOKUP(JR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5839,7 +5864,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0E3C63E-EA25-5849-AC4A-F1A294A10FF6}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$182</xm:f>
+            <xm:f>Players!$A$2:$A$183</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -5865,7 +5890,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -5889,7 +5914,7 @@
     <row r="4" spans="1:5" ht="15.75"/>
     <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>0</v>
@@ -5898,7 +5923,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>5</v>
@@ -5909,7 +5934,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C6" s="23" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5926,7 +5951,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" s="23" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -5950,7 +5975,7 @@
         <v>India</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E8" s="3">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -5962,7 +5987,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6047,7 +6072,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6061,31 +6086,31 @@
     </row>
     <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>South Africa</v>
+        <v>India</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="3">
+      <c r="E15" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
-        <v>0</v>
+        <v>Replacement</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>India</v>
+        <v>South Africa</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3">
@@ -6095,18 +6120,16 @@
     </row>
     <row r="17" spans="1:5" ht="15.75">
       <c r="A17" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>225</v>
-      </c>
+        <v>India</v>
+      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="3">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
         <v>0</v>
@@ -6114,34 +6137,38 @@
     </row>
     <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="3">
+        <v>12</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
+        <v>England</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="3">
+        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75">
+      <c r="A19" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="23" t="str">
+      <c r="C19" s="23" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Australia</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
         <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.75">
-      <c r="A19" s="3">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="str">
-        <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
-        <v/>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75">
@@ -6222,7 +6249,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{820AB018-EF87-7145-BE50-60BE0E869C31}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$182</xm:f>
+            <xm:f>Players!$A$2:$A$183</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -6248,7 +6275,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -6272,7 +6299,7 @@
     <row r="4" spans="1:5" ht="15.75"/>
     <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>0</v>
@@ -6281,7 +6308,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>5</v>
@@ -6326,7 +6353,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6343,14 +6370,14 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>Sri Lanka</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E9" s="3">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -6413,7 +6440,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C13" s="23" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6447,7 +6474,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6464,7 +6491,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6481,14 +6508,14 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>New Zealand</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E17" s="3">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -6500,7 +6527,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6517,7 +6544,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C19" s="3" t="str">
         <f>IFERROR(VLOOKUP(RR[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6607,7 +6634,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DB2A4319-3327-BA40-AFC7-86FBCD333A45}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$182</xm:f>
+            <xm:f>Players!$A$2:$A$183</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -6633,7 +6660,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -6657,7 +6684,7 @@
     <row r="4" spans="1:5" ht="15.75"/>
     <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>0</v>
@@ -6666,7 +6693,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>5</v>
@@ -6728,7 +6755,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6796,7 +6823,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C13" s="3" t="str">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6813,14 +6840,14 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E14" s="3">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -6849,14 +6876,14 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E16" s="3">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -6868,7 +6895,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6885,7 +6912,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6902,7 +6929,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="str">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6919,7 +6946,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C20" s="23" t="str">
         <f>IFERROR(VLOOKUP(SS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -6994,7 +7021,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{51EC2756-B05B-6E45-BD79-B03B65274D71}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$182</xm:f>
+            <xm:f>Players!$A$2:$A$183</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -7020,7 +7047,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
@@ -7044,7 +7071,7 @@
     <row r="4" spans="1:5" ht="15.75"/>
     <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="24" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>0</v>
@@ -7053,7 +7080,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="24" t="s">
         <v>5</v>
@@ -7064,7 +7091,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C6" s="3" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7115,7 +7142,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7132,7 +7159,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7149,7 +7176,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7166,7 +7193,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C12" s="23" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7200,7 +7227,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7217,14 +7244,14 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>South Africa</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E15" s="3">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -7236,7 +7263,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7253,14 +7280,14 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E17" s="3">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -7272,7 +7299,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>IFERROR(VLOOKUP(SGS[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7377,7 +7404,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CE6FA05C-0077-3B42-8DF8-DE46C05DBD3F}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$182</xm:f>
+            <xm:f>Players!$A$2:$A$183</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>
@@ -7403,7 +7430,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="35" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -7427,7 +7454,7 @@
     <row r="4" spans="1:5" ht="15.75"/>
     <row r="5" spans="1:5" ht="15.75">
       <c r="A5" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>0</v>
@@ -7436,7 +7463,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>5</v>
@@ -7447,7 +7474,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C6" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7464,7 +7491,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7481,7 +7508,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C8" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7498,7 +7525,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7522,7 +7549,7 @@
         <v>Australia</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E10" s="3">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -7534,7 +7561,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7558,7 +7585,7 @@
         <v>India</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E12" s="3">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
@@ -7570,7 +7597,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C13" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7587,7 +7614,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7621,7 +7648,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7638,7 +7665,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C17" s="23" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7655,7 +7682,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>IFERROR(VLOOKUP(KT[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
@@ -7760,7 +7787,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5307CA3B-82D8-A448-BD97-BBAFE8855CF8}">
           <x14:formula1>
-            <xm:f>Players!$A$2:$A$182</xm:f>
+            <xm:f>Players!$A$2:$A$183</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B23</xm:sqref>
         </x14:dataValidation>

--- a/dwl-fantasy-platform/backend/WWC_Config.xlsx
+++ b/dwl-fantasy-platform/backend/WWC_Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kishan/Downloads/Delulu Leagues/DWL Delulu Women's League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A490ACC9-F00A-4D73-812D-C8B09ED39343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C3B7CB5-D92A-4357-8B1D-0F879E422BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="4" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="2" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -1530,7 +1530,7 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}" name="GD" displayName="GD" ref="A5:E23" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48" tableBorderDxfId="47">
   <autoFilter ref="A5:E23" xr:uid="{FF49E610-2074-9448-A682-4CF44B25CCCB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:D23">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:E23">
     <sortCondition ref="B5:B23"/>
   </sortState>
   <tableColumns count="5">
@@ -5345,16 +5345,16 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C17" s="3" t="str">
+        <v>73</v>
+      </c>
+      <c r="C17" s="23" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>Scotland</v>
+        <v>India</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="23">
+      <c r="E17" s="23" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
-        <v>0</v>
+        <v>Replacement</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75">
@@ -5362,11 +5362,11 @@
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>India</v>
+        <v>Scotland</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="23">
@@ -5379,16 +5379,16 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
         <v>India</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="23" t="str">
+      <c r="E19" s="23">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
-        <v>Injured</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75">
@@ -5396,16 +5396,16 @@
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C20" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>England</v>
+        <v>India</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="23">
+      <c r="E20" s="23" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
-        <v>0</v>
+        <v>Injured</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75">
@@ -5413,11 +5413,11 @@
         <v>16</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>Netherlands</v>
+        <v>England</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="23">
@@ -5430,11 +5430,11 @@
         <v>17</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="C22" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>England</v>
+        <v>Netherlands</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="23">
@@ -5446,15 +5446,17 @@
       <c r="A23" s="3">
         <v>18</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="23" t="str">
+      <c r="B23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="3" t="str">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v/>
+        <v>England</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="23" t="str">
+      <c r="E23" s="23">
         <f>IFERROR(VLOOKUP(GD[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6086,31 +6088,31 @@
     </row>
     <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>177</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>India</v>
+        <v>South Africa</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="3" t="str">
+      <c r="E15" s="3">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
-        <v>Replacement</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>South Africa</v>
+        <v>India</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3">
@@ -6120,16 +6122,18 @@
     </row>
     <row r="17" spans="1:5" ht="15.75">
       <c r="A17" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>India</v>
-      </c>
-      <c r="D17" s="3"/>
+        <v>England</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="E17" s="3">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
         <v>0</v>
@@ -6137,18 +6141,16 @@
     </row>
     <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="3" t="str">
+        <v>31</v>
+      </c>
+      <c r="C18" s="23" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>England</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>226</v>
-      </c>
+        <v>Australia</v>
+      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="3">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
         <v>0</v>
@@ -6156,19 +6158,17 @@
     </row>
     <row r="19" spans="1:5" ht="15.75">
       <c r="A19" s="3">
-        <v>13</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="23" t="str">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:D,3,0),"")</f>
-        <v>Australia</v>
+        <v/>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="3">
+      <c r="E19" s="3" t="str">
         <f>IFERROR(VLOOKUP(KQ[[#This Row],[Player Name]],Players!A:F,6,FALSE),"")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75">

--- a/dwl-fantasy-platform/backend/WWC_Config.xlsx
+++ b/dwl-fantasy-platform/backend/WWC_Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kishan/Downloads/Delulu Leagues/DWL Delulu Women's League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C3B7CB5-D92A-4357-8B1D-0F879E422BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F56A0A49-D764-4471-8715-5966C15C234B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="2" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" firstSheet="2" xr2:uid="{6957E4A2-D1A9-E849-B61B-E8AC1B9AF357}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -2913,7 +2913,7 @@
         <v>66</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E54" s="25">
         <v>0</v>
